--- a/output/EN_combined_output.xlsx
+++ b/output/EN_combined_output.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kasare Mukund Tukaram</t>
+          <t>Kasare Mukunda Tukaram</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kasare Madhuri Mukund</t>
+          <t>Kasare Madhuri Mukunda</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kasare Mukund</t>
+          <t>Kasare Mukunda</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Birendrasen Tarunachandr</t>
+          <t>Birendrasen Tarunachandra</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Birendrasen Tarunachandr</t>
+          <t>Birendrasen Tarunachandra</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Das Stivan Jojaph</t>
+          <t>Das Stivan Jojapha</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Das Jojaph</t>
+          <t>Das Jojapha</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Jadhav Lila Govind</t>
+          <t>Jadhav Lila Govinda</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Jadhav Nisha Govind</t>
+          <t>Jadhav Nisha Govinda</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Jadhav Gobind</t>
+          <t>Jadhav Gobinda</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Jadhav Anuradha Govind</t>
+          <t>Jadhav Anuradha Govinda</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Jadhav Gobind</t>
+          <t>Jadhav Gobinda</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Shetti Ramesh Di.</t>
+          <t>Shetti Ramesh D.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Khue Rajendr Nandakumar</t>
+          <t>Khue Rajendra Nandakumar</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Khue Rajashri Rajendr</t>
+          <t>Khue Rajashri Rajendra</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Khue Rajendr</t>
+          <t>Khue Rajendra</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Bangera End Q</t>
+          <t>Bangera Enda Q</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Bangera Hemant Ramesh</t>
+          <t>Bangera Hemanta Ramesh</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Anachar Satish Vhi.</t>
+          <t>Anachar Satish V.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Anachar Vhi.</t>
+          <t>Anachar V.</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Anachar Dinesh Vhi.</t>
+          <t>Anachar Dinesh V.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Anachar Vhi.</t>
+          <t>Anachar V.</t>
         </is>
       </c>
     </row>
@@ -3696,12 +3696,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Uttekar Anita Anant</t>
+          <t>Uttekar Anita Ananta</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Uttekar Anant</t>
+          <t>Uttekar Ananta</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Lakshman Lakshman Anant</t>
+          <t>Lakshman Lakshman Ananta</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Manyuel Ennthoni Phransis Va Manyuel Phransis Q</t>
+          <t>Menyuel Ennthoni Phransis Va Menyuel Phransis Q</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Manyuel Ainnthoni</t>
+          <t>Menyuel Ainnthoni</t>
         </is>
       </c>
     </row>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Manyuel Vilsent Ennthoni</t>
+          <t>Menyuel Vilsenta Ennthoni</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Manyuel Ennthoni</t>
+          <t>Menyuel Ennthoni</t>
         </is>
       </c>
     </row>
@@ -3946,12 +3946,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Manyuel Vhiktar Enthoni</t>
+          <t>Menyuel Vhiktar Enthoni</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Manyuel Ai~Nthoni</t>
+          <t>Menyuel Ai~Nthoni</t>
         </is>
       </c>
     </row>
@@ -4003,12 +4003,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Manyuel Vilyam Ainnthoni</t>
+          <t>Menyuel Vilyam Ainnthoni</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Manyuel Ainnthoni</t>
+          <t>Menyuel Ainnthoni</t>
         </is>
       </c>
     </row>
@@ -4060,12 +4060,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Mulukh Prakash Ramachandr</t>
+          <t>Mulukha Prakash Ramachandra</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Mulukh Ramachandr</t>
+          <t>Mulukha Ramachandra</t>
         </is>
       </c>
     </row>
@@ -4117,12 +4117,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Mulukh Pramila Prakash</t>
+          <t>Mulukha Pramila Prakash</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Mulukh Prakash</t>
+          <t>Mulukha Prakash</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Nayar Gopinath Karunakaran</t>
+          <t>Nayar Gopinatha Karunakaran</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Nayar Usha Gopinath</t>
+          <t>Nayar Usha Gopinatha</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Nayar Gopinath</t>
+          <t>Nayar Gopinatha</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pharnadis Jojeph Jan</t>
+          <t>Pharnadis Jojepha Jon</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Pharnadaus Jan</t>
+          <t>Pharnadaus Jon</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pharnadis Phlori Jojeph</t>
+          <t>Pharnadis Phlori Jojepha</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Pharnadis Jojeph</t>
+          <t>Pharnadis Jojepha</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pharnadis Jansita Jojeph</t>
+          <t>Pharnadis Jansita Jojepha</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Pharnadis Jojeph</t>
+          <t>Pharnadis Jojepha</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Disoja E~Ni Balatar</t>
+          <t>Disoja E~Ni Bolatar</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Jadhav Govind Rajaram</t>
+          <t>Jadhav Govinda Rajaram</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Jadhav Kamal Govind</t>
+          <t>Jadhav Kamal Govinda</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Jadhav Govind</t>
+          <t>Jadhav Govinda</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Kuttan Vasanda Ke.</t>
+          <t>Kuttan Vasanda K.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Kuttan Ke.</t>
+          <t>Kuttan K.</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Kuttan Sanjivakumar Ke.</t>
+          <t>Kuttan Sanjivakumar K.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Kuttan Ke.</t>
+          <t>Kuttan K.</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Karmakar Sureshachandr Navakuma</t>
+          <t>Karmakar Sureshachandra Navakuma</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Karmakar Pornima Sureshachandr Pa Karmakar Sureshachandr Satri</t>
+          <t>Karmakar Pornima Sureshachandra Pa Karmakar Sureshachandra Satri</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Kukoyan Gita Esa.</t>
+          <t>Kukoyan Gita S.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Kukoyan Esa.</t>
+          <t>Kukoyan S.</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Disoja Stin I</t>
+          <t>Disoja Ostin I</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Disoja Mariya Stin</t>
+          <t>Disoja Mariya Ostin</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Disoja Stin</t>
+          <t>Disoja Ostin</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Vab Sinh Rayabahadur</t>
+          <t>Vab Sinha Rayabahadur</t>
         </is>
       </c>
     </row>
@@ -6499,12 +6499,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Sinh Shobha Kamalesh</t>
+          <t>Sinha Shobha Kamalesh</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Sinh Kamalesh</t>
+          <t>Sinha Kamalesh</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Soji Vargij Ti. Soji Ti.Ar Shu</t>
+          <t>Soji Vargij T. Soji Ti.Ar Shu</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Tidake Shailendr Jagaderav</t>
+          <t>Tidake Shailendra Jagaderav</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Tidake Aruna Shailendr</t>
+          <t>Tidake Aruna Shailendra</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Tidake Shailendr</t>
+          <t>Tidake Shailendra</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Imyanyuel Danal Hetri Ba Isyanyuel Hetri Q</t>
+          <t>Imyenyuel Donal Hetri Ba Isyenyuel Hetri Q</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Imyenyuel Silviya Danal</t>
+          <t>Imyenyuel Silviya Donal</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Imyenyuel Danal</t>
+          <t>Imyenyuel Donal</t>
         </is>
       </c>
     </row>
@@ -6942,12 +6942,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Imyanyuel Sujan Danal</t>
+          <t>Imyanyuel Sujan Donal</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Imyenyuel Danal</t>
+          <t>Imyenyuel Donal</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Imyanyuel Sa~Rophin Danal</t>
+          <t>Imyenyuel Sa~Rophin Donal</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Imyanyuel Danal</t>
+          <t>Imyenyuel Donal</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Vab Sing Sitaram</t>
+          <t>Vab Singa Sitaram</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Sing Satyavati Shrabanakuma</t>
+          <t>Singa Satyavati Shrabanakuma</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Sing Shravanakumar</t>
+          <t>Singa Shravanakumar</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Shravanakumar Sing Shravanakumar</t>
+          <t>Shravanakumar Singa Shravanakumar</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Sing Radhesham Sitaram</t>
+          <t>Singa Radhesham Sitaram</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Sing Sitaram</t>
+          <t>Singa Sitaram</t>
         </is>
       </c>
     </row>
@@ -7586,12 +7586,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Vagae Mangesh Jagannath</t>
+          <t>Vagae Mangesh Jagannatha</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Vagae Jagannath</t>
+          <t>Vagae Jagannatha</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Vagae Jagannath Mangesh</t>
+          <t>Vagae Jagannatha Mangesh</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Shinde Chandrakant Anant</t>
+          <t>Shinde Chandrakanta Ananta</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Shinde Anant</t>
+          <t>Shinde Ananta</t>
         </is>
       </c>
     </row>
@@ -8209,12 +8209,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Shinde Rohini Chandrakant</t>
+          <t>Shinde Rohini Chandrakanta</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Shinde Chandrakant</t>
+          <t>Shinde Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Shinde Nitin Chandrakant</t>
+          <t>Shinde Nitin Chandrakanta</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Shinde Chandrakant</t>
+          <t>Shinde Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -8323,12 +8323,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Shinde Nilesh Chandrakant</t>
+          <t>Shinde Nilesh Chandrakanta</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Shinde Chandrakant</t>
+          <t>Shinde Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Isuph Shekh Insuph</t>
+          <t>Isupha Shekha Insupha</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Shekh Gajala Salim</t>
+          <t>Shekha Gajala Salim</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Shekh Salim</t>
+          <t>Shekha Salim</t>
         </is>
       </c>
     </row>
@@ -8816,12 +8816,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Shekh Minaj Salim</t>
+          <t>Shekha Minaj Salim</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Shekh Salim</t>
+          <t>Shekha Salim</t>
         </is>
       </c>
     </row>
@@ -8873,12 +8873,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Shekh Pharukh Salim</t>
+          <t>Shekha Pharukha Salim</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Shekh Salim</t>
+          <t>Shekha Salim</t>
         </is>
       </c>
     </row>
@@ -8930,12 +8930,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Shekh Abdul Navab</t>
+          <t>Shekha Abdul Navab</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Shekh Navab</t>
+          <t>Shekha Navab</t>
         </is>
       </c>
     </row>
@@ -8987,12 +8987,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Shekh Kamal Navab</t>
+          <t>Shekha Kamal Navab</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Shekh Navab</t>
+          <t>Shekha Navab</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Shekh Imbram Navab</t>
+          <t>Shekha Imbram Navab</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Shekh Navab</t>
+          <t>Shekha Navab</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Shekh Aphasha Navab</t>
+          <t>Shekha Aphasha Navab</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Shekh Navab</t>
+          <t>Shekha Navab</t>
         </is>
       </c>
     </row>
@@ -9272,12 +9272,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Parelakar Bhagavat Ramachandr</t>
+          <t>Parelakar Bhagavat Ramachandra</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Padelakar Ramachandr</t>
+          <t>Padelakar Ramachandra</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9862,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Sakapa Prajakta Ramakant</t>
+          <t>Sakapa Prajakta Ramakanta</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Sakapa Ramakant</t>
+          <t>Sakapa Ramakanta</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Yadav Lalachand Mangalaprasad</t>
+          <t>Yadav Lalachanda Mangalaprasad</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Yadav Lalachand</t>
+          <t>Yadav Lalachanda</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Peti Rabart Eat</t>
+          <t>Peti Robarta Eat</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Peti Hilda Rabart</t>
+          <t>Peti Hilda Robarta</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Pete Rabart</t>
+          <t>Pete Robarta</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Dandekar Aravind Gajanan</t>
+          <t>Dandekar Aravinda Gajanan</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Dandekar Shila Aravind</t>
+          <t>Dandekar Shila Aravinda</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Dandekar Aravind</t>
+          <t>Dandekar Aravinda</t>
         </is>
       </c>
     </row>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Achary Ratnakar Narasih</t>
+          <t>Acharya Ratnakar Narasih</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Achary Aravind</t>
+          <t>Acharya Aravinda</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Achary Gita Ratnakar</t>
+          <t>Acharya Gita Ratnakar</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Achary Ratnakar</t>
+          <t>Acharya Ratnakar</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Achary Nabisab</t>
+          <t>Acharya Nabisab</t>
         </is>
       </c>
     </row>
@@ -11439,12 +11439,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Bhalachandran Sharada Ke.</t>
+          <t>Bhalachandran Sharada K.</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Bhalachandran Ke.</t>
+          <t>Bhalachandran K.</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Mahale Prashant Dinakar</t>
+          <t>Mahale Prashanta Dinakar</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Shinde Shashikant Tukaram</t>
+          <t>Shinde Shashikanta Tukaram</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Shinde Sangita Shishikant</t>
+          <t>Shinde Sangita Shishikanta</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>Shinde Shishikant</t>
+          <t>Shinde Shishikanta</t>
         </is>
       </c>
     </row>
@@ -11937,12 +11937,12 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Khantaval Chandravallabh Ema.</t>
+          <t>Khantaval Chandravallabha M.</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>Khataval Ema.</t>
+          <t>Khataval M.</t>
         </is>
       </c>
     </row>
@@ -11994,12 +11994,12 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Khantaval Anandi Chandravallabh</t>
+          <t>Khantaval Anandi Chandravallabha</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Khantaval Chandravallabh</t>
+          <t>Khantaval Chandravallabha</t>
         </is>
       </c>
     </row>
@@ -12051,12 +12051,12 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Khantaval Shveta Chandravallabh</t>
+          <t>Khantaval Shveta Chandravallabha</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>Khantaval Chandravallabh</t>
+          <t>Khantaval Chandravallabha</t>
         </is>
       </c>
     </row>
@@ -12227,12 +12227,12 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Saliyan Shekhar Esa.</t>
+          <t>Saliyan Shekhar S.</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>Saliyan Esa.</t>
+          <t>Saliyan S.</t>
         </is>
       </c>
     </row>
@@ -12346,12 +12346,12 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Parekar Sharad Yashavant</t>
+          <t>Parekar Sharad Yashavanta</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Parekar Yashavant</t>
+          <t>Parekar Yashavanta</t>
         </is>
       </c>
     </row>
@@ -12574,12 +12574,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Mejari Gajanan Yashavant</t>
+          <t>Mejari Gajanan Yashavanta</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Mejari Yashavant</t>
+          <t>Mejari Yashavanta</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Bhovad Ekanath Sadashiv</t>
+          <t>Bhovad Ekanatha Sadashiv</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -13097,12 +13097,12 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Bhovad Aruna Ekanath</t>
+          <t>Bhovad Aruna Ekanatha</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Bhovar Ekanath</t>
+          <t>Bhovar Ekanatha</t>
         </is>
       </c>
     </row>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Bhovad Rupali Ekanath</t>
+          <t>Bhovad Rupali Ekanatha</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Was Ekanath</t>
+          <t>Was Ekanatha</t>
         </is>
       </c>
     </row>
@@ -13211,12 +13211,12 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Bhovad Reshma Ekanath</t>
+          <t>Bhovad Reshma Ekanatha</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>Bhovad Ekanath</t>
+          <t>Bhovad Ekanatha</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Vab Sinh Rijabihari</t>
+          <t>Vab Sinha Rijabihari</t>
         </is>
       </c>
     </row>
@@ -13320,12 +13320,12 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Sinh Anjana Ramesh</t>
+          <t>Sinha Anjana Ramesh</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Sinh Ramesh</t>
+          <t>Sinha Ramesh</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Mahapatr Vishvambhar</t>
+          <t>Mahapatra Vishvambhar</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>Mahapatr Vishvambhar</t>
+          <t>Mahapatra Vishvambhar</t>
         </is>
       </c>
     </row>
@@ -13549,12 +13549,12 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Mahapatr Mamata Vishvambhar</t>
+          <t>Mahapatra Mamata Vishvambhar</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>Mahapatr Vishvambhar</t>
+          <t>Mahapatra Vishvambhar</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Paudel Mohanasinh Tekanaray</t>
+          <t>Paudel Mohanasinha Tekanaray</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -14057,12 +14057,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Tambe Shaila Vasant</t>
+          <t>Tambe Shaila Vasanta</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Tambe Vasant</t>
+          <t>Tambe Vasanta</t>
         </is>
       </c>
     </row>
@@ -14114,12 +14114,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Tambe Satish Vasant</t>
+          <t>Tambe Satish Vasanta</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Tambe Vasant</t>
+          <t>Tambe Vasanta</t>
         </is>
       </c>
     </row>
@@ -14228,12 +14228,12 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Tambe Ganesh Vasant</t>
+          <t>Tambe Ganesh Vasanta</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>Tambe Vasant</t>
+          <t>Tambe Vasanta</t>
         </is>
       </c>
     </row>
@@ -14285,12 +14285,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Tambe Ashish Vasant</t>
+          <t>Tambe Ashish Vasanta</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>Tambe Vasant</t>
+          <t>Tambe Vasanta</t>
         </is>
       </c>
     </row>
@@ -14342,12 +14342,12 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Tambe Umesh Vasant</t>
+          <t>Tambe Umesh Vasanta</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Tambe Vasant</t>
+          <t>Tambe Vasanta</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Pavar Kashinath Ratan</t>
+          <t>Pavar Kashinatha Ratan</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Pavar Darshana Kashinath</t>
+          <t>Pavar Darshana Kashinatha</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>Pavar Kashinath</t>
+          <t>Pavar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -15415,12 +15415,12 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Shekh Salama Rasid</t>
+          <t>Shekha Salama Rasid</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>Shekh Rasid</t>
+          <t>Shekha Rasid</t>
         </is>
       </c>
     </row>
@@ -15477,12 +15477,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Shekh Rasid Abdul</t>
+          <t>Shekha Rasid Abdul</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>Shekh Abdul</t>
+          <t>Shekha Abdul</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Vach Shekh Rasid</t>
+          <t>Vach Shekha Rasid</t>
         </is>
       </c>
     </row>
@@ -15576,12 +15576,12 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Shekh Shakola Rasid</t>
+          <t>Shekha Shakola Rasid</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Shekh Rasid</t>
+          <t>Shekha Rasid</t>
         </is>
       </c>
     </row>
@@ -15633,12 +15633,12 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Pavar Chandragupt Ramachandr</t>
+          <t>Pavar Chandragupta Ramachandra</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>Pavar Ramachandr</t>
+          <t>Pavar Ramachandra</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Pavar Smita Chandragupt</t>
+          <t>Pavar Smita Chandragupta</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>Pavar Chandragupt</t>
+          <t>Pavar Chandragupta</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Baban Pavar Chandragupt</t>
+          <t>Baban Pavar Chandragupta</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Vishvas Nishikant Nilod</t>
+          <t>Vishvas Nishikanta Nilod</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Shah Jayashri Hemant Pa Shah Hemant Satri</t>
+          <t>Shah Jayashri Hemanta Pa Shah Hemanta Satri</t>
         </is>
       </c>
     </row>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Vach Shah Hemendr</t>
+          <t>Vach Shah Hemendra</t>
         </is>
       </c>
     </row>
@@ -16211,12 +16211,12 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Shah Dipali Hemendr</t>
+          <t>Shah Dipali Hemendra</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>Shah Hemandr</t>
+          <t>Shah Hemandra</t>
         </is>
       </c>
     </row>
@@ -16273,12 +16273,12 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Savant Shridhar Yashavant</t>
+          <t>Savanta Shridhar Yashavanta</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Savant Yashavant</t>
+          <t>Savanta Yashavanta</t>
         </is>
       </c>
     </row>
@@ -16335,12 +16335,12 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Savant Sangita Shridhar</t>
+          <t>Savanta Sangita Shridhar</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>Savant Shridhar</t>
+          <t>Savanta Shridhar</t>
         </is>
       </c>
     </row>
@@ -16630,12 +16630,12 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Pandit Dipak Raghunath</t>
+          <t>Pandit Dipak Raghunatha</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>Pandit Raghunath</t>
+          <t>Pandit Raghunatha</t>
         </is>
       </c>
     </row>
@@ -17039,12 +17039,12 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Achary Ratnakar</t>
+          <t>Acharya Ratnakar</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Achary Ratnakar</t>
+          <t>Acharya Ratnakar</t>
         </is>
       </c>
     </row>
@@ -17096,12 +17096,12 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Achary Sarasvati Ratnakar</t>
+          <t>Acharya Sarasvati Ratnakar</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Achary Ratmakar</t>
+          <t>Acharya Ratmakar</t>
         </is>
       </c>
     </row>
@@ -17153,12 +17153,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Pille Radhakrushnan Vishvanath</t>
+          <t>Pille Radhakrushnan Vishvanatha</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>Pille Vishvanath</t>
+          <t>Pille Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -17272,12 +17272,12 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Pi. Unnikrushnan Tintu</t>
+          <t>P. Unnikrushnan Tintu</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>Pi. Tintu</t>
+          <t>P. Tintu</t>
         </is>
       </c>
     </row>
@@ -17334,12 +17334,12 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Pi. Umadevi Unnikrushnan</t>
+          <t>P. Umadevi Unnikrushnan</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>Pi. Unnikrushnan</t>
+          <t>P. Unnikrushnan</t>
         </is>
       </c>
     </row>
@@ -17391,12 +17391,12 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Ti. Damodaran Ke.</t>
+          <t>T. Damodaran K.</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>Pi. Ke.</t>
+          <t>P. K.</t>
         </is>
       </c>
     </row>
@@ -17448,12 +17448,12 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Ti. Bina Damodaran</t>
+          <t>T. Bina Damodaran</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Pi. Damodaran</t>
+          <t>P. Damodaran</t>
         </is>
       </c>
     </row>
@@ -17505,12 +17505,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Ti. Pramod Damudaran</t>
+          <t>T. Pramod Damudaran</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Ti. Damudaran</t>
+          <t>T. Damudaran</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Desai Ravindr Mahadev</t>
+          <t>Desai Ravindra Mahadev</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Desai Ravina Ravindr</t>
+          <t>Desai Ravina Ravindra</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>Desai Ravindr</t>
+          <t>Desai Ravindra</t>
         </is>
       </c>
     </row>
@@ -17847,7 +17847,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Pillai Ramakrushnan Esa.</t>
+          <t>Pillai Ramakrushnan S.</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -17909,12 +17909,12 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Pillai Girija Ke.</t>
+          <t>Pillai Girija K.</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>Pillai Ke.</t>
+          <t>Pillai K.</t>
         </is>
       </c>
     </row>
@@ -17966,12 +17966,12 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Pillai Shrikumar Ke.</t>
+          <t>Pillai Shrikumar K.</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>Pillai Ke.</t>
+          <t>Pillai K.</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18028,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Murudakar Shashikant Dhurani</t>
+          <t>Murudakar Shashikanta Dhurani</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Murudakar Smita Shashikant</t>
+          <t>Murudakar Smita Shashikanta</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>Murudakar Shashikant</t>
+          <t>Murudakar Shashikanta</t>
         </is>
       </c>
     </row>
@@ -18147,12 +18147,12 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Suryavanshi Kamalakar Jagannath</t>
+          <t>Suryavanshi Kamalakar Jagannatha</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Suryavanshi Jagannath</t>
+          <t>Suryavanshi Jagannatha</t>
         </is>
       </c>
     </row>
@@ -18204,12 +18204,12 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Suryavanshi Shakuntala Jagannath</t>
+          <t>Suryavanshi Shakuntala Jagannatha</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>Suryavanshi Jagannath</t>
+          <t>Suryavanshi Jagannatha</t>
         </is>
       </c>
     </row>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Suryavanshi Jagannath Sonu</t>
+          <t>Suryavanshi Jagannatha Sonu</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -18556,12 +18556,12 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Joshi Pi. Kashinath</t>
+          <t>Joshi P. Kashinatha</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>Joshi Kashinath</t>
+          <t>Joshi Kashinatha</t>
         </is>
       </c>
     </row>
@@ -18613,12 +18613,12 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Joshi Usha Pi.</t>
+          <t>Joshi Usha P.</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>Epha!14 Pi.</t>
+          <t>Epha!14 P.</t>
         </is>
       </c>
     </row>
@@ -18718,12 +18718,12 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Bangala Ramababu Narasinh</t>
+          <t>Bangala Ramababu Narasinha</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>Bangala Narasinh</t>
+          <t>Bangala Narasinha</t>
         </is>
       </c>
     </row>
@@ -18817,7 +18817,7 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Kudapakar Vishvanath Budhaji</t>
+          <t>Kudapakar Vishvanatha Budhaji</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -18874,12 +18874,12 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Kudapakar Rushali Vishvanath</t>
+          <t>Kudapakar Rushali Vishvanatha</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>Kurapakar Vishvanath</t>
+          <t>Kurapakar Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Dige Anant Kashiram</t>
+          <t>Dige Ananta Kashiram</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -19102,12 +19102,12 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Dige Vedabati Anant</t>
+          <t>Dige Vedabati Ananta</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Fet Anant</t>
+          <t>Fet Ananta</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Ghodase Shashikant Gangaram</t>
+          <t>Ghodase Shashikanta Gangaram</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -19216,12 +19216,12 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Ghorase Smita Shashikant</t>
+          <t>Ghorase Smita Shashikanta</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Ghodase Shashikant</t>
+          <t>Ghodase Shashikanta</t>
         </is>
       </c>
     </row>
@@ -19444,12 +19444,12 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Rav Shaileja Ena.</t>
+          <t>Rav Shaileja N.</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>Rav Ena.</t>
+          <t>Rav N.</t>
         </is>
       </c>
     </row>
@@ -19620,12 +19620,12 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Shekh Mahamad Raphok</t>
+          <t>Shekha Mahamad Raphok</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>Shekh Raphok</t>
+          <t>Shekha Raphok</t>
         </is>
       </c>
     </row>
@@ -19677,12 +19677,12 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Shekh Najama Mahamad</t>
+          <t>Shekha Najama Mahamad</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>Shekh Mahamad</t>
+          <t>Shekha Mahamad</t>
         </is>
       </c>
     </row>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Mahamand Abu Bakkar</t>
+          <t>Mahamanda Abu Bakkar</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Mahamand Sabira Abu</t>
+          <t>Mahamanda Sabira Abu</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Mahamand Ayesh Abu</t>
+          <t>Mahamanda Ayesh Abu</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Mahamand Pharida Abu</t>
+          <t>Mahamanda Pharida Abu</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -20599,12 +20599,12 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Shekh Yusauph Ahamad</t>
+          <t>Shekha Yusaupha Ahamad</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -20656,12 +20656,12 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Shekh Amina Yusiph</t>
+          <t>Shekha Amina Yusipha</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>Shekh Yusiph</t>
+          <t>Shekha Yusipha</t>
         </is>
       </c>
     </row>
@@ -21055,12 +21055,12 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Shekh Abjal Jako</t>
+          <t>Shekha Abjal Jako</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>Shekh Jako</t>
+          <t>Shekha Jako</t>
         </is>
       </c>
     </row>
@@ -21112,12 +21112,12 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Shekh Shahanajh Abjal</t>
+          <t>Shekha Shahanajha Abjal</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>Shekh Abjal</t>
+          <t>Shekha Abjal</t>
         </is>
       </c>
     </row>
@@ -21169,12 +21169,12 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Shekh Ahamad Muhiudadadim</t>
+          <t>Shekha Ahamad Muhiudadadim</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>Shekh Muhiudadadim</t>
+          <t>Shekha Muhiudadadim</t>
         </is>
       </c>
     </row>
@@ -21226,12 +21226,12 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Shekh Raphoya Ahamad</t>
+          <t>Shekha Raphoya Ahamad</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -21284,12 +21284,12 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Shekh Sohel Ahamad</t>
+          <t>Shekha Sohel Ahamad</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Shekh Akhil Ahamad</t>
+          <t>Shekha Akhil Ahamad</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -21398,12 +21398,12 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Shekh Rahil Ahamad</t>
+          <t>Shekha Rahil Ahamad</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -21455,12 +21455,12 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Shekh Sadahiya Ahamad</t>
+          <t>Shekha Sadahiya Ahamad</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -21512,12 +21512,12 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Shekh Sana Sohel</t>
+          <t>Shekha Sana Sohel</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -21569,12 +21569,12 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Sing Harapal Jali</t>
+          <t>Singa Harapal Joli</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>Sing Jali</t>
+          <t>Singa Joli</t>
         </is>
       </c>
     </row>
@@ -21626,12 +21626,12 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Sing Yasamin Jali</t>
+          <t>Singa Yasamin Joli</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>Sing Jali</t>
+          <t>Singa Joli</t>
         </is>
       </c>
     </row>
@@ -21683,12 +21683,12 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Shekh Cha~D Jaiyanudin</t>
+          <t>Shekha Cha~D Jaiyanudin</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>Shekh Jaiyanudin</t>
+          <t>Shekha Jaiyanudin</t>
         </is>
       </c>
     </row>
@@ -21740,12 +21740,12 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Ajij Bi Chand</t>
+          <t>Ajij Bi Chanda</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>Shekh Bi Chand</t>
+          <t>Shekha Bi Chanda</t>
         </is>
       </c>
     </row>
@@ -21797,12 +21797,12 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Shekh Shakola Cha~D</t>
+          <t>Shekha Shakola Cha~D</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>Epha22 Chand</t>
+          <t>Epha22 Chanda</t>
         </is>
       </c>
     </row>
@@ -21854,12 +21854,12 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Shekh Aphoja Cha~D</t>
+          <t>Shekha Aphoja Cha~D</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>Shekh Chand</t>
+          <t>Shekha Chanda</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21916,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>Shekh Masuma Yakub</t>
+          <t>Shekha Masuma Yakub</t>
         </is>
       </c>
     </row>
@@ -21958,7 +21958,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Vab Shekh Badashaha</t>
+          <t>Vab Shekha Badashaha</t>
         </is>
       </c>
     </row>
@@ -22010,12 +22010,12 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Shekh Gulam Badashah</t>
+          <t>Shekha Gulam Badashah</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>Shekh Badashah</t>
+          <t>Shekha Badashah</t>
         </is>
       </c>
     </row>
@@ -22067,12 +22067,12 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Shekh Rahima Mahamad</t>
+          <t>Shekha Rahima Mahamad</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>Shekh Mahamad</t>
+          <t>Shekha Mahamad</t>
         </is>
       </c>
     </row>
@@ -22124,12 +22124,12 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Shekh Matin Mahamad</t>
+          <t>Shekha Matin Mahamad</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>Shekh Mahamad</t>
+          <t>Shekha Mahamad</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Shekh Jamil Mahamad</t>
+          <t>Shekha Jamil Mahamad</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>Shekh Mahamad</t>
+          <t>Shekha Mahamad</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Shekh Pharida Jamil Pa Shekh Jamil Satri</t>
+          <t>Shekha Pharida Jamil Pa Shekha Jamil Satri</t>
         </is>
       </c>
     </row>
@@ -22275,12 +22275,12 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Shekh Paravesh Jamil</t>
+          <t>Shekha Paravesh Jamil</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>Shekh Jamil</t>
+          <t>Shekha Jamil</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22560,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Sayyad Asiph Manasuraali</t>
+          <t>Sayyad Asipha Manasuraali</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -22617,7 +22617,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Sayyad Ariph Manasuraali</t>
+          <t>Sayyad Aripha Manasuraali</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Shekh Mehamumabi Cha~D</t>
+          <t>Shekha Mehamumabi Cha~D</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -22731,12 +22731,12 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Shekh Vahadali Chand</t>
+          <t>Shekha Vahadali Chanda</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>Shekh Cha~D</t>
+          <t>Shekha Cha~D</t>
         </is>
       </c>
     </row>
@@ -22788,12 +22788,12 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Shekh Phatima Vahadali</t>
+          <t>Shekha Phatima Vahadali</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>Shekh Vahadali</t>
+          <t>Shekha Vahadali</t>
         </is>
       </c>
     </row>
@@ -22845,12 +22845,12 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Shekh Khalil Cha~D</t>
+          <t>Shekha Khalil Cha~D</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>Shekh Cha~D</t>
+          <t>Shekha Cha~D</t>
         </is>
       </c>
     </row>
@@ -22902,12 +22902,12 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Shekh Abeda Cha~D</t>
+          <t>Shekha Abeda Cha~D</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>Shekh Cha~D</t>
+          <t>Shekha Cha~D</t>
         </is>
       </c>
     </row>
@@ -23472,12 +23472,12 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Sayyaid Sumayya Pharukh</t>
+          <t>Sayyaid Sumayya Pharukha</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>Samayyaid Pharukh</t>
+          <t>Samayyaid Pharukha</t>
         </is>
       </c>
     </row>
@@ -23529,12 +23529,12 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Sayyaid Hajara Ariph</t>
+          <t>Sayyaid Hajara Aripha</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>Sayyaid Ariph</t>
+          <t>Sayyaid Aripha</t>
         </is>
       </c>
     </row>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Japhari Vakajh Avadil</t>
+          <t>Japhari Vakajha Avadil</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -24100,12 +24100,12 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>Shekh Anij Ahamad</t>
+          <t>Shekha Anij Ahamad</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>Shekh Ahamad</t>
+          <t>Shekha Ahamad</t>
         </is>
       </c>
     </row>
@@ -24157,12 +24157,12 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Saida Bi. Anij</t>
+          <t>Saida B. Anij</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>Shekh Bi. Anij</t>
+          <t>Shekha B. Anij</t>
         </is>
       </c>
     </row>
@@ -24214,12 +24214,12 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Shekh Sohel Anij</t>
+          <t>Shekha Sohel Anij</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>Shekh Anij</t>
+          <t>Shekha Anij</t>
         </is>
       </c>
     </row>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>Saliyan Ara. Chinnama</t>
+          <t>Saliyan R. Chinnama</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>Murudakar Vaibhav Yashavant</t>
+          <t>Murudakar Vaibhav Yashavanta</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>Murudakar Yashavant</t>
+          <t>Murudakar Yashavanta</t>
         </is>
       </c>
     </row>
@@ -26008,12 +26008,12 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Shekh Musa Abdul</t>
+          <t>Shekha Musa Abdul</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>Shekh Abdul</t>
+          <t>Shekha Abdul</t>
         </is>
       </c>
     </row>
@@ -26065,12 +26065,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>Shekh Resama Musa</t>
+          <t>Shekha Resama Musa</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>Shekh Musa</t>
+          <t>Shekha Musa</t>
         </is>
       </c>
     </row>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>Kae Jayant Moreshvar</t>
+          <t>Kae Jayanta Moreshvar</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -26293,12 +26293,12 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>Kae Jayashri Jayant</t>
+          <t>Kae Jayashri Jayanta</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>Kae Jayant</t>
+          <t>Kae Jayanta</t>
         </is>
       </c>
     </row>
@@ -26350,12 +26350,12 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Nayak Sushil Vhi.</t>
+          <t>Nayak Sushil V.</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>Nayak Vhi.</t>
+          <t>Nayak V.</t>
         </is>
       </c>
     </row>
@@ -26579,7 +26579,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>Shelar Chandrakant Dhondu</t>
+          <t>Shelar Chandrakanta Dhondu</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -26636,12 +26636,12 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>Shelar Suchitra Chandrakant</t>
+          <t>Shelar Suchitra Chandrakanta</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>Shelar Chandrakant</t>
+          <t>Shelar Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -27149,12 +27149,12 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>Majalakar Shashikant</t>
+          <t>Majalakar Shashikanta</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>Majalakar Shashikant</t>
+          <t>Majalakar Shashikanta</t>
         </is>
       </c>
     </row>
@@ -27206,12 +27206,12 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Majalakar Shalaka Shashikant</t>
+          <t>Majalakar Shalaka Shashikanta</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>Majalakar Shashikant</t>
+          <t>Majalakar Shashikanta</t>
         </is>
       </c>
     </row>
@@ -27533,7 +27533,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>Jadhav Vasant Ganapat</t>
+          <t>Jadhav Vasanta Ganapat</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -27590,12 +27590,12 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>Jadhav Vaishali Vasant</t>
+          <t>Jadhav Vaishali Vasanta</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>Jadhav Vasant</t>
+          <t>Jadhav Vasanta</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Gala Nalind Amrutalal</t>
+          <t>Gala Nalinda Amrutalal</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -27818,12 +27818,12 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Gala Nisa Nalind</t>
+          <t>Gala Nisa Nalinda</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>Gala Nalind</t>
+          <t>Gala Nalinda</t>
         </is>
       </c>
     </row>
@@ -27989,7 +27989,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Vab Kambae Ramachandr</t>
+          <t>Vab Kambae Ramachandra</t>
         </is>
       </c>
     </row>
@@ -28098,12 +28098,12 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Kambae Vikas Ramachandr</t>
+          <t>Kambae Vikas Ramachandra</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>Kambae Ramachandr</t>
+          <t>Kambae Ramachandra</t>
         </is>
       </c>
     </row>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Shantaram Pavar Ramachandr</t>
+          <t>Shantaram Pavar Ramachandra</t>
         </is>
       </c>
     </row>
@@ -28197,12 +28197,12 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Takasaakar Nandakishor Vhi.</t>
+          <t>Takasaakar Nandakishor V.</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>Takasaakar Vhi.</t>
+          <t>Takasaakar V.</t>
         </is>
       </c>
     </row>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>More Suryakant Moreshch</t>
+          <t>More Suryakanta Moreshcha</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>More Suryakant</t>
+          <t>More Suryakanta</t>
         </is>
       </c>
     </row>
@@ -28995,12 +28995,12 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Shekh Abdul Shakur</t>
+          <t>Shekha Abdul Shakur</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>Shekh Shakur</t>
+          <t>Shekha Shakur</t>
         </is>
       </c>
     </row>
@@ -29053,12 +29053,12 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Shekh Phaijun Nisa</t>
+          <t>Shekha Phaijun Nisa</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>Shekh Nisa</t>
+          <t>Shekha Nisa</t>
         </is>
       </c>
     </row>
@@ -29110,12 +29110,12 @@
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Shekh Juned Abdul</t>
+          <t>Shekha Juned Abdul</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>Shekh Abdul</t>
+          <t>Shekha Abdul</t>
         </is>
       </c>
     </row>
@@ -29167,12 +29167,12 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Shekh Nikhad Hasad</t>
+          <t>Shekha Nikhad Hasad</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>Shekh Hasad</t>
+          <t>Shekha Hasad</t>
         </is>
       </c>
     </row>
@@ -29229,12 +29229,12 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Pavar Rohidas Ramachandr</t>
+          <t>Pavar Rohidas Ramachandra</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>Pavar Ramachandr</t>
+          <t>Pavar Ramachandra</t>
         </is>
       </c>
     </row>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Pavar Bajarang Keshav</t>
+          <t>Pavar Bajaranga Keshav</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -29519,12 +29519,12 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Pavar Ulka Bajarang</t>
+          <t>Pavar Ulka Bajaranga</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>Pavar Bajarang</t>
+          <t>Pavar Bajaranga</t>
         </is>
       </c>
     </row>
@@ -29576,12 +29576,12 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Shekh Najim Abdul</t>
+          <t>Shekha Najim Abdul</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>Shekh Abdul</t>
+          <t>Shekha Abdul</t>
         </is>
       </c>
     </row>
@@ -29633,12 +29633,12 @@
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>Shekh Shahanajh Najim</t>
+          <t>Shekha Shahanajha Najim</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>Shekh Abdul</t>
+          <t>Shekha Abdul</t>
         </is>
       </c>
     </row>
@@ -29690,12 +29690,12 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>Shekh Imaran Najim</t>
+          <t>Shekha Imaran Najim</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>Shekh Najim</t>
+          <t>Shekha Najim</t>
         </is>
       </c>
     </row>
@@ -29747,12 +29747,12 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Sisodiya Ramasvarup Bhavarasinh</t>
+          <t>Sisodiya Ramasvarup Bhavarasinha</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>Sisodiya Bhavarasinh</t>
+          <t>Sisodiya Bhavarasinha</t>
         </is>
       </c>
     </row>
@@ -29940,12 +29940,12 @@
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Rajaram Pandurang</t>
+          <t>Rajaram Panduranga</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>Hegishte Pandurang</t>
+          <t>Hegishte Panduranga</t>
         </is>
       </c>
     </row>
@@ -30339,7 +30339,7 @@
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Dhamapurakar Chandrakant Krushna</t>
+          <t>Dhamapurakar Chandrakanta Krushna</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -30401,12 +30401,12 @@
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>Dhamapurakar Chitra Chandrakant</t>
+          <t>Dhamapurakar Chitra Chandrakanta</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>Dhamapurakar Chandrakant</t>
+          <t>Dhamapurakar Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -30577,12 +30577,12 @@
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Rane Shrikrushn Baakrushn</t>
+          <t>Rane Shrikrushna Baakrushna</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>Rane Baakrushn</t>
+          <t>Rane Baakrushna</t>
         </is>
       </c>
     </row>
@@ -30639,12 +30639,12 @@
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>Rane Shraddha Shrikrushn</t>
+          <t>Rane Shraddha Shrikrushna</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>Rane Shrikrushn</t>
+          <t>Rane Shrikrushna</t>
         </is>
       </c>
     </row>
@@ -30696,12 +30696,12 @@
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>Kulakani Mahadev Raghunath</t>
+          <t>Kulakani Mahadev Raghunatha</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>Kulakarni Raghunath</t>
+          <t>Kulakarni Raghunatha</t>
         </is>
       </c>
     </row>
@@ -30924,7 +30924,7 @@
       </c>
       <c r="K553" t="inlineStr">
         <is>
-          <t>Disoja Pal Mayakal</t>
+          <t>Disoja Pol Mayakal</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
@@ -30981,12 +30981,12 @@
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t>Disoja Mayakal Pal</t>
+          <t>Disoja Mayakal Pol</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>Disoja Pal</t>
+          <t>Disoja Pol</t>
         </is>
       </c>
     </row>
@@ -31038,7 +31038,7 @@
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Disoja Banedik Mayakal</t>
+          <t>Disoja Benedik Mayakal</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
@@ -31095,12 +31095,12 @@
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Disoja Apalis Pal</t>
+          <t>Disoja Apalis Pol</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>Disoja Pal</t>
+          <t>Disoja Pol</t>
         </is>
       </c>
     </row>
@@ -31209,12 +31209,12 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Hemadi Rama Hemant</t>
+          <t>Hemadi Rama Hemanta</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>Hemadi Hemant</t>
+          <t>Hemadi Hemanta</t>
         </is>
       </c>
     </row>
@@ -31608,12 +31608,12 @@
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Das Nipendr Chandr</t>
+          <t>Das Nipendra Chandra</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>Das Chandr</t>
+          <t>Das Chandra</t>
         </is>
       </c>
     </row>
@@ -31666,7 +31666,7 @@
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>Das Sarasvati Nipendr</t>
+          <t>Das Sarasvati Nipendra</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -31723,12 +31723,12 @@
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Das Sanjay Nipendr</t>
+          <t>Das Sanjay Nipendra</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>Das Nipedr</t>
+          <t>Das Nipedra</t>
         </is>
       </c>
     </row>
@@ -31780,12 +31780,12 @@
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Das Svapna Nipedr</t>
+          <t>Das Svapna Nipedra</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>Das Nipedr</t>
+          <t>Das Nipedra</t>
         </is>
       </c>
     </row>
@@ -31837,12 +31837,12 @@
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>Das Suparna Nipendr</t>
+          <t>Das Suparna Nipendra</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>Das Nipedr</t>
+          <t>Das Nipedra</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>Bagarecha Sa</t>
+          <t>Bagarecha Se</t>
         </is>
       </c>
     </row>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="K583" t="inlineStr">
         <is>
-          <t>Bagarecha Liladevi Sa</t>
+          <t>Bagarecha Liladevi Se</t>
         </is>
       </c>
       <c r="L583" t="inlineStr">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>Tambade Hemant Dattaram</t>
+          <t>Tambade Hemanta Dattaram</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -33403,12 +33403,12 @@
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>Tambade Rohini Hemant</t>
+          <t>Tambade Rohini Hemanta</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>Tambade Hemant</t>
+          <t>Tambade Hemanta</t>
         </is>
       </c>
     </row>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>Vadh Anil Gajanan</t>
+          <t>Vadha Anil Gajanan</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>Vadh Gajanan</t>
+          <t>Vadha Gajanan</t>
         </is>
       </c>
     </row>
@@ -33527,12 +33527,12 @@
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>Vagh Sudha Anil</t>
+          <t>Vagha Sudha Anil</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>Vagh Anil</t>
+          <t>Vagha Anil</t>
         </is>
       </c>
     </row>
@@ -33584,12 +33584,12 @@
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>Najhareth Damanik Kasamiro</t>
+          <t>Najharetha Domanik Kesamiro</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>Najhareth Kasamiro</t>
+          <t>Najharetha Kesamiro</t>
         </is>
       </c>
     </row>
@@ -33641,12 +33641,12 @@
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>Najhareth Meririta Damanik</t>
+          <t>Najharetha Meririta Domanik</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>Najhareth Damanik</t>
+          <t>Najharetha Domanik</t>
         </is>
       </c>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>Dhue Shashikant Sahadev</t>
+          <t>Dhue Shashikanta Sahadev</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -33812,7 +33812,7 @@
       </c>
       <c r="K605" t="inlineStr">
         <is>
-          <t>Devasthai Yashavant Dattatray</t>
+          <t>Devasthai Yashavanta Dattatray</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
@@ -33869,7 +33869,7 @@
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>Raut Janavi Ravindr</t>
+          <t>Raut Janavi Ravindra</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -33926,12 +33926,12 @@
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>Dhage Kamalakar Raghunath</t>
+          <t>Dhage Kamalakar Raghunatha</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Dhage Raghunath</t>
+          <t>Dhage Raghunatha</t>
         </is>
       </c>
     </row>
@@ -33983,7 +33983,7 @@
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>Mulla Arshadh Abubakkar</t>
+          <t>Mulla Arshadha Abubakkar</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
@@ -34045,12 +34045,12 @@
       </c>
       <c r="K609" t="inlineStr">
         <is>
-          <t>Mulla Pharida Arshadh</t>
+          <t>Mulla Pharida Arshadha</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>Mulla Arshadh</t>
+          <t>Mulla Arshadha</t>
         </is>
       </c>
     </row>
@@ -34549,7 +34549,7 @@
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>Raman Padmavati Ke.</t>
+          <t>Raman Padmavati K.</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
@@ -34606,12 +34606,12 @@
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>Raman Ramakrushnan Ke.</t>
+          <t>Raman Ramakrushnan K.</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>Raman Ke.</t>
+          <t>Raman K.</t>
         </is>
       </c>
     </row>
@@ -34834,12 +34834,12 @@
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>Devasthai Nitin Yashavant</t>
+          <t>Devasthai Nitin Yashavanta</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>Devasthai Yashavant</t>
+          <t>Devasthai Yashavanta</t>
         </is>
       </c>
     </row>
@@ -34891,12 +34891,12 @@
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>Devasthai Uday Yashavant</t>
+          <t>Devasthai Uday Yashavanta</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>Devasthai Yashavant</t>
+          <t>Devasthai Yashavanta</t>
         </is>
       </c>
     </row>
@@ -35062,12 +35062,12 @@
       </c>
       <c r="K628" t="inlineStr">
         <is>
-          <t>Raut Sunil Taranath</t>
+          <t>Raut Sunil Taranatha</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>Raut Taranath</t>
+          <t>Raut Taranatha</t>
         </is>
       </c>
     </row>
@@ -35176,12 +35176,12 @@
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Raut Kishor Taranath</t>
+          <t>Raut Kishor Taranatha</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>Raut Taranath</t>
+          <t>Raut Taranatha</t>
         </is>
       </c>
     </row>
@@ -35295,12 +35295,12 @@
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>Raut Prashant Taranath</t>
+          <t>Raut Prashanta Taranatha</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>Raut Taranath</t>
+          <t>Raut Taranatha</t>
         </is>
       </c>
     </row>
@@ -35352,12 +35352,12 @@
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>Raut Madhuri Prashant</t>
+          <t>Raut Madhuri Prashanta</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>Raut Prashant</t>
+          <t>Raut Prashanta</t>
         </is>
       </c>
     </row>
@@ -35409,12 +35409,12 @@
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>Raut Hirabai Taranath</t>
+          <t>Raut Hirabai Taranatha</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>Raut Taranath</t>
+          <t>Raut Taranatha</t>
         </is>
       </c>
     </row>
@@ -35466,12 +35466,12 @@
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>Raut Nayan Taranath</t>
+          <t>Raut Nayan Taranatha</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>Raut Taranath</t>
+          <t>Raut Taranatha</t>
         </is>
       </c>
     </row>
@@ -35523,12 +35523,12 @@
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>Raut Vasundhara Ravindr</t>
+          <t>Raut Vasundhara Ravindra</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>Raut Ravindr</t>
+          <t>Raut Ravindra</t>
         </is>
       </c>
     </row>
@@ -35865,12 +35865,12 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Dhage Mohan Raghunath</t>
+          <t>Dhage Mohan Raghunatha</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>Dhage Raghunath</t>
+          <t>Dhage Raghunatha</t>
         </is>
       </c>
     </row>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Khamakar Chandrakant Mahadev</t>
+          <t>Khamakar Chandrakanta Mahadev</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -36165,12 +36165,12 @@
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Khamakar Puja Chandrakant</t>
+          <t>Khamakar Puja Chandrakanta</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>Khamakar Chandrakant</t>
+          <t>Khamakar Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -36284,7 +36284,7 @@
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>Khamakar Rajendr Bapurav</t>
+          <t>Khamakar Rajendra Bapurav</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
@@ -36341,12 +36341,12 @@
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>Dete Sangita Rajendr</t>
+          <t>Dete Sangita Rajendra</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
         <is>
-          <t>Dete Rajendr</t>
+          <t>Dete Rajendra</t>
         </is>
       </c>
     </row>
@@ -36403,7 +36403,7 @@
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>Khamakar Ravindr Mahadev</t>
+          <t>Khamakar Ravindra Mahadev</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -36460,12 +36460,12 @@
       </c>
       <c r="K652" t="inlineStr">
         <is>
-          <t>Khamakar Ruchira Ravidr</t>
+          <t>Khamakar Ruchira Ravidra</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
         <is>
-          <t>Khamakar Ravidr</t>
+          <t>Khamakar Ravidra</t>
         </is>
       </c>
     </row>
@@ -36517,7 +36517,7 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>Khamakar Ramakant Mahadev</t>
+          <t>Khamakar Ramakanta Mahadev</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -36574,12 +36574,12 @@
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>Khamakar Ragini Ramakant</t>
+          <t>Khamakar Ragini Ramakanta</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
         <is>
-          <t>Khamakar Ramakant</t>
+          <t>Khamakar Ramakanta</t>
         </is>
       </c>
     </row>
@@ -36631,12 +36631,12 @@
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>Khamakar Pranoti Ramakant</t>
+          <t>Khamakar Pranoti Ramakanta</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
         <is>
-          <t>Khamakar Ramakant</t>
+          <t>Khamakar Ramakanta</t>
         </is>
       </c>
     </row>
@@ -36688,12 +36688,12 @@
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>Khamakar Pranali Ramakant</t>
+          <t>Khamakar Pranali Ramakanta</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
         <is>
-          <t>Khamakar Ramakant</t>
+          <t>Khamakar Ramakanta</t>
         </is>
       </c>
     </row>
@@ -36745,12 +36745,12 @@
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Khamakar Pranab Ramakant</t>
+          <t>Khamakar Pranab Ramakanta</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
         <is>
-          <t>Khamakar Ramakant</t>
+          <t>Khamakar Ramakanta</t>
         </is>
       </c>
     </row>
@@ -36803,12 +36803,12 @@
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>Gondhai Shashikant</t>
+          <t>Gondhai Shashikanta</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
         <is>
-          <t>Gondhai Shashikant</t>
+          <t>Gondhai Shashikanta</t>
         </is>
       </c>
     </row>
@@ -36860,12 +36860,12 @@
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>Gondhai Shalaka Shashikant</t>
+          <t>Gondhai Shalaka Shashikanta</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
         <is>
-          <t>Gondhai Shashikant</t>
+          <t>Gondhai Shashikanta</t>
         </is>
       </c>
     </row>
@@ -37021,7 +37021,7 @@
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>Khamakar Milind Suresh</t>
+          <t>Khamakar Milinda Suresh</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
@@ -37306,7 +37306,7 @@
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>Mandavakar Harishchandr Viththal</t>
+          <t>Mandavakar Harishchandra Viththal</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
@@ -37363,12 +37363,12 @@
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>Mandavakar Darshana Harishchandr</t>
+          <t>Mandavakar Darshana Harishchandra</t>
         </is>
       </c>
       <c r="L669" t="inlineStr">
         <is>
-          <t>Mandavakar Harishchandr</t>
+          <t>Mandavakar Harishchandra</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>Lad Chandrakant Mahadev</t>
+          <t>Lad Chandrakanta Mahadev</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -37695,12 +37695,12 @@
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>Lad Rekha Chandrakant</t>
+          <t>Lad Rekha Chandrakanta</t>
         </is>
       </c>
       <c r="L675" t="inlineStr">
         <is>
-          <t>Lad Chandrakant</t>
+          <t>Lad Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -37980,12 +37980,12 @@
       </c>
       <c r="K680" t="inlineStr">
         <is>
-          <t>Rajapurakar Dipak Vhi.</t>
+          <t>Rajapurakar Dipak V.</t>
         </is>
       </c>
       <c r="L680" t="inlineStr">
         <is>
-          <t>Rajapurakar Vhi.</t>
+          <t>Rajapurakar V.</t>
         </is>
       </c>
     </row>
@@ -38384,12 +38384,12 @@
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>Shette Ajay Harishchandr</t>
+          <t>Shette Ajay Harishchandra</t>
         </is>
       </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>Kadam Harishchandr</t>
+          <t>Kadam Harishchandra</t>
         </is>
       </c>
     </row>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>Pavar Shailendr Krushna</t>
+          <t>Pavar Shailendra Krushna</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -38560,12 +38560,12 @@
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>Pavar Nita Shailendr</t>
+          <t>Pavar Nita Shailendra</t>
         </is>
       </c>
       <c r="L690" t="inlineStr">
         <is>
-          <t>Pavar Shailendr</t>
+          <t>Pavar Shailendra</t>
         </is>
       </c>
     </row>
@@ -38622,12 +38622,12 @@
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Savant Dattaram Narayan</t>
+          <t>Savanta Dattaram Narayan</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>Savant Narayan</t>
+          <t>Savanta Narayan</t>
         </is>
       </c>
     </row>
@@ -39125,7 +39125,7 @@
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Parab Pandurang Krushna</t>
+          <t>Parab Panduranga Krushna</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -39182,12 +39182,12 @@
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>Parab Pradnya Pandurang</t>
+          <t>Parab Pradnya Panduranga</t>
         </is>
       </c>
       <c r="L701" t="inlineStr">
         <is>
-          <t>Parab Pandurang</t>
+          <t>Parab Panduranga</t>
         </is>
       </c>
     </row>
@@ -39239,12 +39239,12 @@
       </c>
       <c r="K702" t="inlineStr">
         <is>
-          <t>Kode Sitabai Ramachandr</t>
+          <t>Kode Sitabai Ramachandra</t>
         </is>
       </c>
       <c r="L702" t="inlineStr">
         <is>
-          <t>Kode Ramachandr</t>
+          <t>Kode Ramachandra</t>
         </is>
       </c>
     </row>
@@ -39301,12 +39301,12 @@
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>Kode Anant Ramachandr</t>
+          <t>Kode Ananta Ramachandra</t>
         </is>
       </c>
       <c r="L703" t="inlineStr">
         <is>
-          <t>Kode Ramachandr</t>
+          <t>Kode Ramachandra</t>
         </is>
       </c>
     </row>
@@ -39358,12 +39358,12 @@
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>Kode Sharad Ramachandr</t>
+          <t>Kode Sharad Ramachandra</t>
         </is>
       </c>
       <c r="L704" t="inlineStr">
         <is>
-          <t>Kode Ramachandr</t>
+          <t>Kode Ramachandra</t>
         </is>
       </c>
     </row>
@@ -39421,12 +39421,12 @@
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>Kode Amita Anant</t>
+          <t>Kode Amita Ananta</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>Kode Anant</t>
+          <t>Kode Ananta</t>
         </is>
       </c>
     </row>
@@ -39567,12 +39567,12 @@
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>Savant Nitin Anant</t>
+          <t>Savanta Nitin Ananta</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>Savant Anant</t>
+          <t>Savanta Ananta</t>
         </is>
       </c>
     </row>
@@ -39624,12 +39624,12 @@
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>Savant Anant Tukaram</t>
+          <t>Savanta Ananta Tukaram</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>Savant Tukaram</t>
+          <t>Savanta Tukaram</t>
         </is>
       </c>
     </row>
@@ -39681,12 +39681,12 @@
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>Savant Vandana Anant</t>
+          <t>Savanta Vandana Ananta</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>Savant Anant</t>
+          <t>Savanta Ananta</t>
         </is>
       </c>
     </row>
@@ -39738,12 +39738,12 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>Savant Shubhangi Anant</t>
+          <t>Savanta Shubhangi Ananta</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>Savant Anant</t>
+          <t>Savanta Ananta</t>
         </is>
       </c>
     </row>
@@ -40484,12 +40484,12 @@
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>Ambokar Sakhubai Ramachandr</t>
+          <t>Ambokar Sakhubai Ramachandra</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>Ambokar Ramachandr</t>
+          <t>Ambokar Ramachandra</t>
         </is>
       </c>
     </row>
@@ -40546,12 +40546,12 @@
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>Ambokar Daulat Ramachandr</t>
+          <t>Ambokar Daulat Ramachandra</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>Ambokar Ramachandr</t>
+          <t>Ambokar Ramachandra</t>
         </is>
       </c>
     </row>
@@ -40660,7 +40660,7 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>Vab Ambokar Ramachandr</t>
+          <t>Vab Ambokar Ramachandra</t>
         </is>
       </c>
     </row>
@@ -41002,7 +41002,7 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Raut Anant Narayan</t>
+          <t>Raut Ananta Narayan</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -41059,12 +41059,12 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>Raut Indira Anant</t>
+          <t>Raut Indira Ananta</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>Raut Anant</t>
+          <t>Raut Ananta</t>
         </is>
       </c>
     </row>
@@ -41116,12 +41116,12 @@
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Raut Prakash Anant</t>
+          <t>Raut Prakash Ananta</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>Raut Anant</t>
+          <t>Raut Ananta</t>
         </is>
       </c>
     </row>
@@ -41230,12 +41230,12 @@
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>Raut Shekhar Anant</t>
+          <t>Raut Shekhar Ananta</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>Raut Anant</t>
+          <t>Raut Ananta</t>
         </is>
       </c>
     </row>
@@ -41349,12 +41349,12 @@
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>Raut Nitin Anant</t>
+          <t>Raut Nitin Ananta</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
         <is>
-          <t>Raut Anant</t>
+          <t>Raut Ananta</t>
         </is>
       </c>
     </row>
@@ -41468,7 +41468,7 @@
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>Raut Ramachandr Narayan</t>
+          <t>Raut Ramachandra Narayan</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
@@ -41530,12 +41530,12 @@
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>Raut Sitabai Ramachandr</t>
+          <t>Raut Sitabai Ramachandra</t>
         </is>
       </c>
       <c r="L743" t="inlineStr">
         <is>
-          <t>Raut Ramachandr</t>
+          <t>Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -41577,7 +41577,7 @@
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>Vab Raut Ramachandr</t>
+          <t>Vab Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -41634,12 +41634,12 @@
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>Raut Dilip Ramachandr</t>
+          <t>Raut Dilip Ramachandra</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>Raut Ramachandr</t>
+          <t>Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -41857,7 +41857,7 @@
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>Vab Raut Ramachandr</t>
+          <t>Vab Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -42232,7 +42232,7 @@
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>Raut Hemant Narahari</t>
+          <t>Raut Hemanta Narahari</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>Vach Raut Baakrushn</t>
+          <t>Vach Raut Baakrushna</t>
         </is>
       </c>
     </row>
@@ -42502,12 +42502,12 @@
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>Raut Manorama Baakrushn</t>
+          <t>Raut Manorama Baakrushna</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>Raut Baakrushn</t>
+          <t>Raut Baakrushna</t>
         </is>
       </c>
     </row>
@@ -42700,12 +42700,12 @@
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>Raut Dipak Yashavant</t>
+          <t>Raut Dipak Yashavanta</t>
         </is>
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>Raut Yashavant</t>
+          <t>Raut Yashavanta</t>
         </is>
       </c>
     </row>
@@ -42814,12 +42814,12 @@
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>Jambhae Sitabai Ramachandr</t>
+          <t>Jambhae Sitabai Ramachandra</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
         <is>
-          <t>Jambhae Ramachandr</t>
+          <t>Jambhae Ramachandra</t>
         </is>
       </c>
     </row>
@@ -42876,12 +42876,12 @@
       </c>
       <c r="K769" t="inlineStr">
         <is>
-          <t>Jambhae Anil Ramachandr</t>
+          <t>Jambhae Anil Ramachandra</t>
         </is>
       </c>
       <c r="L769" t="inlineStr">
         <is>
-          <t>Jambhae Ramachandr</t>
+          <t>Jambhae Ramachandra</t>
         </is>
       </c>
     </row>
@@ -42995,12 +42995,12 @@
       </c>
       <c r="K771" t="inlineStr">
         <is>
-          <t>Jambhae Sunil Ramachandr</t>
+          <t>Jambhae Sunil Ramachandra</t>
         </is>
       </c>
       <c r="L771" t="inlineStr">
         <is>
-          <t>Jambhae Ramachandr</t>
+          <t>Jambhae Ramachandra</t>
         </is>
       </c>
     </row>
@@ -43228,12 +43228,12 @@
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>Jambhae Subodh Ramachandr</t>
+          <t>Jambhae Subodha Ramachandra</t>
         </is>
       </c>
       <c r="L775" t="inlineStr">
         <is>
-          <t>Jambhae Ramachandr</t>
+          <t>Jambhae Ramachandra</t>
         </is>
       </c>
     </row>
@@ -43290,12 +43290,12 @@
       </c>
       <c r="K776" t="inlineStr">
         <is>
-          <t>Jambhae Suchita Subodh</t>
+          <t>Jambhae Suchita Subodha</t>
         </is>
       </c>
       <c r="L776" t="inlineStr">
         <is>
-          <t>Jambhae Subodh</t>
+          <t>Jambhae Subodha</t>
         </is>
       </c>
     </row>
@@ -43347,12 +43347,12 @@
       </c>
       <c r="K777" t="inlineStr">
         <is>
-          <t>Pande Uma Umaranath</t>
+          <t>Pande Uma Umaranatha</t>
         </is>
       </c>
       <c r="L777" t="inlineStr">
         <is>
-          <t>Pande Umaranath</t>
+          <t>Pande Umaranatha</t>
         </is>
       </c>
     </row>
@@ -43830,7 +43830,7 @@
       </c>
       <c r="K786" t="inlineStr">
         <is>
-          <t>Raut Anant Jayaram</t>
+          <t>Raut Ananta Jayaram</t>
         </is>
       </c>
       <c r="L786" t="inlineStr">
@@ -43887,12 +43887,12 @@
       </c>
       <c r="K787" t="inlineStr">
         <is>
-          <t>Raut Indira Anant</t>
+          <t>Raut Indira Ananta</t>
         </is>
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>Raut Anant</t>
+          <t>Raut Ananta</t>
         </is>
       </c>
     </row>
@@ -43944,12 +43944,12 @@
       </c>
       <c r="K788" t="inlineStr">
         <is>
-          <t>Raut Suresh Anant</t>
+          <t>Raut Suresh Ananta</t>
         </is>
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>Raut Anant</t>
+          <t>Raut Ananta</t>
         </is>
       </c>
     </row>
@@ -44058,12 +44058,12 @@
       </c>
       <c r="K790" t="inlineStr">
         <is>
-          <t>Raut Jayant Narasinh</t>
+          <t>Raut Jayanta Narasinha</t>
         </is>
       </c>
       <c r="L790" t="inlineStr">
         <is>
-          <t>Raut Narasinh</t>
+          <t>Raut Narasinha</t>
         </is>
       </c>
     </row>
@@ -44115,12 +44115,12 @@
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t>Raut Jayashri Jayant</t>
+          <t>Raut Jayashri Jayanta</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>Raut Jayant</t>
+          <t>Raut Jayanta</t>
         </is>
       </c>
     </row>
@@ -44172,12 +44172,12 @@
       </c>
       <c r="K792" t="inlineStr">
         <is>
-          <t>Raut Sachin Narasinh</t>
+          <t>Raut Sachin Narasinha</t>
         </is>
       </c>
       <c r="L792" t="inlineStr">
         <is>
-          <t>Raut Narasinh</t>
+          <t>Raut Narasinha</t>
         </is>
       </c>
     </row>
@@ -44500,7 +44500,7 @@
       </c>
       <c r="K799" t="inlineStr">
         <is>
-          <t>Ghar Kramank Matadarache Purn Nanv Nate Natevaikache Purn Nanv Ling Vay</t>
+          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
         </is>
       </c>
     </row>
@@ -45149,12 +45149,12 @@
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Patanakar Ashok Pandurang</t>
+          <t>Patanakar Ashok Panduranga</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Patanakar Pandurang</t>
+          <t>Patanakar Panduranga</t>
         </is>
       </c>
     </row>
@@ -45377,12 +45377,12 @@
       </c>
       <c r="K815" t="inlineStr">
         <is>
-          <t>Patanakar Dilip Pandurang</t>
+          <t>Patanakar Dilip Panduranga</t>
         </is>
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>Patanakar Pandurang</t>
+          <t>Patanakar Panduranga</t>
         </is>
       </c>
     </row>
@@ -45615,7 +45615,7 @@
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>Patanakar Pandurang</t>
+          <t>Patanakar Panduranga</t>
         </is>
       </c>
     </row>
@@ -45729,7 +45729,7 @@
       </c>
       <c r="K821" t="inlineStr">
         <is>
-          <t>Raut Pandurang Vaman</t>
+          <t>Raut Panduranga Vaman</t>
         </is>
       </c>
       <c r="L821" t="inlineStr">
@@ -45786,12 +45786,12 @@
       </c>
       <c r="K822" t="inlineStr">
         <is>
-          <t>Raut Lakshmi Pandurang</t>
+          <t>Raut Lakshmi Panduranga</t>
         </is>
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>Raut Pandurang</t>
+          <t>Raut Panduranga</t>
         </is>
       </c>
     </row>
@@ -45843,12 +45843,12 @@
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t>Raut Kumar Pandurang</t>
+          <t>Raut Kumar Panduranga</t>
         </is>
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>Raut Pandurang</t>
+          <t>Raut Panduranga</t>
         </is>
       </c>
     </row>
@@ -45900,12 +45900,12 @@
       </c>
       <c r="K824" t="inlineStr">
         <is>
-          <t>Raut Sunita Pandurang</t>
+          <t>Raut Sunita Panduranga</t>
         </is>
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>Raut Pandurang</t>
+          <t>Raut Panduranga</t>
         </is>
       </c>
     </row>
@@ -45957,12 +45957,12 @@
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>Raut Pradip Pandurang</t>
+          <t>Raut Pradip Panduranga</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>Raut Pandurang</t>
+          <t>Raut Panduranga</t>
         </is>
       </c>
     </row>
@@ -46071,12 +46071,12 @@
       </c>
       <c r="K827" t="inlineStr">
         <is>
-          <t>Raut Kiran Pandurang</t>
+          <t>Raut Kiran Panduranga</t>
         </is>
       </c>
       <c r="L827" t="inlineStr">
         <is>
-          <t>Raut Pandurang</t>
+          <t>Raut Panduranga</t>
         </is>
       </c>
     </row>
@@ -46683,7 +46683,7 @@
       </c>
       <c r="K838" t="inlineStr">
         <is>
-          <t>Raut Ramachandr Daji</t>
+          <t>Raut Ramachandra Daji</t>
         </is>
       </c>
       <c r="L838" t="inlineStr">
@@ -46740,12 +46740,12 @@
       </c>
       <c r="K839" t="inlineStr">
         <is>
-          <t>Raut Nila Ramachandr</t>
+          <t>Raut Nila Ramachandra</t>
         </is>
       </c>
       <c r="L839" t="inlineStr">
         <is>
-          <t>Raut Ramachandr</t>
+          <t>Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -46787,7 +46787,7 @@
       </c>
       <c r="K840" t="inlineStr">
         <is>
-          <t>Vach Raut Ramachandr</t>
+          <t>Vach Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -46829,7 +46829,7 @@
       </c>
       <c r="K841" t="inlineStr">
         <is>
-          <t>Vach Raut Ramachandr</t>
+          <t>Vach Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -46881,12 +46881,12 @@
       </c>
       <c r="K842" t="inlineStr">
         <is>
-          <t>Raut Chandrakant Daji</t>
+          <t>Raut Chandrakanta Daji</t>
         </is>
       </c>
       <c r="L842" t="inlineStr">
         <is>
-          <t>Raut Ramachandr</t>
+          <t>Raut Ramachandra</t>
         </is>
       </c>
     </row>
@@ -46938,12 +46938,12 @@
       </c>
       <c r="K843" t="inlineStr">
         <is>
-          <t>Raut Chaya Chandrakant</t>
+          <t>Raut Chaya Chandrakanta</t>
         </is>
       </c>
       <c r="L843" t="inlineStr">
         <is>
-          <t>Raut Chandrakant</t>
+          <t>Raut Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="K848" t="inlineStr">
         <is>
-          <t>Ghar Kramank Matadarache Purn Nanv Nate Natevaikache Purn Nanv Ling Vay</t>
+          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
         </is>
       </c>
     </row>
@@ -47204,7 +47204,7 @@
       </c>
       <c r="K849" t="inlineStr">
         <is>
-          <t>Raut Prashant Damodar</t>
+          <t>Raut Prashanta Damodar</t>
         </is>
       </c>
       <c r="L849" t="inlineStr">
@@ -47816,12 +47816,12 @@
       </c>
       <c r="K860" t="inlineStr">
         <is>
-          <t>Megholi Rajani Ramachandr</t>
+          <t>Megholi Rajani Ramachandra</t>
         </is>
       </c>
       <c r="L860" t="inlineStr">
         <is>
-          <t>Megholi Ramachandr</t>
+          <t>Megholi Ramachandra</t>
         </is>
       </c>
     </row>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="K861" t="inlineStr">
         <is>
-          <t>Megholi Nandakumar Ramachandr</t>
+          <t>Megholi Nandakumar Ramachandra</t>
         </is>
       </c>
       <c r="L861" t="inlineStr">
         <is>
-          <t>Megholi Ramachandr</t>
+          <t>Megholi Ramachandra</t>
         </is>
       </c>
     </row>
@@ -47987,12 +47987,12 @@
       </c>
       <c r="K863" t="inlineStr">
         <is>
-          <t>Megholi Usha Ramachandr</t>
+          <t>Megholi Usha Ramachandra</t>
         </is>
       </c>
       <c r="L863" t="inlineStr">
         <is>
-          <t>Megholi Ramachandr</t>
+          <t>Megholi Ramachandra</t>
         </is>
       </c>
     </row>
@@ -48215,12 +48215,12 @@
       </c>
       <c r="K867" t="inlineStr">
         <is>
-          <t>Megholi Changu Shailendr</t>
+          <t>Megholi Changu Shailendra</t>
         </is>
       </c>
       <c r="L867" t="inlineStr">
         <is>
-          <t>Megholi Shailendr</t>
+          <t>Megholi Shailendra</t>
         </is>
       </c>
     </row>
@@ -48329,7 +48329,7 @@
       </c>
       <c r="K869" t="inlineStr">
         <is>
-          <t>Bhatagavakar Pandurang Krushna</t>
+          <t>Bhatagavakar Panduranga Krushna</t>
         </is>
       </c>
       <c r="L869" t="inlineStr">
@@ -48386,12 +48386,12 @@
       </c>
       <c r="K870" t="inlineStr">
         <is>
-          <t>Bhatagavakar Mandakini Pandurang</t>
+          <t>Bhatagavakar Mandakini Panduranga</t>
         </is>
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>Bhatagavakar Pandurang</t>
+          <t>Bhatagavakar Panduranga</t>
         </is>
       </c>
     </row>
@@ -49164,7 +49164,7 @@
       </c>
       <c r="K884" t="inlineStr">
         <is>
-          <t>Pavar Makarand Baa</t>
+          <t>Pavar Makaranda Baa</t>
         </is>
       </c>
       <c r="L884" t="inlineStr">
@@ -49221,12 +49221,12 @@
       </c>
       <c r="K885" t="inlineStr">
         <is>
-          <t>Raut Bhagavan Kashinath</t>
+          <t>Raut Bhagavan Kashinatha</t>
         </is>
       </c>
       <c r="L885" t="inlineStr">
         <is>
-          <t>Raut Kashinath</t>
+          <t>Raut Kashinatha</t>
         </is>
       </c>
     </row>
@@ -49834,7 +49834,7 @@
       </c>
       <c r="K897" t="inlineStr">
         <is>
-          <t>Ghar Kramank Matadarache Purn Nanv Nate Natevaikache Purn Nanv Ling Vay</t>
+          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
         </is>
       </c>
     </row>
@@ -49970,12 +49970,12 @@
       </c>
       <c r="K900" t="inlineStr">
         <is>
-          <t>Raut Vishvanath Pandurang</t>
+          <t>Raut Vishvanatha Panduranga</t>
         </is>
       </c>
       <c r="L900" t="inlineStr">
         <is>
-          <t>Raut Pandurang</t>
+          <t>Raut Panduranga</t>
         </is>
       </c>
     </row>
@@ -50027,12 +50027,12 @@
       </c>
       <c r="K901" t="inlineStr">
         <is>
-          <t>Raut Sanjivini Vishvanath</t>
+          <t>Raut Sanjivini Vishvanatha</t>
         </is>
       </c>
       <c r="L901" t="inlineStr">
         <is>
-          <t>Raut Vishvanath</t>
+          <t>Raut Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -50084,12 +50084,12 @@
       </c>
       <c r="K902" t="inlineStr">
         <is>
-          <t>Raut Kalpesh Vishvanath</t>
+          <t>Raut Kalpesh Vishvanatha</t>
         </is>
       </c>
       <c r="L902" t="inlineStr">
         <is>
-          <t>Raut Vishvanath</t>
+          <t>Raut Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -50141,12 +50141,12 @@
       </c>
       <c r="K903" t="inlineStr">
         <is>
-          <t>Raut Vilas Pandurang</t>
+          <t>Raut Vilas Panduranga</t>
         </is>
       </c>
       <c r="L903" t="inlineStr">
         <is>
-          <t>Raut Pandurang</t>
+          <t>Raut Panduranga</t>
         </is>
       </c>
     </row>
@@ -50255,7 +50255,7 @@
       </c>
       <c r="K905" t="inlineStr">
         <is>
-          <t>Pharnandis Benat Bi</t>
+          <t>Pharnandis Benot Bi</t>
         </is>
       </c>
       <c r="L905" t="inlineStr">
@@ -50312,12 +50312,12 @@
       </c>
       <c r="K906" t="inlineStr">
         <is>
-          <t>Pharnandis Phrena Benat</t>
+          <t>Pharnandis Phrena Benot</t>
         </is>
       </c>
       <c r="L906" t="inlineStr">
         <is>
-          <t>Phanandis Benat</t>
+          <t>Phanandis Benot</t>
         </is>
       </c>
     </row>
@@ -50768,7 +50768,7 @@
       </c>
       <c r="K914" t="inlineStr">
         <is>
-          <t>Rana Hemant Champakalal</t>
+          <t>Rana Hemanta Champakalal</t>
         </is>
       </c>
       <c r="L914" t="inlineStr">
@@ -50825,12 +50825,12 @@
       </c>
       <c r="K915" t="inlineStr">
         <is>
-          <t>Rana Darshana Hemant</t>
+          <t>Rana Darshana Hemanta</t>
         </is>
       </c>
       <c r="L915" t="inlineStr">
         <is>
-          <t>Rana Hemant</t>
+          <t>Rana Hemanta</t>
         </is>
       </c>
     </row>
@@ -51323,12 +51323,12 @@
       </c>
       <c r="K924" t="inlineStr">
         <is>
-          <t>Bhosale Prakash Vasant</t>
+          <t>Bhosale Prakash Vasanta</t>
         </is>
       </c>
       <c r="L924" t="inlineStr">
         <is>
-          <t>Bhosale Vasant</t>
+          <t>Bhosale Vasanta</t>
         </is>
       </c>
     </row>
@@ -52376,7 +52376,7 @@
       </c>
       <c r="K943" t="inlineStr">
         <is>
-          <t>Nayar Prashant Shankar</t>
+          <t>Nayar Prashanta Shankar</t>
         </is>
       </c>
       <c r="L943" t="inlineStr">
@@ -52476,7 +52476,7 @@
       </c>
       <c r="K946" t="inlineStr">
         <is>
-          <t>Ghar Kramank Matadarache Purn Nanv Nate Natevaikache Purn Nanv Ling Vay</t>
+          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
         </is>
       </c>
     </row>
@@ -52642,12 +52642,12 @@
       </c>
       <c r="K949" t="inlineStr">
         <is>
-          <t>Tare Shakuntala Baakrushn</t>
+          <t>Tare Shakuntala Baakrushna</t>
         </is>
       </c>
       <c r="L949" t="inlineStr">
         <is>
-          <t>Tare Baakrushn</t>
+          <t>Tare Baakrushna</t>
         </is>
       </c>
     </row>
@@ -52699,12 +52699,12 @@
       </c>
       <c r="K950" t="inlineStr">
         <is>
-          <t>Tare Santosh Baakrushn</t>
+          <t>Tare Santosh Baakrushna</t>
         </is>
       </c>
       <c r="L950" t="inlineStr">
         <is>
-          <t>Tare Baakrushn</t>
+          <t>Tare Baakrushna</t>
         </is>
       </c>
     </row>
@@ -52756,12 +52756,12 @@
       </c>
       <c r="K951" t="inlineStr">
         <is>
-          <t>Tare Mangesh Baakrushn</t>
+          <t>Tare Mangesh Baakrushna</t>
         </is>
       </c>
       <c r="L951" t="inlineStr">
         <is>
-          <t>Tare Baakrushn</t>
+          <t>Tare Baakrushna</t>
         </is>
       </c>
     </row>
@@ -52813,7 +52813,7 @@
       </c>
       <c r="K952" t="inlineStr">
         <is>
-          <t>Kulakani Ranganath Ramarav</t>
+          <t>Kulakani Ranganatha Ramarav</t>
         </is>
       </c>
       <c r="L952" t="inlineStr">
@@ -52870,12 +52870,12 @@
       </c>
       <c r="K953" t="inlineStr">
         <is>
-          <t>Kulakani Radha Ranganath</t>
+          <t>Kulakani Radha Ranganatha</t>
         </is>
       </c>
       <c r="L953" t="inlineStr">
         <is>
-          <t>Kulakani Ranganath</t>
+          <t>Kulakani Ranganatha</t>
         </is>
       </c>
     </row>
@@ -53098,12 +53098,12 @@
       </c>
       <c r="K957" t="inlineStr">
         <is>
-          <t>Kolavanakar Rajesh Ravindr</t>
+          <t>Kolavanakar Rajesh Ravindra</t>
         </is>
       </c>
       <c r="L957" t="inlineStr">
         <is>
-          <t>Kolavanakar Ravindr</t>
+          <t>Kolavanakar Ravindra</t>
         </is>
       </c>
     </row>
@@ -53425,7 +53425,7 @@
       </c>
       <c r="K963" t="inlineStr">
         <is>
-          <t>Kini Anant Narayan</t>
+          <t>Kini Ananta Narayan</t>
         </is>
       </c>
       <c r="L963" t="inlineStr">
@@ -53482,12 +53482,12 @@
       </c>
       <c r="K964" t="inlineStr">
         <is>
-          <t>Kini Manaku Anant</t>
+          <t>Kini Manaku Ananta</t>
         </is>
       </c>
       <c r="L964" t="inlineStr">
         <is>
-          <t>Kini Anant</t>
+          <t>Kini Ananta</t>
         </is>
       </c>
     </row>
@@ -53539,12 +53539,12 @@
       </c>
       <c r="K965" t="inlineStr">
         <is>
-          <t>Kini Ajit Anant</t>
+          <t>Kini Ajit Ananta</t>
         </is>
       </c>
       <c r="L965" t="inlineStr">
         <is>
-          <t>Kini Anant</t>
+          <t>Kini Ananta</t>
         </is>
       </c>
     </row>
@@ -53995,7 +53995,7 @@
       </c>
       <c r="K973" t="inlineStr">
         <is>
-          <t>Kini Pandurang Narayan</t>
+          <t>Kini Panduranga Narayan</t>
         </is>
       </c>
       <c r="L973" t="inlineStr">
@@ -54052,12 +54052,12 @@
       </c>
       <c r="K974" t="inlineStr">
         <is>
-          <t>Kini Manda Pandurang</t>
+          <t>Kini Manda Panduranga</t>
         </is>
       </c>
       <c r="L974" t="inlineStr">
         <is>
-          <t>Kini Pandurang</t>
+          <t>Kini Panduranga</t>
         </is>
       </c>
     </row>
@@ -54109,12 +54109,12 @@
       </c>
       <c r="K975" t="inlineStr">
         <is>
-          <t>Kini Naredr Panduran</t>
+          <t>Kini Naredra Panduran</t>
         </is>
       </c>
       <c r="L975" t="inlineStr">
         <is>
-          <t>Kini Pandurang</t>
+          <t>Kini Panduranga</t>
         </is>
       </c>
     </row>
@@ -54166,12 +54166,12 @@
       </c>
       <c r="K976" t="inlineStr">
         <is>
-          <t>Kini Chaya Narendr</t>
+          <t>Kini Chaya Narendra</t>
         </is>
       </c>
       <c r="L976" t="inlineStr">
         <is>
-          <t>Kini Narendr</t>
+          <t>Kini Narendra</t>
         </is>
       </c>
     </row>
@@ -54223,12 +54223,12 @@
       </c>
       <c r="K977" t="inlineStr">
         <is>
-          <t>Kini Rakesh Pandurang</t>
+          <t>Kini Rakesh Panduranga</t>
         </is>
       </c>
       <c r="L977" t="inlineStr">
         <is>
-          <t>Kini Pandurang</t>
+          <t>Kini Panduranga</t>
         </is>
       </c>
     </row>
@@ -55063,7 +55063,7 @@
       </c>
       <c r="K992" t="inlineStr">
         <is>
-          <t>Shirasagar Naredr Viththal</t>
+          <t>Shirasagar Naredra Viththal</t>
         </is>
       </c>
       <c r="L992" t="inlineStr">
@@ -55121,7 +55121,7 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>Shirasagar Nishikant Viththal</t>
+          <t>Shirasagar Nishikanta Viththal</t>
         </is>
       </c>
       <c r="L994" t="inlineStr">
@@ -55178,12 +55178,12 @@
       </c>
       <c r="K995" t="inlineStr">
         <is>
-          <t>Shirasagar Sujata Nishikant</t>
+          <t>Shirasagar Sujata Nishikanta</t>
         </is>
       </c>
       <c r="L995" t="inlineStr">
         <is>
-          <t>Shirasagar Nishikant</t>
+          <t>Shirasagar Nishikanta</t>
         </is>
       </c>
     </row>
@@ -55235,12 +55235,12 @@
       </c>
       <c r="K996" t="inlineStr">
         <is>
-          <t>Shirasagar Yogita Nishikant</t>
+          <t>Shirasagar Yogita Nishikanta</t>
         </is>
       </c>
       <c r="L996" t="inlineStr">
         <is>
-          <t>Shirasagar Nishikant</t>
+          <t>Shirasagar Nishikanta</t>
         </is>
       </c>
     </row>
@@ -55463,7 +55463,7 @@
       </c>
       <c r="K1000" t="inlineStr">
         <is>
-          <t>Raut Niakanth Ramesh</t>
+          <t>Raut Niakantha Ramesh</t>
         </is>
       </c>
       <c r="L1000" t="inlineStr">
@@ -55733,7 +55733,7 @@
       </c>
       <c r="K1005" t="inlineStr">
         <is>
-          <t>Raut Chandrakant Narayan</t>
+          <t>Raut Chandrakanta Narayan</t>
         </is>
       </c>
       <c r="L1005" t="inlineStr">
@@ -55847,12 +55847,12 @@
       </c>
       <c r="K1007" t="inlineStr">
         <is>
-          <t>Raut Naredr Jagannath</t>
+          <t>Raut Naredra Jagannatha</t>
         </is>
       </c>
       <c r="L1007" t="inlineStr">
         <is>
-          <t>Raut Jagannath</t>
+          <t>Raut Jagannatha</t>
         </is>
       </c>
     </row>
@@ -55904,12 +55904,12 @@
       </c>
       <c r="K1008" t="inlineStr">
         <is>
-          <t>Raut Asha Narendr</t>
+          <t>Raut Asha Narendra</t>
         </is>
       </c>
       <c r="L1008" t="inlineStr">
         <is>
-          <t>Raut Narendr</t>
+          <t>Raut Narendra</t>
         </is>
       </c>
     </row>
@@ -55961,7 +55961,7 @@
       </c>
       <c r="K1009" t="inlineStr">
         <is>
-          <t>Thombare Dasharath Arjun</t>
+          <t>Thombare Dasharatha Arjun</t>
         </is>
       </c>
       <c r="L1009" t="inlineStr">
@@ -56018,12 +56018,12 @@
       </c>
       <c r="K1010" t="inlineStr">
         <is>
-          <t>Thombare Sudha Dasharath</t>
+          <t>Thombare Sudha Dasharatha</t>
         </is>
       </c>
       <c r="L1010" t="inlineStr">
         <is>
-          <t>Thombare Dasharath</t>
+          <t>Thombare Dasharatha</t>
         </is>
       </c>
     </row>
@@ -56075,12 +56075,12 @@
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t>Thombare Jitendr Dasharath</t>
+          <t>Thombare Jitendra Dasharatha</t>
         </is>
       </c>
       <c r="L1011" t="inlineStr">
         <is>
-          <t>Thombare Dasharath</t>
+          <t>Thombare Dasharatha</t>
         </is>
       </c>
     </row>
@@ -56132,12 +56132,12 @@
       </c>
       <c r="K1012" t="inlineStr">
         <is>
-          <t>Thombare Arpana Dasharath</t>
+          <t>Thombare Arpana Dasharatha</t>
         </is>
       </c>
       <c r="L1012" t="inlineStr">
         <is>
-          <t>Thombare Dasharath</t>
+          <t>Thombare Dasharatha</t>
         </is>
       </c>
     </row>
@@ -56303,7 +56303,7 @@
       </c>
       <c r="K1015" t="inlineStr">
         <is>
-          <t>Dolatode Hemant Aba</t>
+          <t>Dolatode Hemanta Aba</t>
         </is>
       </c>
       <c r="L1015" t="inlineStr">
@@ -56588,7 +56588,7 @@
       </c>
       <c r="K1020" t="inlineStr">
         <is>
-          <t>Mane Rajendr Mahadu</t>
+          <t>Mane Rajendra Mahadu</t>
         </is>
       </c>
       <c r="L1020" t="inlineStr">
@@ -56645,12 +56645,12 @@
       </c>
       <c r="K1021" t="inlineStr">
         <is>
-          <t>Mane Asha Rajendr</t>
+          <t>Mane Asha Rajendra</t>
         </is>
       </c>
       <c r="L1021" t="inlineStr">
         <is>
-          <t>Mane Rajendr</t>
+          <t>Mane Rajendra</t>
         </is>
       </c>
     </row>
@@ -56702,7 +56702,7 @@
       </c>
       <c r="K1022" t="inlineStr">
         <is>
-          <t>Mane Narendr Mahadu</t>
+          <t>Mane Narendra Mahadu</t>
         </is>
       </c>
       <c r="L1022" t="inlineStr">
@@ -56759,12 +56759,12 @@
       </c>
       <c r="K1023" t="inlineStr">
         <is>
-          <t>Mane Premila Narendr</t>
+          <t>Mane Premila Narendra</t>
         </is>
       </c>
       <c r="L1023" t="inlineStr">
         <is>
-          <t>Mane Narendr</t>
+          <t>Mane Narendra</t>
         </is>
       </c>
     </row>
@@ -57160,7 +57160,7 @@
       </c>
       <c r="K1031" t="inlineStr">
         <is>
-          <t>Jindal Udhamasing Karatar</t>
+          <t>Jindal Udhamasinga Karatar</t>
         </is>
       </c>
       <c r="L1031" t="inlineStr">
@@ -57207,7 +57207,7 @@
       </c>
       <c r="K1032" t="inlineStr">
         <is>
-          <t>Jindal Manjil Udhamasing Pa Jindal Udhamasing Satri</t>
+          <t>Jindal Manjil Udhamasinga Pa Jindal Udhamasinga Satri</t>
         </is>
       </c>
     </row>
@@ -57259,12 +57259,12 @@
       </c>
       <c r="K1033" t="inlineStr">
         <is>
-          <t>Jindal Sandip Udhamasing</t>
+          <t>Jindal Sandip Udhamasinga</t>
         </is>
       </c>
       <c r="L1033" t="inlineStr">
         <is>
-          <t>Jindal Udhamasing</t>
+          <t>Jindal Udhamasinga</t>
         </is>
       </c>
     </row>
@@ -57316,12 +57316,12 @@
       </c>
       <c r="K1034" t="inlineStr">
         <is>
-          <t>Jindal Sanjiv Udhamasaung</t>
+          <t>Jindal Sanjiv Udhamasaunga</t>
         </is>
       </c>
       <c r="L1034" t="inlineStr">
         <is>
-          <t>Jindal Udhamasing</t>
+          <t>Jindal Udhamasinga</t>
         </is>
       </c>
     </row>
@@ -58253,7 +58253,7 @@
       </c>
       <c r="K1053" t="inlineStr">
         <is>
-          <t>Ravat Gyanasing Sundarasi</t>
+          <t>Ravat Gyanasinga Sundarasi</t>
         </is>
       </c>
       <c r="L1053" t="inlineStr">
@@ -58310,12 +58310,12 @@
       </c>
       <c r="K1054" t="inlineStr">
         <is>
-          <t>Ravat Radha Gyanasing</t>
+          <t>Ravat Radha Gyanasinga</t>
         </is>
       </c>
       <c r="L1054" t="inlineStr">
         <is>
-          <t>Ravat Gyanasing</t>
+          <t>Ravat Gyanasinga</t>
         </is>
       </c>
     </row>
@@ -58850,7 +58850,7 @@
       </c>
       <c r="K1064" t="inlineStr">
         <is>
-          <t>Pamakort</t>
+          <t>Pamakorta</t>
         </is>
       </c>
       <c r="L1064" t="inlineStr">
@@ -59509,7 +59509,7 @@
       </c>
       <c r="K1076" t="inlineStr">
         <is>
-          <t>Pamakort</t>
+          <t>Pamakorta</t>
         </is>
       </c>
       <c r="L1076" t="inlineStr">
@@ -59851,12 +59851,12 @@
       </c>
       <c r="K1082" t="inlineStr">
         <is>
-          <t>Pamakortasi Ravat Viredrasing</t>
+          <t>Pamakortasi Ravat Viredrasinga</t>
         </is>
       </c>
       <c r="L1082" t="inlineStr">
         <is>
-          <t>Ravat Virendrasing</t>
+          <t>Ravat Virendrasinga</t>
         </is>
       </c>
     </row>
@@ -59908,12 +59908,12 @@
       </c>
       <c r="K1083" t="inlineStr">
         <is>
-          <t>Ravat Gita Virendrasing</t>
+          <t>Ravat Gita Virendrasinga</t>
         </is>
       </c>
       <c r="L1083" t="inlineStr">
         <is>
-          <t>Ravat Virendrasong</t>
+          <t>Ravat Virendrasonga</t>
         </is>
       </c>
     </row>
@@ -60278,12 +60278,12 @@
       </c>
       <c r="K1091" t="inlineStr">
         <is>
-          <t>Bandekar Ramakrushn Niakanth</t>
+          <t>Bandekar Ramakrushna Niakantha</t>
         </is>
       </c>
       <c r="L1091" t="inlineStr">
         <is>
-          <t>Bandekar Niakanth</t>
+          <t>Bandekar Niakantha</t>
         </is>
       </c>
     </row>
@@ -60335,12 +60335,12 @@
       </c>
       <c r="K1092" t="inlineStr">
         <is>
-          <t>Bandekar Shailesh Ramakrushn</t>
+          <t>Bandekar Shailesh Ramakrushna</t>
         </is>
       </c>
       <c r="L1092" t="inlineStr">
         <is>
-          <t>Bandekar Ramakrushn</t>
+          <t>Bandekar Ramakrushna</t>
         </is>
       </c>
     </row>
@@ -60449,12 +60449,12 @@
       </c>
       <c r="K1094" t="inlineStr">
         <is>
-          <t>Bandekar Nilesh Ramakrushn</t>
+          <t>Bandekar Nilesh Ramakrushna</t>
         </is>
       </c>
       <c r="L1094" t="inlineStr">
         <is>
-          <t>Bandekar Ramakrushn</t>
+          <t>Bandekar Ramakrushna</t>
         </is>
       </c>
     </row>
@@ -60506,12 +60506,12 @@
       </c>
       <c r="K1095" t="inlineStr">
         <is>
-          <t>Bandekar Yogesh Ramakrushn</t>
+          <t>Bandekar Yogesh Ramakrushna</t>
         </is>
       </c>
       <c r="L1095" t="inlineStr">
         <is>
-          <t>Bandekar Ramakrushn</t>
+          <t>Bandekar Ramakrushna</t>
         </is>
       </c>
     </row>
@@ -60667,7 +60667,7 @@
       </c>
       <c r="K1098" t="inlineStr">
         <is>
-          <t>Vab Shekh Nasir</t>
+          <t>Vab Shekha Nasir</t>
         </is>
       </c>
     </row>
@@ -60719,12 +60719,12 @@
       </c>
       <c r="K1099" t="inlineStr">
         <is>
-          <t>Shekh Rijhavana Javed</t>
+          <t>Shekha Rijhavana Javed</t>
         </is>
       </c>
       <c r="L1099" t="inlineStr">
         <is>
-          <t>Shekh Javed</t>
+          <t>Shekha Javed</t>
         </is>
       </c>
     </row>
@@ -60776,12 +60776,12 @@
       </c>
       <c r="K1100" t="inlineStr">
         <is>
-          <t>Shekh Anjum Nasir</t>
+          <t>Shekha Anjum Nasir</t>
         </is>
       </c>
       <c r="L1100" t="inlineStr">
         <is>
-          <t>Shekh Nasir</t>
+          <t>Shekha Nasir</t>
         </is>
       </c>
     </row>
@@ -60833,12 +60833,12 @@
       </c>
       <c r="K1101" t="inlineStr">
         <is>
-          <t>Kasarale Gajanan Vishvanath</t>
+          <t>Kasarale Gajanan Vishvanatha</t>
         </is>
       </c>
       <c r="L1101" t="inlineStr">
         <is>
-          <t>Kasarale Vishvanath</t>
+          <t>Kasarale Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -60890,12 +60890,12 @@
       </c>
       <c r="K1102" t="inlineStr">
         <is>
-          <t>Kasarale Lilavati Vishvanath</t>
+          <t>Kasarale Lilavati Vishvanatha</t>
         </is>
       </c>
       <c r="L1102" t="inlineStr">
         <is>
-          <t>Kasarale Vishvanath</t>
+          <t>Kasarale Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -61165,7 +61165,7 @@
       </c>
       <c r="K1107" t="inlineStr">
         <is>
-          <t>Vach Bharadvaj Raghunath</t>
+          <t>Vach Bharadvaj Raghunatha</t>
         </is>
       </c>
     </row>
@@ -61274,12 +61274,12 @@
       </c>
       <c r="K1109" t="inlineStr">
         <is>
-          <t>Shekh Mohammad Yasin</t>
+          <t>Shekha Mohammad Yasin</t>
         </is>
       </c>
       <c r="L1109" t="inlineStr">
         <is>
-          <t>Shekh Yasin</t>
+          <t>Shekha Yasin</t>
         </is>
       </c>
     </row>
@@ -61331,12 +61331,12 @@
       </c>
       <c r="K1110" t="inlineStr">
         <is>
-          <t>Shekh Rajiyakhatun Mohamm</t>
+          <t>Shekha Rajiyakhatun Mohamma</t>
         </is>
       </c>
       <c r="L1110" t="inlineStr">
         <is>
-          <t>Shekh Mohammad</t>
+          <t>Shekha Mohammad</t>
         </is>
       </c>
     </row>
@@ -61388,12 +61388,12 @@
       </c>
       <c r="K1111" t="inlineStr">
         <is>
-          <t>Shekh Yusuph Mohammad</t>
+          <t>Shekha Yusupha Mohammad</t>
         </is>
       </c>
       <c r="L1111" t="inlineStr">
         <is>
-          <t>Shekh Mohammad</t>
+          <t>Shekha Mohammad</t>
         </is>
       </c>
     </row>
@@ -61445,12 +61445,12 @@
       </c>
       <c r="K1112" t="inlineStr">
         <is>
-          <t>Shekh Abida Yusuph</t>
+          <t>Shekha Abida Yusupha</t>
         </is>
       </c>
       <c r="L1112" t="inlineStr">
         <is>
-          <t>Shekh Yusuph</t>
+          <t>Shekha Yusupha</t>
         </is>
       </c>
     </row>
@@ -61502,12 +61502,12 @@
       </c>
       <c r="K1113" t="inlineStr">
         <is>
-          <t>Shekh Yunus Mohammad</t>
+          <t>Shekha Yunus Mohammad</t>
         </is>
       </c>
       <c r="L1113" t="inlineStr">
         <is>
-          <t>Shekh Mohammad</t>
+          <t>Shekha Mohammad</t>
         </is>
       </c>
     </row>
@@ -61559,12 +61559,12 @@
       </c>
       <c r="K1114" t="inlineStr">
         <is>
-          <t>Shekh Salim Mohammad</t>
+          <t>Shekha Salim Mohammad</t>
         </is>
       </c>
       <c r="L1114" t="inlineStr">
         <is>
-          <t>Shekh Mohammad</t>
+          <t>Shekha Mohammad</t>
         </is>
       </c>
     </row>
@@ -61616,12 +61616,12 @@
       </c>
       <c r="K1115" t="inlineStr">
         <is>
-          <t>Shekh Shakol Mohammad</t>
+          <t>Shekha Shakol Mohammad</t>
         </is>
       </c>
       <c r="L1115" t="inlineStr">
         <is>
-          <t>Shekh Mohammad</t>
+          <t>Shekha Mohammad</t>
         </is>
       </c>
     </row>
@@ -61673,12 +61673,12 @@
       </c>
       <c r="K1116" t="inlineStr">
         <is>
-          <t>Shekh Naushad Mohammad</t>
+          <t>Shekha Naushad Mohammad</t>
         </is>
       </c>
       <c r="L1116" t="inlineStr">
         <is>
-          <t>Shekh Mohammad</t>
+          <t>Shekha Mohammad</t>
         </is>
       </c>
     </row>
@@ -61844,12 +61844,12 @@
       </c>
       <c r="K1119" t="inlineStr">
         <is>
-          <t>Karayat Tejasaunh Hyatasing</t>
+          <t>Karayat Tejasaunha Hyatasinga</t>
         </is>
       </c>
       <c r="L1119" t="inlineStr">
         <is>
-          <t>Karayat Hyatasing</t>
+          <t>Karayat Hyatasinga</t>
         </is>
       </c>
     </row>
@@ -61901,12 +61901,12 @@
       </c>
       <c r="K1120" t="inlineStr">
         <is>
-          <t>Karayat Pushpa Tejasinh</t>
+          <t>Karayat Pushpa Tejasinha</t>
         </is>
       </c>
       <c r="L1120" t="inlineStr">
         <is>
-          <t>Karayat Tejasinh</t>
+          <t>Karayat Tejasinha</t>
         </is>
       </c>
     </row>
@@ -61958,12 +61958,12 @@
       </c>
       <c r="K1121" t="inlineStr">
         <is>
-          <t>Karayat Yogesh Tejasinh</t>
+          <t>Karayat Yogesh Tejasinha</t>
         </is>
       </c>
       <c r="L1121" t="inlineStr">
         <is>
-          <t>Karayat Tejasinh</t>
+          <t>Karayat Tejasinha</t>
         </is>
       </c>
     </row>
@@ -62072,12 +62072,12 @@
       </c>
       <c r="K1123" t="inlineStr">
         <is>
-          <t>Karayat Vini Tejasinh</t>
+          <t>Karayat Vini Tejasinha</t>
         </is>
       </c>
       <c r="L1123" t="inlineStr">
         <is>
-          <t>Karayat Tejasinh</t>
+          <t>Karayat Tejasinha</t>
         </is>
       </c>
     </row>
@@ -62129,12 +62129,12 @@
       </c>
       <c r="K1124" t="inlineStr">
         <is>
-          <t>Karayat Raki Tejasinh</t>
+          <t>Karayat Roki Tejasinha</t>
         </is>
       </c>
       <c r="L1124" t="inlineStr">
         <is>
-          <t>Karayat Tejasinh</t>
+          <t>Karayat Tejasinha</t>
         </is>
       </c>
     </row>
@@ -62652,7 +62652,7 @@
       </c>
       <c r="K1133" t="inlineStr">
         <is>
-          <t>Prasad Shivaprasad Mhaisanand</t>
+          <t>Prasad Shivaprasad Mhaisananda</t>
         </is>
       </c>
       <c r="L1133" t="inlineStr">
@@ -63007,7 +63007,7 @@
       </c>
       <c r="L1141" t="inlineStr">
         <is>
-          <t>Savant Chandrakant Dhondu Va Savant Dhondu</t>
+          <t>Savanta Chandrakanta Dhondu Va Savanta Dhondu</t>
         </is>
       </c>
     </row>
@@ -63064,7 +63064,7 @@
       </c>
       <c r="L1142" t="inlineStr">
         <is>
-          <t>Sabant Madhuri Chandrakant Pa Savant Chandrakant</t>
+          <t>Sabanta Madhuri Chandrakanta Pa Savanta Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -63116,12 +63116,12 @@
       </c>
       <c r="K1143" t="inlineStr">
         <is>
-          <t>Savant Girish Chandrakant</t>
+          <t>Savanta Girish Chandrakanta</t>
         </is>
       </c>
       <c r="L1143" t="inlineStr">
         <is>
-          <t>Savant Chandrakant</t>
+          <t>Savanta Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -63178,7 +63178,7 @@
       </c>
       <c r="L1144" t="inlineStr">
         <is>
-          <t>Savant Anandi Dhondu Pa Savant Dhondu</t>
+          <t>Savanta Anandi Dhondu Pa Savanta Dhondu</t>
         </is>
       </c>
     </row>
@@ -63344,7 +63344,7 @@
       </c>
       <c r="K1147" t="inlineStr">
         <is>
-          <t>Kentura Shankarasaung Bhagava</t>
+          <t>Kentura Shankarasaunga Bhagava</t>
         </is>
       </c>
       <c r="L1147" t="inlineStr">
@@ -63401,12 +63401,12 @@
       </c>
       <c r="K1148" t="inlineStr">
         <is>
-          <t>Kentura Liladevi Shankarasing</t>
+          <t>Kentura Liladevi Shankarasinga</t>
         </is>
       </c>
       <c r="L1148" t="inlineStr">
         <is>
-          <t>Kentura Shankarasing</t>
+          <t>Kentura Shankarasinga</t>
         </is>
       </c>
     </row>
@@ -63458,12 +63458,12 @@
       </c>
       <c r="K1149" t="inlineStr">
         <is>
-          <t>Gavai Manohar Pandurang</t>
+          <t>Gavai Manohar Panduranga</t>
         </is>
       </c>
       <c r="L1149" t="inlineStr">
         <is>
-          <t>Gavai Pandurang</t>
+          <t>Gavai Panduranga</t>
         </is>
       </c>
     </row>
@@ -63624,7 +63624,7 @@
       </c>
       <c r="K1152" t="inlineStr">
         <is>
-          <t>Baakrushn Gavai Manohar</t>
+          <t>Baakrushna Gavai Manohar</t>
         </is>
       </c>
     </row>
@@ -63681,12 +63681,12 @@
       </c>
       <c r="K1153" t="inlineStr">
         <is>
-          <t>Bandagae Sadanand Yashavant</t>
+          <t>Bandagae Sadananda Yashavanta</t>
         </is>
       </c>
       <c r="L1153" t="inlineStr">
         <is>
-          <t>Bandagae Yashavant</t>
+          <t>Bandagae Yashavanta</t>
         </is>
       </c>
     </row>
@@ -63743,12 +63743,12 @@
       </c>
       <c r="K1154" t="inlineStr">
         <is>
-          <t>Bandagae Suvarna Sadanand</t>
+          <t>Bandagae Suvarna Sadananda</t>
         </is>
       </c>
       <c r="L1154" t="inlineStr">
         <is>
-          <t>Bandagae Sadanand</t>
+          <t>Bandagae Sadananda</t>
         </is>
       </c>
     </row>
@@ -63800,12 +63800,12 @@
       </c>
       <c r="K1155" t="inlineStr">
         <is>
-          <t>Bandagae Sachin Sadanand</t>
+          <t>Bandagae Sachin Sadananda</t>
         </is>
       </c>
       <c r="L1155" t="inlineStr">
         <is>
-          <t>Bandagae Sadanand</t>
+          <t>Bandagae Sadananda</t>
         </is>
       </c>
     </row>
@@ -63857,12 +63857,12 @@
       </c>
       <c r="K1156" t="inlineStr">
         <is>
-          <t>Bandagae Sudhakar Sadanand</t>
+          <t>Bandagae Sudhakar Sadananda</t>
         </is>
       </c>
       <c r="L1156" t="inlineStr">
         <is>
-          <t>Bandagae Sadanand</t>
+          <t>Bandagae Sadananda</t>
         </is>
       </c>
     </row>
@@ -63914,12 +63914,12 @@
       </c>
       <c r="K1157" t="inlineStr">
         <is>
-          <t>Bandagae Sandip Yashavant</t>
+          <t>Bandagae Sandip Yashavanta</t>
         </is>
       </c>
       <c r="L1157" t="inlineStr">
         <is>
-          <t>Bandagae Yashavant</t>
+          <t>Bandagae Yashavanta</t>
         </is>
       </c>
     </row>
@@ -63971,7 +63971,7 @@
       </c>
       <c r="K1158" t="inlineStr">
         <is>
-          <t>Notiyal Maheshanand Sitaram</t>
+          <t>Notiyal Maheshananda Sitaram</t>
         </is>
       </c>
       <c r="L1158" t="inlineStr">
@@ -64033,7 +64033,7 @@
       </c>
       <c r="L1159" t="inlineStr">
         <is>
-          <t>Notiyal Maheshanand</t>
+          <t>Notiyal Maheshananda</t>
         </is>
       </c>
     </row>
@@ -64090,12 +64090,12 @@
       </c>
       <c r="K1160" t="inlineStr">
         <is>
-          <t>Notiyal Anil Maheshanand</t>
+          <t>Notiyal Anil Maheshananda</t>
         </is>
       </c>
       <c r="L1160" t="inlineStr">
         <is>
-          <t>Notiyal Maheshanand</t>
+          <t>Notiyal Maheshananda</t>
         </is>
       </c>
     </row>
@@ -64152,12 +64152,12 @@
       </c>
       <c r="K1161" t="inlineStr">
         <is>
-          <t>Notiyal Arun Maheshanand</t>
+          <t>Notiyal Arun Maheshananda</t>
         </is>
       </c>
       <c r="L1161" t="inlineStr">
         <is>
-          <t>Notiyal Maheshanand</t>
+          <t>Notiyal Maheshananda</t>
         </is>
       </c>
     </row>
@@ -64209,12 +64209,12 @@
       </c>
       <c r="K1162" t="inlineStr">
         <is>
-          <t>Kurup Balakrushn Govid</t>
+          <t>Kurup Balakrushna Govid</t>
         </is>
       </c>
       <c r="L1162" t="inlineStr">
         <is>
-          <t>Kurup Govind</t>
+          <t>Kurup Govinda</t>
         </is>
       </c>
     </row>
@@ -64266,12 +64266,12 @@
       </c>
       <c r="K1163" t="inlineStr">
         <is>
-          <t>Kurup Sumati Balakrushn</t>
+          <t>Kurup Sumati Balakrushna</t>
         </is>
       </c>
       <c r="L1163" t="inlineStr">
         <is>
-          <t>Kurup Balakrushn</t>
+          <t>Kurup Balakrushna</t>
         </is>
       </c>
     </row>
@@ -64323,12 +64323,12 @@
       </c>
       <c r="K1164" t="inlineStr">
         <is>
-          <t>Kurup Brijesh Balakrushn</t>
+          <t>Kurup Brijesh Balakrushna</t>
         </is>
       </c>
       <c r="L1164" t="inlineStr">
         <is>
-          <t>Kurup Balakrushn</t>
+          <t>Kurup Balakrushna</t>
         </is>
       </c>
     </row>
@@ -64380,12 +64380,12 @@
       </c>
       <c r="K1165" t="inlineStr">
         <is>
-          <t>Kurup Brijula Balakrushn</t>
+          <t>Kurup Brijula Balakrushna</t>
         </is>
       </c>
       <c r="L1165" t="inlineStr">
         <is>
-          <t>Kurup Balakrushn</t>
+          <t>Kurup Balakrushna</t>
         </is>
       </c>
     </row>
@@ -64551,12 +64551,12 @@
       </c>
       <c r="K1168" t="inlineStr">
         <is>
-          <t>Jadhav Nilesh Pandurang</t>
+          <t>Jadhav Nilesh Panduranga</t>
         </is>
       </c>
       <c r="L1168" t="inlineStr">
         <is>
-          <t>Jadhav Pandurang</t>
+          <t>Jadhav Panduranga</t>
         </is>
       </c>
     </row>
@@ -64608,7 +64608,7 @@
       </c>
       <c r="K1169" t="inlineStr">
         <is>
-          <t>Jadhav Pandurang Dhondu</t>
+          <t>Jadhav Panduranga Dhondu</t>
         </is>
       </c>
       <c r="L1169" t="inlineStr">
@@ -64665,12 +64665,12 @@
       </c>
       <c r="K1170" t="inlineStr">
         <is>
-          <t>Jadhav Pramila Pandurang</t>
+          <t>Jadhav Pramila Panduranga</t>
         </is>
       </c>
       <c r="L1170" t="inlineStr">
         <is>
-          <t>Jadhav Pandurang</t>
+          <t>Jadhav Panduranga</t>
         </is>
       </c>
     </row>
@@ -64764,7 +64764,7 @@
       </c>
       <c r="K1172" t="inlineStr">
         <is>
-          <t>Bokha Putul Mrunalakant</t>
+          <t>Bokha Putul Mrunalakanta</t>
         </is>
       </c>
       <c r="L1172" t="inlineStr">
@@ -64935,7 +64935,7 @@
       </c>
       <c r="K1175" t="inlineStr">
         <is>
-          <t>Tambe Shashikant Shankar</t>
+          <t>Tambe Shashikanta Shankar</t>
         </is>
       </c>
       <c r="L1175" t="inlineStr">
@@ -64997,12 +64997,12 @@
       </c>
       <c r="K1176" t="inlineStr">
         <is>
-          <t>Tambe Smita Shashikant</t>
+          <t>Tambe Smita Shashikanta</t>
         </is>
       </c>
       <c r="L1176" t="inlineStr">
         <is>
-          <t>Tambe Shashikant</t>
+          <t>Tambe Shashikanta</t>
         </is>
       </c>
     </row>
@@ -65215,7 +65215,7 @@
       </c>
       <c r="K1180" t="inlineStr">
         <is>
-          <t>Miya~ Babujonn Alamashe</t>
+          <t>Miya~ Babujonna Alamashe</t>
         </is>
       </c>
       <c r="L1180" t="inlineStr">
@@ -65277,7 +65277,7 @@
       </c>
       <c r="L1181" t="inlineStr">
         <is>
-          <t>Miya~ Babujan</t>
+          <t>Miya~ Babujon</t>
         </is>
       </c>
     </row>
@@ -65357,12 +65357,12 @@
       </c>
       <c r="K1184" t="inlineStr">
         <is>
-          <t>Miya~ Samimanisa Babujan</t>
+          <t>Miya~ Samimanisa Babujon</t>
         </is>
       </c>
       <c r="L1184" t="inlineStr">
         <is>
-          <t>Miya~ Babujan</t>
+          <t>Miya~ Babujon</t>
         </is>
       </c>
     </row>
@@ -65528,7 +65528,7 @@
       </c>
       <c r="K1187" t="inlineStr">
         <is>
-          <t>Barua Abhitabh Anupakuma</t>
+          <t>Barua Abhitabha Anupakuma</t>
         </is>
       </c>
       <c r="L1187" t="inlineStr">
@@ -65585,7 +65585,7 @@
       </c>
       <c r="K1188" t="inlineStr">
         <is>
-          <t>Barua Ajitabh Anupakuma</t>
+          <t>Barua Ajitabha Anupakuma</t>
         </is>
       </c>
       <c r="L1188" t="inlineStr">
@@ -66227,7 +66227,7 @@
       </c>
       <c r="K1199" t="inlineStr">
         <is>
-          <t>Dudavadakar Anand Gajanan</t>
+          <t>Dudavadakar Ananda Gajanan</t>
         </is>
       </c>
       <c r="L1199" t="inlineStr">
@@ -66284,12 +66284,12 @@
       </c>
       <c r="K1200" t="inlineStr">
         <is>
-          <t>Dudabadakar Ashvini Anand</t>
+          <t>Dudabadakar Ashvini Ananda</t>
         </is>
       </c>
       <c r="L1200" t="inlineStr">
         <is>
-          <t>Dudavarakar Anand</t>
+          <t>Dudavarakar Ananda</t>
         </is>
       </c>
     </row>
@@ -66341,12 +66341,12 @@
       </c>
       <c r="K1201" t="inlineStr">
         <is>
-          <t>Pitae Arun Ramachandr</t>
+          <t>Pitae Arun Ramachandra</t>
         </is>
       </c>
       <c r="L1201" t="inlineStr">
         <is>
-          <t>Pitae Ramachandr</t>
+          <t>Pitae Ramachandra</t>
         </is>
       </c>
     </row>
@@ -66683,12 +66683,12 @@
       </c>
       <c r="K1207" t="inlineStr">
         <is>
-          <t>Maakar Mangesh Harishchandr</t>
+          <t>Maakar Mangesh Harishchandra</t>
         </is>
       </c>
       <c r="L1207" t="inlineStr">
         <is>
-          <t>Maakar Harishchandr</t>
+          <t>Maakar Harishchandra</t>
         </is>
       </c>
     </row>
@@ -66968,7 +66968,7 @@
       </c>
       <c r="K1212" t="inlineStr">
         <is>
-          <t>Jakhia Chandrakant Premaji</t>
+          <t>Jakhia Chandrakanta Premaji</t>
         </is>
       </c>
       <c r="L1212" t="inlineStr">
@@ -67025,12 +67025,12 @@
       </c>
       <c r="K1213" t="inlineStr">
         <is>
-          <t>Jakhia Jasmina Chandrakant</t>
+          <t>Jakhia Jasmina Chandrakanta</t>
         </is>
       </c>
       <c r="L1213" t="inlineStr">
         <is>
-          <t>Jakhia Chandrakant</t>
+          <t>Jakhia Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -67560,12 +67560,12 @@
       </c>
       <c r="K1223" t="inlineStr">
         <is>
-          <t>Bisht Khemasinh Chandrasih</t>
+          <t>Bishta Khemasinha Chandrasih</t>
         </is>
       </c>
       <c r="L1223" t="inlineStr">
         <is>
-          <t>Bisht Chandrasih</t>
+          <t>Bishta Chandrasih</t>
         </is>
       </c>
     </row>
@@ -67622,12 +67622,12 @@
       </c>
       <c r="K1224" t="inlineStr">
         <is>
-          <t>Bisht Pramod Khemasinh</t>
+          <t>Bishta Pramod Khemasinha</t>
         </is>
       </c>
       <c r="L1224" t="inlineStr">
         <is>
-          <t>Bisht Khemasinh</t>
+          <t>Bishta Khemasinha</t>
         </is>
       </c>
     </row>
@@ -67684,12 +67684,12 @@
       </c>
       <c r="K1225" t="inlineStr">
         <is>
-          <t>Bisht Reshma Pramod</t>
+          <t>Bishta Reshma Pramod</t>
         </is>
       </c>
       <c r="L1225" t="inlineStr">
         <is>
-          <t>Bisht Pramod</t>
+          <t>Bishta Pramod</t>
         </is>
       </c>
     </row>
@@ -67746,12 +67746,12 @@
       </c>
       <c r="K1226" t="inlineStr">
         <is>
-          <t>Bisht Gita Khemasinh</t>
+          <t>Bishta Gita Khemasinha</t>
         </is>
       </c>
       <c r="L1226" t="inlineStr">
         <is>
-          <t>Bisht Khemasinh</t>
+          <t>Bishta Khemasinha</t>
         </is>
       </c>
     </row>
@@ -68656,12 +68656,12 @@
       </c>
       <c r="K1244" t="inlineStr">
         <is>
-          <t>Rathod Rajendrasig Vikramasing</t>
+          <t>Rathod Rajendrasig Vikramasinga</t>
         </is>
       </c>
       <c r="L1244" t="inlineStr">
         <is>
-          <t>Rathod Vikramasing</t>
+          <t>Rathod Vikramasinga</t>
         </is>
       </c>
     </row>
@@ -68718,7 +68718,7 @@
       </c>
       <c r="L1245" t="inlineStr">
         <is>
-          <t>Rathod Rajendrasing</t>
+          <t>Rathod Rajendrasinga</t>
         </is>
       </c>
     </row>
@@ -68998,7 +68998,7 @@
       </c>
       <c r="K1250" t="inlineStr">
         <is>
-          <t>Patel Yageshr Amit</t>
+          <t>Patel Yageshra Amit</t>
         </is>
       </c>
       <c r="L1250" t="inlineStr">
@@ -69283,12 +69283,12 @@
       </c>
       <c r="K1255" t="inlineStr">
         <is>
-          <t>Shikhavat Rajavirasing Anupasing</t>
+          <t>Shikhavat Rajavirasinga Anupasinga</t>
         </is>
       </c>
       <c r="L1255" t="inlineStr">
         <is>
-          <t>Shikhavat Anupasing</t>
+          <t>Shikhavat Anupasinga</t>
         </is>
       </c>
     </row>
@@ -69340,12 +69340,12 @@
       </c>
       <c r="K1256" t="inlineStr">
         <is>
-          <t>Shikhavat Vinod Rajavirasing</t>
+          <t>Shikhavat Vinod Rajavirasinga</t>
         </is>
       </c>
       <c r="L1256" t="inlineStr">
         <is>
-          <t>Shikhavat Rajavirasing</t>
+          <t>Shikhavat Rajavirasinga</t>
         </is>
       </c>
     </row>
@@ -69397,12 +69397,12 @@
       </c>
       <c r="K1257" t="inlineStr">
         <is>
-          <t>Chauhan Samarasing Padmasi</t>
+          <t>Chauhan Samarasinga Padmasi</t>
         </is>
       </c>
       <c r="L1257" t="inlineStr">
         <is>
-          <t>Chauhan Padmasing</t>
+          <t>Chauhan Padmasinga</t>
         </is>
       </c>
     </row>
@@ -69459,7 +69459,7 @@
       </c>
       <c r="L1258" t="inlineStr">
         <is>
-          <t>Chauhan Samarasing</t>
+          <t>Chauhan Samarasinga</t>
         </is>
       </c>
     </row>
@@ -69511,12 +69511,12 @@
       </c>
       <c r="K1259" t="inlineStr">
         <is>
-          <t>Kundanaph Prasad Vishvanath</t>
+          <t>Kundanapha Prasad Vishvanatha</t>
         </is>
       </c>
       <c r="L1259" t="inlineStr">
         <is>
-          <t>Prasad Vishvanath</t>
+          <t>Prasad Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -69568,12 +69568,12 @@
       </c>
       <c r="K1260" t="inlineStr">
         <is>
-          <t>Prasad Dipti Vishvanath</t>
+          <t>Prasad Dipti Vishvanatha</t>
         </is>
       </c>
       <c r="L1260" t="inlineStr">
         <is>
-          <t>Prasad Vishvanath</t>
+          <t>Prasad Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -69625,12 +69625,12 @@
       </c>
       <c r="K1261" t="inlineStr">
         <is>
-          <t>Prasad Sangita Vishvanath</t>
+          <t>Prasad Sangita Vishvanatha</t>
         </is>
       </c>
       <c r="L1261" t="inlineStr">
         <is>
-          <t>Prasad Vishvanath</t>
+          <t>Prasad Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -69682,12 +69682,12 @@
       </c>
       <c r="K1262" t="inlineStr">
         <is>
-          <t>Prasad Sanjay Vishvanath</t>
+          <t>Prasad Sanjay Vishvanatha</t>
         </is>
       </c>
       <c r="L1262" t="inlineStr">
         <is>
-          <t>Prasad Vishvanath</t>
+          <t>Prasad Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -70185,7 +70185,7 @@
       </c>
       <c r="K1271" t="inlineStr">
         <is>
-          <t>Badrike Pandurang Sadashiv</t>
+          <t>Badrike Panduranga Sadashiv</t>
         </is>
       </c>
       <c r="L1271" t="inlineStr">
@@ -70242,12 +70242,12 @@
       </c>
       <c r="K1272" t="inlineStr">
         <is>
-          <t>Badrike Surekha Pandurang</t>
+          <t>Badrike Surekha Panduranga</t>
         </is>
       </c>
       <c r="L1272" t="inlineStr">
         <is>
-          <t>Badrike Pandurang</t>
+          <t>Badrike Panduranga</t>
         </is>
       </c>
     </row>
@@ -70726,12 +70726,12 @@
       </c>
       <c r="K1282" t="inlineStr">
         <is>
-          <t>Kakkar Pritam Paramanand</t>
+          <t>Kakkar Pritam Paramananda</t>
         </is>
       </c>
       <c r="L1282" t="inlineStr">
         <is>
-          <t>Kakkar Paramanand</t>
+          <t>Kakkar Paramananda</t>
         </is>
       </c>
     </row>
@@ -71053,12 +71053,12 @@
       </c>
       <c r="K1288" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanath Baavant</t>
+          <t>Chavhan Vishvanatha Baavanta</t>
         </is>
       </c>
       <c r="L1288" t="inlineStr">
         <is>
-          <t>Chavhan Baavant</t>
+          <t>Chavhan Baavanta</t>
         </is>
       </c>
     </row>
@@ -71110,12 +71110,12 @@
       </c>
       <c r="K1289" t="inlineStr">
         <is>
-          <t>Chavhan Prabha Vishvanath</t>
+          <t>Chavhan Prabha Vishvanatha</t>
         </is>
       </c>
       <c r="L1289" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanath</t>
+          <t>Chavhan Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -71167,12 +71167,12 @@
       </c>
       <c r="K1290" t="inlineStr">
         <is>
-          <t>Chavhan Sadanand Vishvanath</t>
+          <t>Chavhan Sadananda Vishvanatha</t>
         </is>
       </c>
       <c r="L1290" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanath</t>
+          <t>Chavhan Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -71224,12 +71224,12 @@
       </c>
       <c r="K1291" t="inlineStr">
         <is>
-          <t>Chavhan Kamal Vishvanath</t>
+          <t>Chavhan Kamal Vishvanatha</t>
         </is>
       </c>
       <c r="L1291" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanath</t>
+          <t>Chavhan Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -71271,7 +71271,7 @@
       </c>
       <c r="K1292" t="inlineStr">
         <is>
-          <t>Vach Chavhan Vishvanath</t>
+          <t>Vach Chavhan Vishvanatha</t>
         </is>
       </c>
     </row>
@@ -72778,12 +72778,12 @@
       </c>
       <c r="K1318" t="inlineStr">
         <is>
-          <t>Ghag Harishchandr Ramachandr</t>
+          <t>Ghag Harishchandra Ramachandra</t>
         </is>
       </c>
       <c r="L1318" t="inlineStr">
         <is>
-          <t>Ghag Ramachandr</t>
+          <t>Ghag Ramachandra</t>
         </is>
       </c>
     </row>
@@ -72840,12 +72840,12 @@
       </c>
       <c r="K1319" t="inlineStr">
         <is>
-          <t>Ghag Snehalata Harishchandr</t>
+          <t>Ghag Snehalata Harishchandra</t>
         </is>
       </c>
       <c r="L1319" t="inlineStr">
         <is>
-          <t>Ghag Harishchandr</t>
+          <t>Ghag Harishchandra</t>
         </is>
       </c>
     </row>
@@ -72902,12 +72902,12 @@
       </c>
       <c r="K1320" t="inlineStr">
         <is>
-          <t>Ghag Surendr Harishchandr</t>
+          <t>Ghag Surendra Harishchandra</t>
         </is>
       </c>
       <c r="L1320" t="inlineStr">
         <is>
-          <t>Ghag Harishchandr</t>
+          <t>Ghag Harishchandra</t>
         </is>
       </c>
     </row>
@@ -72964,12 +72964,12 @@
       </c>
       <c r="K1321" t="inlineStr">
         <is>
-          <t>Ghag Shashank Harishchandr</t>
+          <t>Ghag Shashanka Harishchandra</t>
         </is>
       </c>
       <c r="L1321" t="inlineStr">
         <is>
-          <t>Ghag Harishchandr</t>
+          <t>Ghag Harishchandra</t>
         </is>
       </c>
     </row>
@@ -73178,12 +73178,12 @@
       </c>
       <c r="K1326" t="inlineStr">
         <is>
-          <t>Nerakar Dipti Dasharath</t>
+          <t>Nerakar Dipti Dasharatha</t>
         </is>
       </c>
       <c r="L1326" t="inlineStr">
         <is>
-          <t>Nerakar Dasharath</t>
+          <t>Nerakar Dasharatha</t>
         </is>
       </c>
     </row>
@@ -73225,7 +73225,7 @@
       </c>
       <c r="K1327" t="inlineStr">
         <is>
-          <t>Bhiva Nerakar Dasharath</t>
+          <t>Bhiva Nerakar Dasharatha</t>
         </is>
       </c>
     </row>
@@ -73277,12 +73277,12 @@
       </c>
       <c r="K1328" t="inlineStr">
         <is>
-          <t>Nerakar Darshana Dasharath</t>
+          <t>Nerakar Darshana Dasharatha</t>
         </is>
       </c>
       <c r="L1328" t="inlineStr">
         <is>
-          <t>Nerakar Dasharath</t>
+          <t>Nerakar Dasharatha</t>
         </is>
       </c>
     </row>
@@ -73525,7 +73525,7 @@
       </c>
       <c r="K1332" t="inlineStr">
         <is>
-          <t>Maglor Rama Devadas</t>
+          <t>Meglor Rama Devadas</t>
         </is>
       </c>
       <c r="L1332" t="inlineStr">
@@ -73582,7 +73582,7 @@
       </c>
       <c r="K1333" t="inlineStr">
         <is>
-          <t>Maglor Malati Rama</t>
+          <t>Meglor Malati Rama</t>
         </is>
       </c>
       <c r="L1333" t="inlineStr">
@@ -73753,7 +73753,7 @@
       </c>
       <c r="K1336" t="inlineStr">
         <is>
-          <t>Saavi Sachin Shyamasund</t>
+          <t>Saavi Sachin Shyamasunda</t>
         </is>
       </c>
       <c r="L1336" t="inlineStr">
@@ -74484,12 +74484,12 @@
       </c>
       <c r="K1349" t="inlineStr">
         <is>
-          <t>Gavai Devadas Ekanath</t>
+          <t>Gavai Devadas Ekanatha</t>
         </is>
       </c>
       <c r="L1349" t="inlineStr">
         <is>
-          <t>Gavai Ekanath</t>
+          <t>Gavai Ekanatha</t>
         </is>
       </c>
     </row>
@@ -75059,7 +75059,7 @@
       </c>
       <c r="K1359" t="inlineStr">
         <is>
-          <t>Saavi Rajendr Bhaurav</t>
+          <t>Saavi Rajendra Bhaurav</t>
         </is>
       </c>
       <c r="L1359" t="inlineStr">
@@ -75116,12 +75116,12 @@
       </c>
       <c r="K1360" t="inlineStr">
         <is>
-          <t>Saavi Rashmi Rajendr</t>
+          <t>Saavi Rashmi Rajendra</t>
         </is>
       </c>
       <c r="L1360" t="inlineStr">
         <is>
-          <t>Saavi Rajendr</t>
+          <t>Saavi Rajendra</t>
         </is>
       </c>
     </row>
@@ -75354,7 +75354,7 @@
       </c>
       <c r="K1364" t="inlineStr">
         <is>
-          <t>Saavi Milind Dattaram</t>
+          <t>Saavi Milinda Dattaram</t>
         </is>
       </c>
       <c r="L1364" t="inlineStr">
@@ -75468,7 +75468,7 @@
       </c>
       <c r="K1366" t="inlineStr">
         <is>
-          <t>Gurav Pandurang Dhondu</t>
+          <t>Gurav Panduranga Dhondu</t>
         </is>
       </c>
       <c r="L1366" t="inlineStr">
@@ -75525,12 +75525,12 @@
       </c>
       <c r="K1367" t="inlineStr">
         <is>
-          <t>Gurav Sudhan Pandurang</t>
+          <t>Gurav Sudhan Panduranga</t>
         </is>
       </c>
       <c r="L1367" t="inlineStr">
         <is>
-          <t>Gurav Pandurang</t>
+          <t>Gurav Panduranga</t>
         </is>
       </c>
     </row>
@@ -75796,12 +75796,12 @@
       </c>
       <c r="K1373" t="inlineStr">
         <is>
-          <t>Kadam Sharad Anant</t>
+          <t>Kadam Sharad Ananta</t>
         </is>
       </c>
       <c r="L1373" t="inlineStr">
         <is>
-          <t>Kadam Anant</t>
+          <t>Kadam Ananta</t>
         </is>
       </c>
     </row>
@@ -75910,12 +75910,12 @@
       </c>
       <c r="K1375" t="inlineStr">
         <is>
-          <t>Kadam Sanjay Anant</t>
+          <t>Kadam Sanjay Ananta</t>
         </is>
       </c>
       <c r="L1375" t="inlineStr">
         <is>
-          <t>Kadam Anant</t>
+          <t>Kadam Ananta</t>
         </is>
       </c>
     </row>
@@ -75967,7 +75967,7 @@
       </c>
       <c r="K1376" t="inlineStr">
         <is>
-          <t>Saavi Jayavant Chandrarav</t>
+          <t>Saavi Jayavanta Chandrarav</t>
         </is>
       </c>
       <c r="L1376" t="inlineStr">
@@ -76029,12 +76029,12 @@
       </c>
       <c r="K1377" t="inlineStr">
         <is>
-          <t>Saavi Nita Jayavant</t>
+          <t>Saavi Nita Jayavanta</t>
         </is>
       </c>
       <c r="L1377" t="inlineStr">
         <is>
-          <t>Saavi Jayavant</t>
+          <t>Saavi Jayavanta</t>
         </is>
       </c>
     </row>
@@ -76086,12 +76086,12 @@
       </c>
       <c r="K1378" t="inlineStr">
         <is>
-          <t>Saavi Atul Jayavant</t>
+          <t>Saavi Atul Jayavanta</t>
         </is>
       </c>
       <c r="L1378" t="inlineStr">
         <is>
-          <t>Saavi Jayavant</t>
+          <t>Saavi Jayavanta</t>
         </is>
       </c>
     </row>
@@ -76143,12 +76143,12 @@
       </c>
       <c r="K1379" t="inlineStr">
         <is>
-          <t>Saavi Mahesh Jayavant</t>
+          <t>Saavi Mahesh Jayavanta</t>
         </is>
       </c>
       <c r="L1379" t="inlineStr">
         <is>
-          <t>Saavi Jayavant</t>
+          <t>Saavi Jayavanta</t>
         </is>
       </c>
     </row>
@@ -76200,12 +76200,12 @@
       </c>
       <c r="K1380" t="inlineStr">
         <is>
-          <t>Saavi Sagar Jayavant</t>
+          <t>Saavi Sagar Jayavanta</t>
         </is>
       </c>
       <c r="L1380" t="inlineStr">
         <is>
-          <t>Saavi Jayavant</t>
+          <t>Saavi Jayavanta</t>
         </is>
       </c>
     </row>
@@ -76257,7 +76257,7 @@
       </c>
       <c r="K1381" t="inlineStr">
         <is>
-          <t>Manjarekar Pandurang Sakharam</t>
+          <t>Manjarekar Panduranga Sakharam</t>
         </is>
       </c>
       <c r="L1381" t="inlineStr">
@@ -76314,12 +76314,12 @@
       </c>
       <c r="K1382" t="inlineStr">
         <is>
-          <t>Manjarekar Rajashri Pandurang</t>
+          <t>Manjarekar Rajashri Panduranga</t>
         </is>
       </c>
       <c r="L1382" t="inlineStr">
         <is>
-          <t>Manjarekar Pandurang</t>
+          <t>Manjarekar Panduranga</t>
         </is>
       </c>
     </row>
@@ -76371,12 +76371,12 @@
       </c>
       <c r="K1383" t="inlineStr">
         <is>
-          <t>Manjarekar Yatin Pandurang</t>
+          <t>Manjarekar Yatin Panduranga</t>
         </is>
       </c>
       <c r="L1383" t="inlineStr">
         <is>
-          <t>Manjarekar Pandurang</t>
+          <t>Manjarekar Panduranga</t>
         </is>
       </c>
     </row>
@@ -76433,7 +76433,7 @@
       </c>
       <c r="L1384" t="inlineStr">
         <is>
-          <t>Manjarekar Pandurang</t>
+          <t>Manjarekar Panduranga</t>
         </is>
       </c>
     </row>
@@ -76485,12 +76485,12 @@
       </c>
       <c r="K1385" t="inlineStr">
         <is>
-          <t>Manjarekar Lalita Pandurang</t>
+          <t>Manjarekar Lalita Panduranga</t>
         </is>
       </c>
       <c r="L1385" t="inlineStr">
         <is>
-          <t>Manjarekar Pandurang</t>
+          <t>Manjarekar Panduranga</t>
         </is>
       </c>
     </row>
@@ -76547,7 +76547,7 @@
       </c>
       <c r="K1386" t="inlineStr">
         <is>
-          <t>Jadhav Anant Shankar</t>
+          <t>Jadhav Ananta Shankar</t>
         </is>
       </c>
       <c r="L1386" t="inlineStr">
@@ -76609,12 +76609,12 @@
       </c>
       <c r="K1387" t="inlineStr">
         <is>
-          <t>Jadhav Nilima Anant</t>
+          <t>Jadhav Nilima Ananta</t>
         </is>
       </c>
       <c r="L1387" t="inlineStr">
         <is>
-          <t>Jadhav Anant</t>
+          <t>Jadhav Ananta</t>
         </is>
       </c>
     </row>
@@ -76666,12 +76666,12 @@
       </c>
       <c r="K1388" t="inlineStr">
         <is>
-          <t>Jadhav Sanjog Anant</t>
+          <t>Jadhav Sanjog Ananta</t>
         </is>
       </c>
       <c r="L1388" t="inlineStr">
         <is>
-          <t>Jadhav Anant</t>
+          <t>Jadhav Ananta</t>
         </is>
       </c>
     </row>
@@ -76713,7 +76713,7 @@
       </c>
       <c r="K1389" t="inlineStr">
         <is>
-          <t>Sanjog Jadhav Anant</t>
+          <t>Sanjog Jadhav Ananta</t>
         </is>
       </c>
     </row>
@@ -78150,7 +78150,7 @@
       </c>
       <c r="L1415" t="inlineStr">
         <is>
-          <t>Solanko Govind</t>
+          <t>Solanko Govinda</t>
         </is>
       </c>
     </row>
@@ -78317,7 +78317,7 @@
       </c>
       <c r="K1419" t="inlineStr">
         <is>
-          <t>More Chandrakant Gopa</t>
+          <t>More Chandrakanta Gopa</t>
         </is>
       </c>
       <c r="L1419" t="inlineStr">
@@ -78374,12 +78374,12 @@
       </c>
       <c r="K1420" t="inlineStr">
         <is>
-          <t>More Nita Chandrakant</t>
+          <t>More Nita Chandrakanta</t>
         </is>
       </c>
       <c r="L1420" t="inlineStr">
         <is>
-          <t>More Chandrakant</t>
+          <t>More Chandrakanta</t>
         </is>
       </c>
     </row>
@@ -78941,7 +78941,7 @@
       </c>
       <c r="K1431" t="inlineStr">
         <is>
-          <t>Nikam Anant Govind</t>
+          <t>Nikam Ananta Govinda</t>
         </is>
       </c>
       <c r="L1431" t="inlineStr">
@@ -78998,12 +78998,12 @@
       </c>
       <c r="K1432" t="inlineStr">
         <is>
-          <t>Nikam Arati Anant</t>
+          <t>Nikam Arati Ananta</t>
         </is>
       </c>
       <c r="L1432" t="inlineStr">
         <is>
-          <t>Nikam Anant</t>
+          <t>Nikam Ananta</t>
         </is>
       </c>
     </row>
@@ -79055,12 +79055,12 @@
       </c>
       <c r="K1433" t="inlineStr">
         <is>
-          <t>Shekh Mahamadajaphar Imauddin</t>
+          <t>Shekha Mahamadajaphar Imauddin</t>
         </is>
       </c>
       <c r="L1433" t="inlineStr">
         <is>
-          <t>Shekh Imauddin</t>
+          <t>Shekha Imauddin</t>
         </is>
       </c>
     </row>
@@ -79112,12 +79112,12 @@
       </c>
       <c r="K1434" t="inlineStr">
         <is>
-          <t>Shekh Aripha Mahamadajaphar</t>
+          <t>Shekha Aripha Mahamadajaphar</t>
         </is>
       </c>
       <c r="L1434" t="inlineStr">
         <is>
-          <t>Shekh Mahamadajaphar</t>
+          <t>Shekha Mahamadajaphar</t>
         </is>
       </c>
     </row>
@@ -79169,12 +79169,12 @@
       </c>
       <c r="K1435" t="inlineStr">
         <is>
-          <t>Sonavane Sanjay Ramachandr</t>
+          <t>Sonavane Sanjay Ramachandra</t>
         </is>
       </c>
       <c r="L1435" t="inlineStr">
         <is>
-          <t>Sonavane Ramachandr</t>
+          <t>Sonavane Ramachandra</t>
         </is>
       </c>
     </row>
@@ -79283,12 +79283,12 @@
       </c>
       <c r="K1437" t="inlineStr">
         <is>
-          <t>Sonavane Santosh Ramachandr</t>
+          <t>Sonavane Santosh Ramachandra</t>
         </is>
       </c>
       <c r="L1437" t="inlineStr">
         <is>
-          <t>Sonavane Ramachandr</t>
+          <t>Sonavane Ramachandra</t>
         </is>
       </c>
     </row>
@@ -79625,7 +79625,7 @@
       </c>
       <c r="K1443" t="inlineStr">
         <is>
-          <t>Kae Shriram Govind</t>
+          <t>Kae Shriram Govinda</t>
         </is>
       </c>
       <c r="L1443" t="inlineStr">
@@ -79853,12 +79853,12 @@
       </c>
       <c r="K1447" t="inlineStr">
         <is>
-          <t>Rasam Prabhakar Ramachandr</t>
+          <t>Rasam Prabhakar Ramachandra</t>
         </is>
       </c>
       <c r="L1447" t="inlineStr">
         <is>
-          <t>Rasam Ramachandr</t>
+          <t>Rasam Ramachandra</t>
         </is>
       </c>
     </row>
@@ -80081,7 +80081,7 @@
       </c>
       <c r="K1451" t="inlineStr">
         <is>
-          <t>Rasam Prashant Prabhakar</t>
+          <t>Rasam Prashanta Prabhakar</t>
         </is>
       </c>
       <c r="L1451" t="inlineStr">
@@ -80294,12 +80294,12 @@
       </c>
       <c r="K1455" t="inlineStr">
         <is>
-          <t>Shinde Shankar Ramachandr</t>
+          <t>Shinde Shankar Ramachandra</t>
         </is>
       </c>
       <c r="L1455" t="inlineStr">
         <is>
-          <t>Shinde Ramachandr</t>
+          <t>Shinde Ramachandra</t>
         </is>
       </c>
     </row>
@@ -80648,7 +80648,7 @@
       </c>
       <c r="K1462" t="inlineStr">
         <is>
-          <t>Hannsi Virupaksh Shivabhat</t>
+          <t>Hannsi Virupaksha Shivabhat</t>
         </is>
       </c>
       <c r="L1462" t="inlineStr">
@@ -80810,7 +80810,7 @@
       </c>
       <c r="K1466" t="inlineStr">
         <is>
-          <t>Vach Vagh Baavant</t>
+          <t>Vach Vagha Baavanta</t>
         </is>
       </c>
     </row>
@@ -80862,12 +80862,12 @@
       </c>
       <c r="K1467" t="inlineStr">
         <is>
-          <t>Vagh Sunita Bhairinath</t>
+          <t>Vagha Sunita Bhairinatha</t>
         </is>
       </c>
       <c r="L1467" t="inlineStr">
         <is>
-          <t>Vagh Bhairinath</t>
+          <t>Vagha Bhairinatha</t>
         </is>
       </c>
     </row>
@@ -81199,7 +81199,7 @@
       </c>
       <c r="K1473" t="inlineStr">
         <is>
-          <t>Vainjakar Kashinath Viththal</t>
+          <t>Vainjakar Kashinatha Viththal</t>
         </is>
       </c>
       <c r="L1473" t="inlineStr">
@@ -81256,12 +81256,12 @@
       </c>
       <c r="K1474" t="inlineStr">
         <is>
-          <t>Vainjakar Smita Kashinath</t>
+          <t>Vainjakar Smita Kashinatha</t>
         </is>
       </c>
       <c r="L1474" t="inlineStr">
         <is>
-          <t>Vainjakar Kashinath</t>
+          <t>Vainjakar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -81313,12 +81313,12 @@
       </c>
       <c r="K1475" t="inlineStr">
         <is>
-          <t>Varaujakar Krushnakant Kashinath</t>
+          <t>Varaujakar Krushnakanta Kashinatha</t>
         </is>
       </c>
       <c r="L1475" t="inlineStr">
         <is>
-          <t>Varijakar Kashinath</t>
+          <t>Varijakar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -81370,12 +81370,12 @@
       </c>
       <c r="K1476" t="inlineStr">
         <is>
-          <t>Vaijakar Bharat Kashinath</t>
+          <t>Vaijakar Bharat Kashinatha</t>
         </is>
       </c>
       <c r="L1476" t="inlineStr">
         <is>
-          <t>Varijakar Kashinath</t>
+          <t>Varijakar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -81417,7 +81417,7 @@
       </c>
       <c r="K1477" t="inlineStr">
         <is>
-          <t>Krushnakant Vainjakar Kashinath</t>
+          <t>Krushnakanta Vainjakar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -81459,7 +81459,7 @@
       </c>
       <c r="K1478" t="inlineStr">
         <is>
-          <t>Bharat Vaijakar Kashinath</t>
+          <t>Bharat Vaijakar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -81511,12 +81511,12 @@
       </c>
       <c r="K1479" t="inlineStr">
         <is>
-          <t>Kae Ashok Harishchandr</t>
+          <t>Kae Ashok Harishchandra</t>
         </is>
       </c>
       <c r="L1479" t="inlineStr">
         <is>
-          <t>Kae Harishchandr</t>
+          <t>Kae Harishchandra</t>
         </is>
       </c>
     </row>
@@ -81739,7 +81739,7 @@
       </c>
       <c r="K1483" t="inlineStr">
         <is>
-          <t>Kumbhar Chaya Govind</t>
+          <t>Kumbhar Chaya Govinda</t>
         </is>
       </c>
       <c r="L1483" t="inlineStr">
@@ -81853,12 +81853,12 @@
       </c>
       <c r="K1485" t="inlineStr">
         <is>
-          <t>Kumbhar Pradip Govind</t>
+          <t>Kumbhar Pradip Govinda</t>
         </is>
       </c>
       <c r="L1485" t="inlineStr">
         <is>
-          <t>Kumbhar Govind</t>
+          <t>Kumbhar Govinda</t>
         </is>
       </c>
     </row>
@@ -82024,7 +82024,7 @@
       </c>
       <c r="K1488" t="inlineStr">
         <is>
-          <t>Bhalerav Dasharath Nana</t>
+          <t>Bhalerav Dasharatha Nana</t>
         </is>
       </c>
       <c r="L1488" t="inlineStr">
@@ -82081,12 +82081,12 @@
       </c>
       <c r="K1489" t="inlineStr">
         <is>
-          <t>Bhalerav Gayabai Dasharath</t>
+          <t>Bhalerav Gayabai Dasharatha</t>
         </is>
       </c>
       <c r="L1489" t="inlineStr">
         <is>
-          <t>Bhalerav Dasharath</t>
+          <t>Bhalerav Dasharatha</t>
         </is>
       </c>
     </row>
@@ -82133,7 +82133,7 @@
       </c>
       <c r="K1490" t="inlineStr">
         <is>
-          <t>Vab Bhalerav Dasharath</t>
+          <t>Vab Bhalerav Dasharatha</t>
         </is>
       </c>
     </row>
@@ -82175,7 +82175,7 @@
       </c>
       <c r="K1491" t="inlineStr">
         <is>
-          <t>Dinesh Bhalerav Dasharath</t>
+          <t>Dinesh Bhalerav Dasharatha</t>
         </is>
       </c>
     </row>
@@ -82227,12 +82227,12 @@
       </c>
       <c r="K1492" t="inlineStr">
         <is>
-          <t>Bhalerav Santosh Dasharath</t>
+          <t>Bhalerav Santosh Dasharatha</t>
         </is>
       </c>
       <c r="L1492" t="inlineStr">
         <is>
-          <t>Bhalerav Dasharath</t>
+          <t>Bhalerav Dasharatha</t>
         </is>
       </c>
     </row>
@@ -82522,12 +82522,12 @@
       </c>
       <c r="K1497" t="inlineStr">
         <is>
-          <t>Janavalekar Kashinath Pandurang</t>
+          <t>Janavalekar Kashinatha Panduranga</t>
         </is>
       </c>
       <c r="L1497" t="inlineStr">
         <is>
-          <t>Janavalekar Pandurang</t>
+          <t>Janavalekar Panduranga</t>
         </is>
       </c>
     </row>
@@ -82579,12 +82579,12 @@
       </c>
       <c r="K1498" t="inlineStr">
         <is>
-          <t>Janavalekar Kanta Kashinath</t>
+          <t>Janavalekar Kanta Kashinatha</t>
         </is>
       </c>
       <c r="L1498" t="inlineStr">
         <is>
-          <t>Janavalekar Kashinath</t>
+          <t>Janavalekar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -82636,12 +82636,12 @@
       </c>
       <c r="K1499" t="inlineStr">
         <is>
-          <t>Janavalekar Kishor Kashinath</t>
+          <t>Janavalekar Kishor Kashinatha</t>
         </is>
       </c>
       <c r="L1499" t="inlineStr">
         <is>
-          <t>Janavalekar Kashinath</t>
+          <t>Janavalekar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -82683,7 +82683,7 @@
       </c>
       <c r="K1500" t="inlineStr">
         <is>
-          <t>Kishor Janavalekar Kashinath</t>
+          <t>Kishor Janavalekar Kashinatha</t>
         </is>
       </c>
     </row>
@@ -83323,7 +83323,7 @@
       </c>
       <c r="K1513" t="inlineStr">
         <is>
-          <t>Satam Suryakant Shankar</t>
+          <t>Satam Suryakanta Shankar</t>
         </is>
       </c>
       <c r="L1513" t="inlineStr">
@@ -83385,12 +83385,12 @@
       </c>
       <c r="K1514" t="inlineStr">
         <is>
-          <t>Satam Suvarnalata Suryakant</t>
+          <t>Satam Suvarnalata Suryakanta</t>
         </is>
       </c>
       <c r="L1514" t="inlineStr">
         <is>
-          <t>Satam Suryakant</t>
+          <t>Satam Suryakanta</t>
         </is>
       </c>
     </row>
@@ -83447,7 +83447,7 @@
       </c>
       <c r="K1515" t="inlineStr">
         <is>
-          <t>Satam Hemant Suryakant</t>
+          <t>Satam Hemanta Suryakanta</t>
         </is>
       </c>
       <c r="L1515" t="inlineStr">
@@ -83504,12 +83504,12 @@
       </c>
       <c r="K1516" t="inlineStr">
         <is>
-          <t>Satam Shrikant Suryakant</t>
+          <t>Satam Shrikanta Suryakanta</t>
         </is>
       </c>
       <c r="L1516" t="inlineStr">
         <is>
-          <t>Satam Suryakant</t>
+          <t>Satam Suryakanta</t>
         </is>
       </c>
     </row>
@@ -83561,12 +83561,12 @@
       </c>
       <c r="K1517" t="inlineStr">
         <is>
-          <t>Shirke Pratap Ramachandr</t>
+          <t>Shirke Pratap Ramachandra</t>
         </is>
       </c>
       <c r="L1517" t="inlineStr">
         <is>
-          <t>Shirke Ramachandr</t>
+          <t>Shirke Ramachandra</t>
         </is>
       </c>
     </row>
@@ -83913,7 +83913,7 @@
       </c>
       <c r="K1523" t="inlineStr">
         <is>
-          <t>Banjari Shrimant Keru</t>
+          <t>Banjari Shrimanta Keru</t>
         </is>
       </c>
       <c r="L1523" t="inlineStr">
@@ -83970,12 +83970,12 @@
       </c>
       <c r="K1524" t="inlineStr">
         <is>
-          <t>Banjari Dhanashri Shrimant</t>
+          <t>Banjari Dhanashri Shrimanta</t>
         </is>
       </c>
       <c r="L1524" t="inlineStr">
         <is>
-          <t>Vanjari Shrimant</t>
+          <t>Vanjari Shrimanta</t>
         </is>
       </c>
     </row>
@@ -84017,7 +84017,7 @@
       </c>
       <c r="K1525" t="inlineStr">
         <is>
-          <t>Keru Banjari Shrimant</t>
+          <t>Keru Banjari Shrimanta</t>
         </is>
       </c>
     </row>
@@ -84282,7 +84282,7 @@
       </c>
       <c r="K1530" t="inlineStr">
         <is>
-          <t>Sonavane Varsha Chandukh</t>
+          <t>Sonavane Varsha Chandukha</t>
         </is>
       </c>
       <c r="L1530" t="inlineStr">
@@ -84396,12 +84396,12 @@
       </c>
       <c r="K1532" t="inlineStr">
         <is>
-          <t>Javakar Suresh Harishchandr</t>
+          <t>Javakar Suresh Harishchandra</t>
         </is>
       </c>
       <c r="L1532" t="inlineStr">
         <is>
-          <t>Javakar Harishchandr</t>
+          <t>Javakar Harishchandra</t>
         </is>
       </c>
     </row>
@@ -84510,12 +84510,12 @@
       </c>
       <c r="K1534" t="inlineStr">
         <is>
-          <t>Thakur Sunil Rupasing</t>
+          <t>Thakur Sunil Rupasinga</t>
         </is>
       </c>
       <c r="L1534" t="inlineStr">
         <is>
-          <t>Thakur Rupasing</t>
+          <t>Thakur Rupasinga</t>
         </is>
       </c>
     </row>
@@ -84914,12 +84914,12 @@
       </c>
       <c r="K1541" t="inlineStr">
         <is>
-          <t>Thakuradesai Sanjay Kashinath</t>
+          <t>Thakuradesai Sanjay Kashinatha</t>
         </is>
       </c>
       <c r="L1541" t="inlineStr">
         <is>
-          <t>Thakuradesai Kashinath</t>
+          <t>Thakuradesai Kashinatha</t>
         </is>
       </c>
     </row>
@@ -85028,12 +85028,12 @@
       </c>
       <c r="K1543" t="inlineStr">
         <is>
-          <t>Gavade Krushna Ramachandr</t>
+          <t>Gavade Krushna Ramachandra</t>
         </is>
       </c>
       <c r="L1543" t="inlineStr">
         <is>
-          <t>Gavade Ramachandr</t>
+          <t>Gavade Ramachandra</t>
         </is>
       </c>
     </row>
@@ -85147,12 +85147,12 @@
       </c>
       <c r="K1545" t="inlineStr">
         <is>
-          <t>Shekh Shariphauddin Basirauddin</t>
+          <t>Shekha Shariphauddin Basirauddin</t>
         </is>
       </c>
       <c r="L1545" t="inlineStr">
         <is>
-          <t>Shekh Basirauddin</t>
+          <t>Shekha Basirauddin</t>
         </is>
       </c>
     </row>
@@ -85209,12 +85209,12 @@
       </c>
       <c r="K1546" t="inlineStr">
         <is>
-          <t>Shekh Rajiya Shariph</t>
+          <t>Shekha Rajiya Sharipha</t>
         </is>
       </c>
       <c r="L1546" t="inlineStr">
         <is>
-          <t>Shekh Shariph</t>
+          <t>Shekha Sharipha</t>
         </is>
       </c>
     </row>
@@ -85266,12 +85266,12 @@
       </c>
       <c r="K1547" t="inlineStr">
         <is>
-          <t>Shekh Rahena Shariph</t>
+          <t>Shekha Rahena Sharipha</t>
         </is>
       </c>
       <c r="L1547" t="inlineStr">
         <is>
-          <t>Shekh Shariph</t>
+          <t>Shekha Sharipha</t>
         </is>
       </c>
     </row>
@@ -85323,12 +85323,12 @@
       </c>
       <c r="K1548" t="inlineStr">
         <is>
-          <t>Shekh Sulatana Shariph</t>
+          <t>Shekha Sulatana Sharipha</t>
         </is>
       </c>
       <c r="L1548" t="inlineStr">
         <is>
-          <t>Shekh Shariph</t>
+          <t>Shekha Sharipha</t>
         </is>
       </c>
     </row>
@@ -85366,7 +85366,7 @@
       </c>
       <c r="K1550" t="inlineStr">
         <is>
-          <t>Samavisht</t>
+          <t>Samavishta</t>
         </is>
       </c>
     </row>

--- a/output/EN_combined_output.xlsx
+++ b/output/EN_combined_output.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kasare Mukunda Tukaram</t>
+          <t>Kasare Mukund Tukaram</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kasare Madhuri Mukunda</t>
+          <t>Kasare Madhuri Mukund</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kasare Mukunda</t>
+          <t>Kasare Mukund</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Savadekar Tanaji Lakshman</t>
+          <t>Savadekar Tanaji Lakshmana</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Savadekar Lakshman</t>
+          <t>Savadekar Lakshmana</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Pulak Lakshman Kanakappa</t>
+          <t>Pulak Lakshmana Kanakappa</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pulak Polamma Lakshman</t>
+          <t>Pulak Polamma Lakshmana</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Pulak Lakshman</t>
+          <t>Pulak Lakshmana</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Vab Pulak Lakshman</t>
+          <t>Vab Pulak Lakshmana</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pulak Suresh Lakshman</t>
+          <t>Pulak Suresh Lakshmana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Pulak Lakshman</t>
+          <t>Pulak Lakshmana</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Allam Sanju Anamatta</t>
+          <t>Allama Sanju Anamatta</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Allam Anamatta</t>
+          <t>Allama Anamatta</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Khan Anvar Hasan</t>
+          <t>Khan Anvara Hasan</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Das Stivan Jojapha</t>
+          <t>Das Stivan Jojaph</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Das Jojapha</t>
+          <t>Das Jojaph</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Jadhav Lila Govinda</t>
+          <t>Jadhav Lila Govind</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Jadhav Nisha Govinda</t>
+          <t>Jadhav Nisha Govind</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Jadhav Gobinda</t>
+          <t>Jadhav Gobind</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Jadhav Anuradha Govinda</t>
+          <t>Jadhav Anuradha Govind</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Jadhav Gobinda</t>
+          <t>Jadhav Gobind</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Bangera Hemanta Ramesh</t>
+          <t>Bangera Hemant Ramesh</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Uttekar Anita Ananta</t>
+          <t>Uttekar Anita Anant</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Uttekar Ananta</t>
+          <t>Uttekar Anant</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Lakshman Lakshman Ananta</t>
+          <t>Lakshmana Lakshmana Anant</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Menyuel Vilsenta Ennthoni</t>
+          <t>Menyuel Vilsent Ennthoni</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Menyuel Vhiktar Enthoni</t>
+          <t>Menyuel Vhiktara Enthoni</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Menyuel Ai~Nthoni</t>
+          <t>Menyuel Ainnthoni</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Menyuel Vilyam Ainnthoni</t>
+          <t>Menyuel Vilyama Ainnthoni</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Mulukha Prakash Ramachandra</t>
+          <t>Mulukh Prakash Ramachandra</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Mulukha Ramachandra</t>
+          <t>Mulukh Ramachandra</t>
         </is>
       </c>
     </row>
@@ -4117,12 +4117,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Mulukha Pramila Prakash</t>
+          <t>Mulukh Pramila Prakash</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Mulukha Prakash</t>
+          <t>Mulukh Prakash</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Nayar Gopinatha Karunakaran</t>
+          <t>Nayar Gopinath Karunakaran</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Nayar Usha Gopinatha</t>
+          <t>Nayar Usha Gopinath</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Nayar Gopinatha</t>
+          <t>Nayar Gopinath</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pharnadis Jojepha Jon</t>
+          <t>Pharnadis Jojeph Jon</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pharnadis Phlori Jojepha</t>
+          <t>Pharnadis Phlori Jojeph</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Pharnadis Jojepha</t>
+          <t>Pharnadis Jojeph</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pharnadis Jansita Jojepha</t>
+          <t>Pharnadis Jansita Jojeph</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Pharnadis Jojepha</t>
+          <t>Pharnadis Jojeph</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Disoja Ba~Latar Inas</t>
+          <t>Disoja Banlatar Inas</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Disoja E~Ni Bolatar</t>
+          <t>Disoja Enni Bolatar</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Disoja Va~Latar</t>
+          <t>Disoja Vanlatar</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Jadhav Govinda Rajaram</t>
+          <t>Jadhav Govind Rajaram</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Jadhav Kamal Govinda</t>
+          <t>Jadhav Kamal Govind</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Jadhav Govinda</t>
+          <t>Jadhav Govind</t>
         </is>
       </c>
     </row>
@@ -5002,12 +5002,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Si-102 Kuttan Ke.Nanu</t>
+          <t>Si-102 Kuttana Ke.Nanu</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Kuttan Ke.Nanu</t>
+          <t>Kuttana Ke.Nanu</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Kuttan Vasanda K.</t>
+          <t>Kuttana Vasanda K.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Kuttan K.</t>
+          <t>Kuttana K.</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Kuttan Nanu</t>
+          <t>Kuttana Nanu</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Kuttan Sanjivakumar K.</t>
+          <t>Kuttana Sanjivakumar K.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Kuttan K.</t>
+          <t>Kuttana K.</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Vab Sinha Rayabahadur</t>
+          <t>Vab Sinh Rayabahadur</t>
         </is>
       </c>
     </row>
@@ -6499,12 +6499,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Sinha Shobha Kamalesh</t>
+          <t>Sinh Shobha Kamalesh</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Sinha Kamalesh</t>
+          <t>Sinh Kamalesh</t>
         </is>
       </c>
     </row>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Imyenyuel Sa~Rophin Donal</t>
+          <t>Imyenyuel Sanrophin Donal</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Vab Singa Sitaram</t>
+          <t>Vab Sing Sitaram</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Singa Satyavati Shrabanakuma</t>
+          <t>Sing Satyavati Shrabanakuma</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Singa Shravanakumar</t>
+          <t>Sing Shravanakumar</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Shravanakumar Singa Shravanakumar</t>
+          <t>Shravanakumar Sing Shravanakumar</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Singa Radhesham Sitaram</t>
+          <t>Sing Radhesham Sitaram</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Singa Sitaram</t>
+          <t>Sing Sitaram</t>
         </is>
       </c>
     </row>
@@ -7586,12 +7586,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Vagae Mangesh Jagannatha</t>
+          <t>Vagae Mangesh Jagannath</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Vagae Jagannatha</t>
+          <t>Vagae Jagannath</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Vagae Jagannatha Mangesh</t>
+          <t>Vagae Jagannath Mangesh</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Shinde Chandrakanta Ananta</t>
+          <t>Shinde Chandrakant Anant</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Shinde Ananta</t>
+          <t>Shinde Anant</t>
         </is>
       </c>
     </row>
@@ -8209,12 +8209,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Shinde Rohini Chandrakanta</t>
+          <t>Shinde Rohini Chandrakant</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Shinde Chandrakanta</t>
+          <t>Shinde Chandrakant</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Shinde Nitin Chandrakanta</t>
+          <t>Shinde Nitin Chandrakant</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Shinde Chandrakanta</t>
+          <t>Shinde Chandrakant</t>
         </is>
       </c>
     </row>
@@ -8323,12 +8323,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Shinde Nilesh Chandrakanta</t>
+          <t>Shinde Nilesh Chandrakant</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Shinde Chandrakanta</t>
+          <t>Shinde Chandrakant</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Riphai Aphatab Sayyad</t>
+          <t>Riphai Aphatab Sayyada</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Riphai Sayyad</t>
+          <t>Riphai Sayyada</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Isupha Shekha Insupha</t>
+          <t>Isuph Shekh Insuph</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Shekha Gajala Salim</t>
+          <t>Shekh Gajala Salim</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Shekha Salim</t>
+          <t>Shekh Salim</t>
         </is>
       </c>
     </row>
@@ -8816,12 +8816,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Shekha Minaj Salim</t>
+          <t>Shekh Minaj Salim</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Shekha Salim</t>
+          <t>Shekh Salim</t>
         </is>
       </c>
     </row>
@@ -8873,12 +8873,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Shekha Pharukha Salim</t>
+          <t>Shekh Pharukh Salim</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Shekha Salim</t>
+          <t>Shekh Salim</t>
         </is>
       </c>
     </row>
@@ -8930,12 +8930,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Shekha Abdul Navab</t>
+          <t>Shekh Abdul Navab</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Shekha Navab</t>
+          <t>Shekh Navab</t>
         </is>
       </c>
     </row>
@@ -8987,12 +8987,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Shekha Kamal Navab</t>
+          <t>Shekh Kamal Navab</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Shekha Navab</t>
+          <t>Shekh Navab</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Shekha Imbram Navab</t>
+          <t>Shekh Imbram Navab</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Shekha Navab</t>
+          <t>Shekh Navab</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Shekha Aphasha Navab</t>
+          <t>Shekh Aphasha Navab</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Shekha Navab</t>
+          <t>Shekh Navab</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9862,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Sakapa Prajakta Ramakanta</t>
+          <t>Sakapa Prajakta Ramakant</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Sakapa Ramakanta</t>
+          <t>Sakapa Ramakant</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Yadav Lalachanda Mangalaprasad</t>
+          <t>Yadav Lalachand Mangalaprasad</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Yadav Lalachanda</t>
+          <t>Yadav Lalachand</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Mastar Vhi Di</t>
+          <t>Mastara Vhi Di</t>
         </is>
       </c>
     </row>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Sri-103 Mastar Echa.Vhi.</t>
+          <t>Sri-103 Mastara Echa.Vhi.</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Mastar Echa.Vhi.</t>
+          <t>Mastara Echa.Vhi.</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Ayyar Subramanyam Narayan</t>
+          <t>Ayyara Subramanyama Narayan</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Ayyar Narayan</t>
+          <t>Ayyara Narayan</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Ayyar Maitili Subramanyam</t>
+          <t>Ayyara Maitili Subramanyama</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Ayyar Subramanyam</t>
+          <t>Ayyara Subramanyama</t>
         </is>
       </c>
     </row>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Ayyar Svati Subramanyam</t>
+          <t>Ayyara Svati Subramanyama</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Ayyar Subramanyam</t>
+          <t>Ayyara Subramanyama</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Dandekar Aravinda Gajanan</t>
+          <t>Dandekar Aravind Gajanan</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Dandekar Shila Aravinda</t>
+          <t>Dandekar Shila Aravind</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Dandekar Aravinda</t>
+          <t>Dandekar Aravind</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Acharya Aravinda</t>
+          <t>Acharya Aravind</t>
         </is>
       </c>
     </row>
@@ -11377,12 +11377,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>A-4 Bhalachandran Ke.Ji.</t>
+          <t>A-4 Bhalachandrana Ke.Ji.</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Bhalachandran Ke.Ji.</t>
+          <t>Bhalachandrana Ke.Ji.</t>
         </is>
       </c>
     </row>
@@ -11439,12 +11439,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Bhalachandran Sharada K.</t>
+          <t>Bhalachandrana Sharada K.</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Bhalachandran K.</t>
+          <t>Bhalachandrana K.</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Mahale Prashanta Dinakar</t>
+          <t>Mahale Prashant Dinakar</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Shinde Shashikanta Tukaram</t>
+          <t>Shinde Shashikant Tukaram</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Shinde Sangita Shishikanta</t>
+          <t>Shinde Sangita Shishikant</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>Shinde Shishikanta</t>
+          <t>Shinde Shishikant</t>
         </is>
       </c>
     </row>
@@ -12346,12 +12346,12 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Parekar Sharad Yashavanta</t>
+          <t>Parekar Sharad Yashavant</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Parekar Yashavanta</t>
+          <t>Parekar Yashavant</t>
         </is>
       </c>
     </row>
@@ -12574,12 +12574,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Mejari Gajanan Yashavanta</t>
+          <t>Mejari Gajanan Yashavant</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Mejari Yashavanta</t>
+          <t>Mejari Yashavant</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Bhovad Ekanatha Sadashiv</t>
+          <t>Bhovad Ekanath Sadashiv</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -13097,12 +13097,12 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Bhovad Aruna Ekanatha</t>
+          <t>Bhovad Aruna Ekanath</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Bhovar Ekanatha</t>
+          <t>Bhovar Ekanath</t>
         </is>
       </c>
     </row>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Bhovad Rupali Ekanatha</t>
+          <t>Bhovad Rupali Ekanath</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Was Ekanatha</t>
+          <t>Was Ekanath</t>
         </is>
       </c>
     </row>
@@ -13211,12 +13211,12 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Bhovad Reshma Ekanatha</t>
+          <t>Bhovad Reshma Ekanath</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>Bhovad Ekanatha</t>
+          <t>Bhovad Ekanath</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Vab Sinha Rijabihari</t>
+          <t>Vab Sinh Rijabihari</t>
         </is>
       </c>
     </row>
@@ -13320,12 +13320,12 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Sinha Anjana Ramesh</t>
+          <t>Sinh Anjana Ramesh</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Sinha Ramesh</t>
+          <t>Sinh Ramesh</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Paudel Mohanasinha Tekanaray</t>
+          <t>Paudel Mohanasinh Tekanaray</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Paudel Parameshvar Tekanaray</t>
+          <t>Paudel Parameshvara Tekanaray</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -14057,12 +14057,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Tambe Shaila Vasanta</t>
+          <t>Tambe Shaila Vasant</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Tambe Vasanta</t>
+          <t>Tambe Vasant</t>
         </is>
       </c>
     </row>
@@ -14114,12 +14114,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Tambe Satish Vasanta</t>
+          <t>Tambe Satish Vasant</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Tambe Vasanta</t>
+          <t>Tambe Vasant</t>
         </is>
       </c>
     </row>
@@ -14228,12 +14228,12 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Tambe Ganesh Vasanta</t>
+          <t>Tambe Ganesh Vasant</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>Tambe Vasanta</t>
+          <t>Tambe Vasant</t>
         </is>
       </c>
     </row>
@@ -14285,12 +14285,12 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Tambe Ashish Vasanta</t>
+          <t>Tambe Ashish Vasant</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>Tambe Vasanta</t>
+          <t>Tambe Vasant</t>
         </is>
       </c>
     </row>
@@ -14342,12 +14342,12 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Tambe Umesh Vasanta</t>
+          <t>Tambe Umesh Vasant</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Tambe Vasanta</t>
+          <t>Tambe Vasant</t>
         </is>
       </c>
     </row>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Ghude Harshad Vijay</t>
+          <t>Ghude Harshada Vijay</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -14627,12 +14627,12 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Pavasakar Mahadev Viththal</t>
+          <t>Pavasakar Mahadev Viththala</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>Pavasakar Viththal</t>
+          <t>Pavasakar Viththala</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Pavar Kashinatha Ratan</t>
+          <t>Pavar Kashinath Ratan</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Pavar Darshana Kashinatha</t>
+          <t>Pavar Darshana Kashinath</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>Pavar Kashinatha</t>
+          <t>Pavar Kashinath</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Mhatre Kiran Moreshvar</t>
+          <t>Mhatre Kiran Moreshvara</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>Mhatre Moreshvar</t>
+          <t>Mhatre Moreshvara</t>
         </is>
       </c>
     </row>
@@ -15415,12 +15415,12 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Shekha Salama Rasid</t>
+          <t>Shekh Salama Rasid</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>Shekha Rasid</t>
+          <t>Shekh Rasid</t>
         </is>
       </c>
     </row>
@@ -15477,12 +15477,12 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Shekha Rasid Abdul</t>
+          <t>Shekh Rasid Abdul</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>Shekha Abdul</t>
+          <t>Shekh Abdul</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Vach Shekha Rasid</t>
+          <t>Vach Shekh Rasid</t>
         </is>
       </c>
     </row>
@@ -15576,12 +15576,12 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Shekha Shakola Rasid</t>
+          <t>Shekh Shakola Rasid</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Shekha Rasid</t>
+          <t>Shekh Rasid</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Vishvas Nishikanta Nilod</t>
+          <t>Vishvas Nishikant Nilod</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Shah Jayashri Hemanta Pa Shah Hemanta Satri</t>
+          <t>Shah Jayashri Hemant Pa Shah Hemant Satri</t>
         </is>
       </c>
     </row>
@@ -16273,12 +16273,12 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Savanta Shridhar Yashavanta</t>
+          <t>Savant Shridhar Yashavant</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Savanta Yashavanta</t>
+          <t>Savant Yashavant</t>
         </is>
       </c>
     </row>
@@ -16335,12 +16335,12 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Savanta Sangita Shridhar</t>
+          <t>Savant Sangita Shridhar</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>Savanta Shridhar</t>
+          <t>Savant Shridhar</t>
         </is>
       </c>
     </row>
@@ -16630,12 +16630,12 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Pandit Dipak Raghunatha</t>
+          <t>Pandit Dipak Raghunath</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>Pandit Raghunatha</t>
+          <t>Pandit Raghunath</t>
         </is>
       </c>
     </row>
@@ -17153,12 +17153,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Pille Radhakrushnan Vishvanatha</t>
+          <t>Pille Radhakrushnana Vishvanath</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>Pille Vishvanatha</t>
+          <t>Pille Vishvanath</t>
         </is>
       </c>
     </row>
@@ -17210,12 +17210,12 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Pille Bhoneshchari Radhakrushnam</t>
+          <t>Pille Bhoneshchari Radhakrushnama</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>Pille Radhakrushnam</t>
+          <t>Pille Radhakrushnama</t>
         </is>
       </c>
     </row>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>P. Unnikrushnan Tintu</t>
+          <t>P. Unnikrushnana Tintu</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -17334,12 +17334,12 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>P. Umadevi Unnikrushnan</t>
+          <t>P. Umadevi Unnikrushnana</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>P. Unnikrushnan</t>
+          <t>P. Unnikrushnana</t>
         </is>
       </c>
     </row>
@@ -17847,7 +17847,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Pillai Ramakrushnan S.</t>
+          <t>Pillai Ramakrushnana S.</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Murudakar Shashikanta Dhurani</t>
+          <t>Murudakar Shashikant Dhurani</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Murudakar Smita Shashikanta</t>
+          <t>Murudakar Smita Shashikant</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>Murudakar Shashikanta</t>
+          <t>Murudakar Shashikant</t>
         </is>
       </c>
     </row>
@@ -18147,12 +18147,12 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Suryavanshi Kamalakar Jagannatha</t>
+          <t>Suryavanshi Kamalakar Jagannath</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Suryavanshi Jagannatha</t>
+          <t>Suryavanshi Jagannath</t>
         </is>
       </c>
     </row>
@@ -18204,12 +18204,12 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Suryavanshi Shakuntala Jagannatha</t>
+          <t>Suryavanshi Shakuntala Jagannath</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>Suryavanshi Jagannatha</t>
+          <t>Suryavanshi Jagannath</t>
         </is>
       </c>
     </row>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Suryavanshi Jagannatha Sonu</t>
+          <t>Suryavanshi Jagannath Sonu</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -18380,12 +18380,12 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Datar Urmila Lakshman</t>
+          <t>Datar Urmila Lakshmana</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>Datar Lakshman</t>
+          <t>Datar Lakshmana</t>
         </is>
       </c>
     </row>
@@ -18556,12 +18556,12 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Joshi P. Kashinatha</t>
+          <t>Joshi P. Kashinath</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>Joshi Kashinatha</t>
+          <t>Joshi Kashinath</t>
         </is>
       </c>
     </row>
@@ -18718,12 +18718,12 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Bangala Ramababu Narasinha</t>
+          <t>Bangala Ramababu Narasinh</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>Bangala Narasinha</t>
+          <t>Bangala Narasinh</t>
         </is>
       </c>
     </row>
@@ -18817,7 +18817,7 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Kudapakar Vishvanatha Budhaji</t>
+          <t>Kudapakar Vishvanath Budhaji</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -18874,12 +18874,12 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Kudapakar Rushali Vishvanatha</t>
+          <t>Kudapakar Rushali Vishvanath</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>Kurapakar Vishvanatha</t>
+          <t>Kurapakar Vishvanath</t>
         </is>
       </c>
     </row>
@@ -18931,12 +18931,12 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Dige Kashiram Lakshman</t>
+          <t>Dige Kashiram Lakshmana</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>Fet Lakshman</t>
+          <t>Fet Lakshmana</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Dige Ananta Kashiram</t>
+          <t>Dige Anant Kashiram</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -19102,12 +19102,12 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Dige Vedabati Ananta</t>
+          <t>Dige Vedabati Anant</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Fet Ananta</t>
+          <t>Fet Anant</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Ghodase Shashikanta Gangaram</t>
+          <t>Ghodase Shashikant Gangaram</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -19216,12 +19216,12 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Ghorase Smita Shashikanta</t>
+          <t>Ghorase Smita Shashikant</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Ghodase Shashikanta</t>
+          <t>Ghodase Shashikant</t>
         </is>
       </c>
     </row>
@@ -19620,12 +19620,12 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Shekha Mahamad Raphok</t>
+          <t>Shekh Mahamad Raphok</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>Shekha Raphok</t>
+          <t>Shekh Raphok</t>
         </is>
       </c>
     </row>
@@ -19677,12 +19677,12 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Shekha Najama Mahamad</t>
+          <t>Shekh Najama Mahamad</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>Shekha Mahamad</t>
+          <t>Shekh Mahamad</t>
         </is>
       </c>
     </row>
@@ -19734,12 +19734,12 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Mahamanda Abu Bakkar</t>
+          <t>Mahamand Abu Bakkara</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>Mahamad Bakkar</t>
+          <t>Mahamad Bakkara</t>
         </is>
       </c>
     </row>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Mahamanda Sabira Abu</t>
+          <t>Mahamand Sabira Abu</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Mahamanda Ayesh Abu</t>
+          <t>Mahamand Ayesh Abu</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Mahamanda Pharida Abu</t>
+          <t>Mahamand Pharida Abu</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -20081,12 +20081,12 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Khan Husenadas Mohammad</t>
+          <t>Khan Husenadas Mohammada</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>Khan Mohammad</t>
+          <t>Khan Mohammada</t>
         </is>
       </c>
     </row>
@@ -20599,12 +20599,12 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Shekha Yusaupha Ahamad</t>
+          <t>Shekh Yusauph Ahamad</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -20656,12 +20656,12 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Shekha Amina Yusipha</t>
+          <t>Shekh Amina Yusiph</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>Shekha Yusipha</t>
+          <t>Shekh Yusiph</t>
         </is>
       </c>
     </row>
@@ -21055,12 +21055,12 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Shekha Abjal Jako</t>
+          <t>Shekh Abjala Jako</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>Shekha Jako</t>
+          <t>Shekh Jako</t>
         </is>
       </c>
     </row>
@@ -21112,12 +21112,12 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Shekha Shahanajha Abjal</t>
+          <t>Shekh Shahanajh Abjala</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>Shekha Abjal</t>
+          <t>Shekh Abjala</t>
         </is>
       </c>
     </row>
@@ -21169,12 +21169,12 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Shekha Ahamad Muhiudadadim</t>
+          <t>Shekh Ahamad Muhiudadadim</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>Shekha Muhiudadadim</t>
+          <t>Shekh Muhiudadadim</t>
         </is>
       </c>
     </row>
@@ -21226,12 +21226,12 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Shekha Raphoya Ahamad</t>
+          <t>Shekh Raphoya Ahamad</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -21284,12 +21284,12 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Shekha Sohel Ahamad</t>
+          <t>Shekh Sohel Ahamad</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Shekha Akhil Ahamad</t>
+          <t>Shekh Akhil Ahamad</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -21398,12 +21398,12 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Shekha Rahil Ahamad</t>
+          <t>Shekh Rahil Ahamad</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -21455,12 +21455,12 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Shekha Sadahiya Ahamad</t>
+          <t>Shekh Sadahiya Ahamad</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -21512,12 +21512,12 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Shekha Sana Sohel</t>
+          <t>Shekh Sana Sohel</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -21569,12 +21569,12 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Singa Harapal Joli</t>
+          <t>Sing Harapal Joli</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>Singa Joli</t>
+          <t>Sing Joli</t>
         </is>
       </c>
     </row>
@@ -21626,12 +21626,12 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Singa Yasamin Joli</t>
+          <t>Sing Yasamin Joli</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>Singa Joli</t>
+          <t>Sing Joli</t>
         </is>
       </c>
     </row>
@@ -21683,12 +21683,12 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Shekha Cha~D Jaiyanudin</t>
+          <t>Shekh Chand Jaiyanudin</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>Shekha Jaiyanudin</t>
+          <t>Shekh Jaiyanudin</t>
         </is>
       </c>
     </row>
@@ -21740,12 +21740,12 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Ajij Bi Chanda</t>
+          <t>Ajij Bi Chand</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>Shekha Bi Chanda</t>
+          <t>Shekh Bi Chand</t>
         </is>
       </c>
     </row>
@@ -21797,12 +21797,12 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Shekha Shakola Cha~D</t>
+          <t>Shekh Shakola Chand</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>Epha22 Chanda</t>
+          <t>Epha22 Chand</t>
         </is>
       </c>
     </row>
@@ -21854,12 +21854,12 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Shekha Aphoja Cha~D</t>
+          <t>Shekh Aphoja Chand</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>Shekha Chanda</t>
+          <t>Shekh Chand</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21916,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>Shekha Masuma Yakub</t>
+          <t>Shekh Masuma Yakub</t>
         </is>
       </c>
     </row>
@@ -21958,7 +21958,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Vab Shekha Badashaha</t>
+          <t>Vab Shekh Badashaha</t>
         </is>
       </c>
     </row>
@@ -22010,12 +22010,12 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Shekha Gulam Badashah</t>
+          <t>Shekh Gulam Badashah</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>Shekha Badashah</t>
+          <t>Shekh Badashah</t>
         </is>
       </c>
     </row>
@@ -22067,12 +22067,12 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Shekha Rahima Mahamad</t>
+          <t>Shekh Rahima Mahamad</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>Shekha Mahamad</t>
+          <t>Shekh Mahamad</t>
         </is>
       </c>
     </row>
@@ -22124,12 +22124,12 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Shekha Matin Mahamad</t>
+          <t>Shekh Matin Mahamad</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>Shekha Mahamad</t>
+          <t>Shekh Mahamad</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Shekha Jamil Mahamad</t>
+          <t>Shekh Jamil Mahamad</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>Shekha Mahamad</t>
+          <t>Shekh Mahamad</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Shekha Pharida Jamil Pa Shekha Jamil Satri</t>
+          <t>Shekh Pharida Jamil Pa Shekh Jamil Satri</t>
         </is>
       </c>
     </row>
@@ -22275,12 +22275,12 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Shekha Paravesh Jamil</t>
+          <t>Shekh Paravesh Jamil</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>Shekha Jamil</t>
+          <t>Shekh Jamil</t>
         </is>
       </c>
     </row>
@@ -22446,12 +22446,12 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>Sayyad Manasuraali Kurban</t>
+          <t>Sayyada Manasuraali Kurban</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>Sayyad Kurban</t>
+          <t>Sayyada Kurban</t>
         </is>
       </c>
     </row>
@@ -22508,7 +22508,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>Sayyad Manasuraali</t>
+          <t>Sayyada Manasuraali</t>
         </is>
       </c>
     </row>
@@ -22560,12 +22560,12 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Sayyad Asipha Manasuraali</t>
+          <t>Sayyada Asiph Manasuraali</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>Sayyad Manasuraali</t>
+          <t>Sayyada Manasuraali</t>
         </is>
       </c>
     </row>
@@ -22617,12 +22617,12 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Sayyad Aripha Manasuraali</t>
+          <t>Sayyada Ariph Manasuraali</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>Sayyad Manasuraali</t>
+          <t>Sayyada Manasuraali</t>
         </is>
       </c>
     </row>
@@ -22674,12 +22674,12 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Shekha Mehamumabi Cha~D</t>
+          <t>Shekh Mehamumabi Chand</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>Epha$0 Cha~D</t>
+          <t>Epha$0 Chand</t>
         </is>
       </c>
     </row>
@@ -22731,12 +22731,12 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Shekha Vahadali Chanda</t>
+          <t>Shekh Vahadali Chand</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>Shekha Cha~D</t>
+          <t>Shekh Chand</t>
         </is>
       </c>
     </row>
@@ -22788,12 +22788,12 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Shekha Phatima Vahadali</t>
+          <t>Shekh Phatima Vahadali</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>Shekha Vahadali</t>
+          <t>Shekh Vahadali</t>
         </is>
       </c>
     </row>
@@ -22845,12 +22845,12 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Shekha Khalil Cha~D</t>
+          <t>Shekh Khalil Chand</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>Shekha Cha~D</t>
+          <t>Shekh Chand</t>
         </is>
       </c>
     </row>
@@ -22902,12 +22902,12 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Shekha Abeda Cha~D</t>
+          <t>Shekh Abeda Chand</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>Shekha Cha~D</t>
+          <t>Shekh Chand</t>
         </is>
       </c>
     </row>
@@ -23073,12 +23073,12 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Lambe Satakar Mohammad</t>
+          <t>Lambe Satakar Mohammada</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>Lambe Mohammad</t>
+          <t>Lambe Mohammada</t>
         </is>
       </c>
     </row>
@@ -23472,12 +23472,12 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Sayyaid Sumayya Pharukha</t>
+          <t>Sayyaid Sumayya Pharukh</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>Samayyaid Pharukha</t>
+          <t>Samayyaid Pharukh</t>
         </is>
       </c>
     </row>
@@ -23529,12 +23529,12 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Sayyaid Hajara Aripha</t>
+          <t>Sayyaid Hajara Ariph</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>Sayyaid Aripha</t>
+          <t>Sayyaid Ariph</t>
         </is>
       </c>
     </row>
@@ -23872,12 +23872,12 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Sayyad Sajid Ali</t>
+          <t>Sayyada Sajid Ali</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>Sayyad Ali</t>
+          <t>Sayyada Ali</t>
         </is>
       </c>
     </row>
@@ -23929,12 +23929,12 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Sayyad Khalida Sajid</t>
+          <t>Sayyada Khalida Sajid</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>Sayyad Sajid</t>
+          <t>Sayyada Sajid</t>
         </is>
       </c>
     </row>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Japhari Vakajha Avadil</t>
+          <t>Japhari Vakajh Avadil</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -24100,12 +24100,12 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>Shekha Anij Ahamad</t>
+          <t>Shekh Anij Ahamad</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>Shekha Ahamad</t>
+          <t>Shekh Ahamad</t>
         </is>
       </c>
     </row>
@@ -24162,7 +24162,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>Shekha B. Anij</t>
+          <t>Shekh B. Anij</t>
         </is>
       </c>
     </row>
@@ -24214,12 +24214,12 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Shekha Sohel Anij</t>
+          <t>Shekh Sohel Anij</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>Shekha Anij</t>
+          <t>Shekh Anij</t>
         </is>
       </c>
     </row>
@@ -24276,12 +24276,12 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Save Dilip Moreshvar</t>
+          <t>Save Dilip Moreshvara</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>Save Moreshvar</t>
+          <t>Save Moreshvara</t>
         </is>
       </c>
     </row>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Karakera Radhakrushnam</t>
+          <t>Karakera Radhakrushnama</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -25426,12 +25426,12 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Karakera Kavita Radhakrushnam</t>
+          <t>Karakera Kavita Radhakrushnama</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>Karakera Radhakrushnam</t>
+          <t>Karakera Radhakrushnama</t>
         </is>
       </c>
     </row>
@@ -25540,12 +25540,12 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>Murudakar Vaibhav Yashavanta</t>
+          <t>Murudakar Vaibhav Yashavant</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>Murudakar Yashavanta</t>
+          <t>Murudakar Yashavant</t>
         </is>
       </c>
     </row>
@@ -25753,12 +25753,12 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>Paravej Aktar Gulam</t>
+          <t>Paravej Aktara Gulam</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>Sidhdiko Aktar Gulam</t>
+          <t>Sidhdiko Aktara Gulam</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Sidhdiko Aktar Gulam</t>
+          <t>Sidhdiko Aktara Gulam</t>
         </is>
       </c>
     </row>
@@ -25956,7 +25956,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>Sidhdiko Aktar Gulam</t>
+          <t>Sidhdiko Aktara Gulam</t>
         </is>
       </c>
     </row>
@@ -26008,12 +26008,12 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Shekha Musa Abdul</t>
+          <t>Shekh Musa Abdul</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>Shekha Abdul</t>
+          <t>Shekh Abdul</t>
         </is>
       </c>
     </row>
@@ -26065,12 +26065,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>Shekha Resama Musa</t>
+          <t>Shekh Resama Musa</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>Shekha Musa</t>
+          <t>Shekh Musa</t>
         </is>
       </c>
     </row>
@@ -26236,12 +26236,12 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>Kae Jayanta Moreshvar</t>
+          <t>Kae Jayant Moreshvara</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>Kae Moreshvar</t>
+          <t>Kae Moreshvara</t>
         </is>
       </c>
     </row>
@@ -26293,12 +26293,12 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>Kae Jayashri Jayanta</t>
+          <t>Kae Jayashri Jayant</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>Kae Jayanta</t>
+          <t>Kae Jayant</t>
         </is>
       </c>
     </row>
@@ -26579,7 +26579,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>Shelar Chandrakanta Dhondu</t>
+          <t>Shelar Chandrakant Dhondu</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -26636,12 +26636,12 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>Shelar Suchitra Chandrakanta</t>
+          <t>Shelar Suchitra Chandrakant</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>Shelar Chandrakanta</t>
+          <t>Shelar Chandrakant</t>
         </is>
       </c>
     </row>
@@ -27149,12 +27149,12 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>Majalakar Shashikanta</t>
+          <t>Majalakar Shashikant</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>Majalakar Shashikanta</t>
+          <t>Majalakar Shashikant</t>
         </is>
       </c>
     </row>
@@ -27206,12 +27206,12 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Majalakar Shalaka Shashikanta</t>
+          <t>Majalakar Shalaka Shashikant</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>Majalakar Shashikanta</t>
+          <t>Majalakar Shashikant</t>
         </is>
       </c>
     </row>
@@ -27533,7 +27533,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>Jadhav Vasanta Ganapat</t>
+          <t>Jadhav Vasant Ganapat</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -27590,12 +27590,12 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>Jadhav Vaishali Vasanta</t>
+          <t>Jadhav Vaishali Vasant</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>Jadhav Vasanta</t>
+          <t>Jadhav Vasant</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Gala Nalinda Amrutalal</t>
+          <t>Gala Nalind Amrutalal</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -27818,12 +27818,12 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Gala Nisa Nalinda</t>
+          <t>Gala Nisa Nalind</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>Gala Nalinda</t>
+          <t>Gala Nalind</t>
         </is>
       </c>
     </row>
@@ -28430,12 +28430,12 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>More Suryakanta Moreshcha</t>
+          <t>More Suryakant Moreshcha</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>More Moreshvar</t>
+          <t>More Moreshvara</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>More Suryakanta</t>
+          <t>More Suryakant</t>
         </is>
       </c>
     </row>
@@ -28881,7 +28881,7 @@
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>Haidar Mohommad Nasim</t>
+          <t>Haidar Mohommada Nasim</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>Haidar Paravin Mohammad</t>
+          <t>Haidar Paravin Mohammada</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>Haidar Mohammad</t>
+          <t>Haidar Mohammada</t>
         </is>
       </c>
     </row>
@@ -28995,12 +28995,12 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Shekha Abdul Shakur</t>
+          <t>Shekh Abdul Shakur</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>Shekha Shakur</t>
+          <t>Shekh Shakur</t>
         </is>
       </c>
     </row>
@@ -29053,12 +29053,12 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Shekha Phaijun Nisa</t>
+          <t>Shekh Phaijun Nisa</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>Shekha Nisa</t>
+          <t>Shekh Nisa</t>
         </is>
       </c>
     </row>
@@ -29110,12 +29110,12 @@
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Shekha Juned Abdul</t>
+          <t>Shekh Juned Abdul</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>Shekha Abdul</t>
+          <t>Shekh Abdul</t>
         </is>
       </c>
     </row>
@@ -29167,12 +29167,12 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Shekha Nikhad Hasad</t>
+          <t>Shekh Nikhad Hasad</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>Shekha Hasad</t>
+          <t>Shekh Hasad</t>
         </is>
       </c>
     </row>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Pavar Bajaranga Keshav</t>
+          <t>Pavar Bajarang Keshav</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -29519,12 +29519,12 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Pavar Ulka Bajaranga</t>
+          <t>Pavar Ulka Bajarang</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>Pavar Bajaranga</t>
+          <t>Pavar Bajarang</t>
         </is>
       </c>
     </row>
@@ -29576,12 +29576,12 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Shekha Najim Abdul</t>
+          <t>Shekh Najim Abdul</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>Shekha Abdul</t>
+          <t>Shekh Abdul</t>
         </is>
       </c>
     </row>
@@ -29633,12 +29633,12 @@
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>Shekha Shahanajha Najim</t>
+          <t>Shekh Shahanajh Najim</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>Shekha Abdul</t>
+          <t>Shekh Abdul</t>
         </is>
       </c>
     </row>
@@ -29690,12 +29690,12 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>Shekha Imaran Najim</t>
+          <t>Shekh Imaran Najim</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>Shekha Najim</t>
+          <t>Shekh Najim</t>
         </is>
       </c>
     </row>
@@ -29747,12 +29747,12 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Sisodiya Ramasvarup Bhavarasinha</t>
+          <t>Sisodiya Ramasvarup Bhavarasinh</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>Sisodiya Bhavarasinha</t>
+          <t>Sisodiya Bhavarasinh</t>
         </is>
       </c>
     </row>
@@ -29940,12 +29940,12 @@
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Rajaram Panduranga</t>
+          <t>Rajaram Pandurang</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>Hegishte Panduranga</t>
+          <t>Hegishte Pandurang</t>
         </is>
       </c>
     </row>
@@ -30339,7 +30339,7 @@
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Dhamapurakar Chandrakanta Krushna</t>
+          <t>Dhamapurakar Chandrakant Krushna</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -30401,12 +30401,12 @@
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>Dhamapurakar Chitra Chandrakanta</t>
+          <t>Dhamapurakar Chitra Chandrakant</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>Dhamapurakar Chandrakanta</t>
+          <t>Dhamapurakar Chandrakant</t>
         </is>
       </c>
     </row>
@@ -30696,12 +30696,12 @@
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>Kulakani Mahadev Raghunatha</t>
+          <t>Kulakani Mahadev Raghunath</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>Kulakarni Raghunatha</t>
+          <t>Kulakarni Raghunath</t>
         </is>
       </c>
     </row>
@@ -31209,12 +31209,12 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Hemadi Rama Hemanta</t>
+          <t>Hemadi Rama Hemant</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>Hemadi Hemanta</t>
+          <t>Hemadi Hemant</t>
         </is>
       </c>
     </row>
@@ -31266,7 +31266,7 @@
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>Mulla Mohammad Hasan</t>
+          <t>Mulla Mohammada Hasan</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
@@ -31323,12 +31323,12 @@
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>Mulla Rubina Mohammad</t>
+          <t>Mulla Rubina Mohammada</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>Mulla Mohammad</t>
+          <t>Mulla Mohammada</t>
         </is>
       </c>
     </row>
@@ -32640,7 +32640,7 @@
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>Bagarecha Sa~</t>
+          <t>Bagarecha San</t>
         </is>
       </c>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>Tambade Hemanta Dattaram</t>
+          <t>Tambade Hemant Dattaram</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -33403,12 +33403,12 @@
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>Tambade Rohini Hemanta</t>
+          <t>Tambade Rohini Hemant</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>Tambade Hemanta</t>
+          <t>Tambade Hemant</t>
         </is>
       </c>
     </row>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>Vadha Anil Gajanan</t>
+          <t>Vadh Anil Gajanan</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>Vadha Gajanan</t>
+          <t>Vadh Gajanan</t>
         </is>
       </c>
     </row>
@@ -33527,12 +33527,12 @@
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>Vagha Sudha Anil</t>
+          <t>Vagh Sudha Anil</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>Vagha Anil</t>
+          <t>Vagh Anil</t>
         </is>
       </c>
     </row>
@@ -33584,12 +33584,12 @@
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>Najharetha Domanik Kesamiro</t>
+          <t>Najhareth Domanik Kesamiro</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>Najharetha Kesamiro</t>
+          <t>Najhareth Kesamiro</t>
         </is>
       </c>
     </row>
@@ -33641,12 +33641,12 @@
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>Najharetha Meririta Domanik</t>
+          <t>Najhareth Meririta Domanik</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>Najharetha Domanik</t>
+          <t>Najhareth Domanik</t>
         </is>
       </c>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>Dhue Shashikanta Sahadev</t>
+          <t>Dhue Shashikant Sahadev</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -33812,12 +33812,12 @@
       </c>
       <c r="K605" t="inlineStr">
         <is>
-          <t>Devasthai Yashavanta Dattatray</t>
+          <t>Devasthai Yashavant Dattatraya</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>Devasthai Dattatray</t>
+          <t>Devasthai Dattatraya</t>
         </is>
       </c>
     </row>
@@ -33926,12 +33926,12 @@
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>Dhage Kamalakar Raghunatha</t>
+          <t>Dhage Kamalakar Raghunath</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Dhage Raghunatha</t>
+          <t>Dhage Raghunath</t>
         </is>
       </c>
     </row>
@@ -33983,12 +33983,12 @@
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>Mulla Arshadha Abubakkar</t>
+          <t>Mulla Arshadha Abubakkara</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>Mulla Abubakkar</t>
+          <t>Mulla Abubakkara</t>
         </is>
       </c>
     </row>
@@ -34606,7 +34606,7 @@
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>Raman Ramakrushnan K.</t>
+          <t>Raman Ramakrushnana K.</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
@@ -34663,12 +34663,12 @@
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>Kamakshi Kamakshi Ramakrushnan</t>
+          <t>Kamakshi Kamakshi Ramakrushnana</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>Kamakshi Ramakrushnan</t>
+          <t>Kamakshi Ramakrushnana</t>
         </is>
       </c>
     </row>
@@ -34834,12 +34834,12 @@
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>Devasthai Nitin Yashavanta</t>
+          <t>Devasthai Nitin Yashavant</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>Devasthai Yashavanta</t>
+          <t>Devasthai Yashavant</t>
         </is>
       </c>
     </row>
@@ -34891,12 +34891,12 @@
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>Devasthai Uday Yashavanta</t>
+          <t>Devasthai Uday Yashavant</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>Devasthai Yashavanta</t>
+          <t>Devasthai Yashavant</t>
         </is>
       </c>
     </row>
@@ -35062,12 +35062,12 @@
       </c>
       <c r="K628" t="inlineStr">
         <is>
-          <t>Raut Sunil Taranatha</t>
+          <t>Raut Sunil Taranath</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>Raut Taranatha</t>
+          <t>Raut Taranath</t>
         </is>
       </c>
     </row>
@@ -35176,12 +35176,12 @@
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Raut Kishor Taranatha</t>
+          <t>Raut Kishor Taranath</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>Raut Taranatha</t>
+          <t>Raut Taranath</t>
         </is>
       </c>
     </row>
@@ -35295,12 +35295,12 @@
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>Raut Prashanta Taranatha</t>
+          <t>Raut Prashant Taranath</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>Raut Taranatha</t>
+          <t>Raut Taranath</t>
         </is>
       </c>
     </row>
@@ -35352,12 +35352,12 @@
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>Raut Madhuri Prashanta</t>
+          <t>Raut Madhuri Prashant</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>Raut Prashanta</t>
+          <t>Raut Prashant</t>
         </is>
       </c>
     </row>
@@ -35409,12 +35409,12 @@
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>Raut Hirabai Taranatha</t>
+          <t>Raut Hirabai Taranath</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>Raut Taranatha</t>
+          <t>Raut Taranath</t>
         </is>
       </c>
     </row>
@@ -35466,12 +35466,12 @@
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>Raut Nayan Taranatha</t>
+          <t>Raut Nayan Taranath</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>Raut Taranatha</t>
+          <t>Raut Taranath</t>
         </is>
       </c>
     </row>
@@ -35865,12 +35865,12 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Dhage Mohan Raghunatha</t>
+          <t>Dhage Mohan Raghunath</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>Dhage Raghunatha</t>
+          <t>Dhage Raghunath</t>
         </is>
       </c>
     </row>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Khamakar Chandrakanta Mahadev</t>
+          <t>Khamakar Chandrakant Mahadev</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -36165,12 +36165,12 @@
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Khamakar Puja Chandrakanta</t>
+          <t>Khamakar Puja Chandrakant</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>Khamakar Chandrakanta</t>
+          <t>Khamakar Chandrakant</t>
         </is>
       </c>
     </row>
@@ -36517,7 +36517,7 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>Khamakar Ramakanta Mahadev</t>
+          <t>Khamakar Ramakant Mahadev</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -36574,12 +36574,12 @@
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>Khamakar Ragini Ramakanta</t>
+          <t>Khamakar Ragini Ramakant</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
         <is>
-          <t>Khamakar Ramakanta</t>
+          <t>Khamakar Ramakant</t>
         </is>
       </c>
     </row>
@@ -36631,12 +36631,12 @@
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>Khamakar Pranoti Ramakanta</t>
+          <t>Khamakar Pranoti Ramakant</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
         <is>
-          <t>Khamakar Ramakanta</t>
+          <t>Khamakar Ramakant</t>
         </is>
       </c>
     </row>
@@ -36688,12 +36688,12 @@
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>Khamakar Pranali Ramakanta</t>
+          <t>Khamakar Pranali Ramakant</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
         <is>
-          <t>Khamakar Ramakanta</t>
+          <t>Khamakar Ramakant</t>
         </is>
       </c>
     </row>
@@ -36745,12 +36745,12 @@
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Khamakar Pranab Ramakanta</t>
+          <t>Khamakar Pranab Ramakant</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
         <is>
-          <t>Khamakar Ramakanta</t>
+          <t>Khamakar Ramakant</t>
         </is>
       </c>
     </row>
@@ -36803,12 +36803,12 @@
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>Gondhai Shashikanta</t>
+          <t>Gondhai Shashikant</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
         <is>
-          <t>Gondhai Shashikanta</t>
+          <t>Gondhai Shashikant</t>
         </is>
       </c>
     </row>
@@ -36860,12 +36860,12 @@
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>Gondhai Shalaka Shashikanta</t>
+          <t>Gondhai Shalaka Shashikant</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
         <is>
-          <t>Gondhai Shashikanta</t>
+          <t>Gondhai Shashikant</t>
         </is>
       </c>
     </row>
@@ -37021,7 +37021,7 @@
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>Khamakar Milinda Suresh</t>
+          <t>Khamakar Milind Suresh</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
@@ -37306,12 +37306,12 @@
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>Mandavakar Harishchandra Viththal</t>
+          <t>Mandavakar Harishchandra Viththala</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
         <is>
-          <t>Mandavakar Viththal</t>
+          <t>Mandavakar Viththala</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>Lad Chandrakanta Mahadev</t>
+          <t>Lad Chandrakant Mahadev</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -37695,12 +37695,12 @@
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>Lad Rekha Chandrakanta</t>
+          <t>Lad Rekha Chandrakant</t>
         </is>
       </c>
       <c r="L675" t="inlineStr">
         <is>
-          <t>Lad Chandrakanta</t>
+          <t>Lad Chandrakant</t>
         </is>
       </c>
     </row>
@@ -38622,12 +38622,12 @@
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Savanta Dattaram Narayan</t>
+          <t>Savant Dattaram Narayan</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>Savanta Narayan</t>
+          <t>Savant Narayan</t>
         </is>
       </c>
     </row>
@@ -39016,7 +39016,7 @@
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>Vab Gangavane Lakshman</t>
+          <t>Vab Gangavane Lakshmana</t>
         </is>
       </c>
     </row>
@@ -39125,7 +39125,7 @@
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Parab Panduranga Krushna</t>
+          <t>Parab Pandurang Krushna</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -39182,12 +39182,12 @@
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>Parab Pradnya Panduranga</t>
+          <t>Parab Pradnya Pandurang</t>
         </is>
       </c>
       <c r="L701" t="inlineStr">
         <is>
-          <t>Parab Panduranga</t>
+          <t>Parab Pandurang</t>
         </is>
       </c>
     </row>
@@ -39301,7 +39301,7 @@
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>Kode Ananta Ramachandra</t>
+          <t>Kode Anant Ramachandra</t>
         </is>
       </c>
       <c r="L703" t="inlineStr">
@@ -39421,12 +39421,12 @@
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>Kode Amita Ananta</t>
+          <t>Kode Amita Anant</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>Kode Ananta</t>
+          <t>Kode Anant</t>
         </is>
       </c>
     </row>
@@ -39567,12 +39567,12 @@
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>Savanta Nitin Ananta</t>
+          <t>Savant Nitin Anant</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>Savanta Ananta</t>
+          <t>Savant Anant</t>
         </is>
       </c>
     </row>
@@ -39624,12 +39624,12 @@
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>Savanta Ananta Tukaram</t>
+          <t>Savant Anant Tukaram</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>Savanta Tukaram</t>
+          <t>Savant Tukaram</t>
         </is>
       </c>
     </row>
@@ -39681,12 +39681,12 @@
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>Savanta Vandana Ananta</t>
+          <t>Savant Vandana Anant</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>Savanta Ananta</t>
+          <t>Savant Anant</t>
         </is>
       </c>
     </row>
@@ -39738,12 +39738,12 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>Savanta Shubhangi Ananta</t>
+          <t>Savant Shubhangi Anant</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>Savanta Ananta</t>
+          <t>Savant Anant</t>
         </is>
       </c>
     </row>
@@ -41002,7 +41002,7 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Raut Ananta Narayan</t>
+          <t>Raut Anant Narayan</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -41059,12 +41059,12 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>Raut Indira Ananta</t>
+          <t>Raut Indira Anant</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>Raut Ananta</t>
+          <t>Raut Anant</t>
         </is>
       </c>
     </row>
@@ -41116,12 +41116,12 @@
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Raut Prakash Ananta</t>
+          <t>Raut Prakash Anant</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>Raut Ananta</t>
+          <t>Raut Anant</t>
         </is>
       </c>
     </row>
@@ -41230,12 +41230,12 @@
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>Raut Shekhar Ananta</t>
+          <t>Raut Shekhar Anant</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>Raut Ananta</t>
+          <t>Raut Anant</t>
         </is>
       </c>
     </row>
@@ -41349,12 +41349,12 @@
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>Raut Nitin Ananta</t>
+          <t>Raut Nitin Anant</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
         <is>
-          <t>Raut Ananta</t>
+          <t>Raut Anant</t>
         </is>
       </c>
     </row>
@@ -42232,7 +42232,7 @@
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>Raut Hemanta Narahari</t>
+          <t>Raut Hemant Narahari</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
@@ -42388,12 +42388,12 @@
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>Raut Mohini Moreshvar</t>
+          <t>Raut Mohini Moreshvara</t>
         </is>
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>Raut Moreshvar</t>
+          <t>Raut Moreshvara</t>
         </is>
       </c>
     </row>
@@ -42445,12 +42445,12 @@
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>Raut Ashish Moreshvar</t>
+          <t>Raut Ashish Moreshvara</t>
         </is>
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>Raut Moreshvar</t>
+          <t>Raut Moreshvara</t>
         </is>
       </c>
     </row>
@@ -42700,12 +42700,12 @@
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>Raut Dipak Yashavanta</t>
+          <t>Raut Dipak Yashavant</t>
         </is>
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>Raut Yashavanta</t>
+          <t>Raut Yashavant</t>
         </is>
       </c>
     </row>
@@ -43228,7 +43228,7 @@
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>Jambhae Subodha Ramachandra</t>
+          <t>Jambhae Subodh Ramachandra</t>
         </is>
       </c>
       <c r="L775" t="inlineStr">
@@ -43290,12 +43290,12 @@
       </c>
       <c r="K776" t="inlineStr">
         <is>
-          <t>Jambhae Suchita Subodha</t>
+          <t>Jambhae Suchita Subodh</t>
         </is>
       </c>
       <c r="L776" t="inlineStr">
         <is>
-          <t>Jambhae Subodha</t>
+          <t>Jambhae Subodh</t>
         </is>
       </c>
     </row>
@@ -43347,12 +43347,12 @@
       </c>
       <c r="K777" t="inlineStr">
         <is>
-          <t>Pande Uma Umaranatha</t>
+          <t>Pande Uma Umaranath</t>
         </is>
       </c>
       <c r="L777" t="inlineStr">
         <is>
-          <t>Pande Umaranatha</t>
+          <t>Pande Umaranath</t>
         </is>
       </c>
     </row>
@@ -43830,7 +43830,7 @@
       </c>
       <c r="K786" t="inlineStr">
         <is>
-          <t>Raut Ananta Jayaram</t>
+          <t>Raut Anant Jayaram</t>
         </is>
       </c>
       <c r="L786" t="inlineStr">
@@ -43887,12 +43887,12 @@
       </c>
       <c r="K787" t="inlineStr">
         <is>
-          <t>Raut Indira Ananta</t>
+          <t>Raut Indira Anant</t>
         </is>
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>Raut Ananta</t>
+          <t>Raut Anant</t>
         </is>
       </c>
     </row>
@@ -43944,12 +43944,12 @@
       </c>
       <c r="K788" t="inlineStr">
         <is>
-          <t>Raut Suresh Ananta</t>
+          <t>Raut Suresh Anant</t>
         </is>
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>Raut Ananta</t>
+          <t>Raut Anant</t>
         </is>
       </c>
     </row>
@@ -44058,12 +44058,12 @@
       </c>
       <c r="K790" t="inlineStr">
         <is>
-          <t>Raut Jayanta Narasinha</t>
+          <t>Raut Jayant Narasinh</t>
         </is>
       </c>
       <c r="L790" t="inlineStr">
         <is>
-          <t>Raut Narasinha</t>
+          <t>Raut Narasinh</t>
         </is>
       </c>
     </row>
@@ -44115,12 +44115,12 @@
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t>Raut Jayashri Jayanta</t>
+          <t>Raut Jayashri Jayant</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>Raut Jayanta</t>
+          <t>Raut Jayant</t>
         </is>
       </c>
     </row>
@@ -44172,12 +44172,12 @@
       </c>
       <c r="K792" t="inlineStr">
         <is>
-          <t>Raut Sachin Narasinha</t>
+          <t>Raut Sachin Narasinh</t>
         </is>
       </c>
       <c r="L792" t="inlineStr">
         <is>
-          <t>Raut Narasinha</t>
+          <t>Raut Narasinh</t>
         </is>
       </c>
     </row>
@@ -44500,7 +44500,7 @@
       </c>
       <c r="K799" t="inlineStr">
         <is>
-          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
+          <t>Ghar Kramank Matadarache Purna Nanv Nate Natevaikache Purna Nanv Ling Vay</t>
         </is>
       </c>
     </row>
@@ -45149,12 +45149,12 @@
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Patanakar Ashok Panduranga</t>
+          <t>Patanakar Ashok Pandurang</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Patanakar Panduranga</t>
+          <t>Patanakar Pandurang</t>
         </is>
       </c>
     </row>
@@ -45377,12 +45377,12 @@
       </c>
       <c r="K815" t="inlineStr">
         <is>
-          <t>Patanakar Dilip Panduranga</t>
+          <t>Patanakar Dilip Pandurang</t>
         </is>
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>Patanakar Panduranga</t>
+          <t>Patanakar Pandurang</t>
         </is>
       </c>
     </row>
@@ -45615,7 +45615,7 @@
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>Patanakar Panduranga</t>
+          <t>Patanakar Pandurang</t>
         </is>
       </c>
     </row>
@@ -45729,7 +45729,7 @@
       </c>
       <c r="K821" t="inlineStr">
         <is>
-          <t>Raut Panduranga Vaman</t>
+          <t>Raut Pandurang Vaman</t>
         </is>
       </c>
       <c r="L821" t="inlineStr">
@@ -45786,12 +45786,12 @@
       </c>
       <c r="K822" t="inlineStr">
         <is>
-          <t>Raut Lakshmi Panduranga</t>
+          <t>Raut Lakshmi Pandurang</t>
         </is>
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>Raut Panduranga</t>
+          <t>Raut Pandurang</t>
         </is>
       </c>
     </row>
@@ -45843,12 +45843,12 @@
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t>Raut Kumar Panduranga</t>
+          <t>Raut Kumar Pandurang</t>
         </is>
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>Raut Panduranga</t>
+          <t>Raut Pandurang</t>
         </is>
       </c>
     </row>
@@ -45900,12 +45900,12 @@
       </c>
       <c r="K824" t="inlineStr">
         <is>
-          <t>Raut Sunita Panduranga</t>
+          <t>Raut Sunita Pandurang</t>
         </is>
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>Raut Panduranga</t>
+          <t>Raut Pandurang</t>
         </is>
       </c>
     </row>
@@ -45957,12 +45957,12 @@
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>Raut Pradip Panduranga</t>
+          <t>Raut Pradip Pandurang</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>Raut Panduranga</t>
+          <t>Raut Pandurang</t>
         </is>
       </c>
     </row>
@@ -46071,12 +46071,12 @@
       </c>
       <c r="K827" t="inlineStr">
         <is>
-          <t>Raut Kiran Panduranga</t>
+          <t>Raut Kiran Pandurang</t>
         </is>
       </c>
       <c r="L827" t="inlineStr">
         <is>
-          <t>Raut Panduranga</t>
+          <t>Raut Pandurang</t>
         </is>
       </c>
     </row>
@@ -46881,7 +46881,7 @@
       </c>
       <c r="K842" t="inlineStr">
         <is>
-          <t>Raut Chandrakanta Daji</t>
+          <t>Raut Chandrakant Daji</t>
         </is>
       </c>
       <c r="L842" t="inlineStr">
@@ -46938,12 +46938,12 @@
       </c>
       <c r="K843" t="inlineStr">
         <is>
-          <t>Raut Chaya Chandrakanta</t>
+          <t>Raut Chaya Chandrakant</t>
         </is>
       </c>
       <c r="L843" t="inlineStr">
         <is>
-          <t>Raut Chandrakanta</t>
+          <t>Raut Chandrakant</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="K848" t="inlineStr">
         <is>
-          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
+          <t>Ghar Kramank Matadarache Purna Nanv Nate Natevaikache Purna Nanv Ling Vay</t>
         </is>
       </c>
     </row>
@@ -47204,7 +47204,7 @@
       </c>
       <c r="K849" t="inlineStr">
         <is>
-          <t>Raut Prashanta Damodar</t>
+          <t>Raut Prashant Damodar</t>
         </is>
       </c>
       <c r="L849" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="K851" t="inlineStr">
         <is>
-          <t>Raut Hareshvar Daji</t>
+          <t>Raut Hareshvara Daji</t>
         </is>
       </c>
       <c r="L851" t="inlineStr">
@@ -47375,12 +47375,12 @@
       </c>
       <c r="K852" t="inlineStr">
         <is>
-          <t>Raut Usha Hareshvar</t>
+          <t>Raut Usha Hareshvara</t>
         </is>
       </c>
       <c r="L852" t="inlineStr">
         <is>
-          <t>Raut Hareshvar</t>
+          <t>Raut Hareshvara</t>
         </is>
       </c>
     </row>
@@ -47432,12 +47432,12 @@
       </c>
       <c r="K853" t="inlineStr">
         <is>
-          <t>Raut Naresh Hareshvar</t>
+          <t>Raut Naresh Hareshvara</t>
         </is>
       </c>
       <c r="L853" t="inlineStr">
         <is>
-          <t>Raut Hareshvar</t>
+          <t>Raut Hareshvara</t>
         </is>
       </c>
     </row>
@@ -47546,12 +47546,12 @@
       </c>
       <c r="K855" t="inlineStr">
         <is>
-          <t>Megholi Bharati Bhaskar</t>
+          <t>Megholi Bharati Bhaskara</t>
         </is>
       </c>
       <c r="L855" t="inlineStr">
         <is>
-          <t>Megholi Bhaskar</t>
+          <t>Megholi Bhaskara</t>
         </is>
       </c>
     </row>
@@ -47603,12 +47603,12 @@
       </c>
       <c r="K856" t="inlineStr">
         <is>
-          <t>Megholi Prakash Bhaskar</t>
+          <t>Megholi Prakash Bhaskara</t>
         </is>
       </c>
       <c r="L856" t="inlineStr">
         <is>
-          <t>Megholi Bhaskar</t>
+          <t>Megholi Bhaskara</t>
         </is>
       </c>
     </row>
@@ -48329,7 +48329,7 @@
       </c>
       <c r="K869" t="inlineStr">
         <is>
-          <t>Bhatagavakar Panduranga Krushna</t>
+          <t>Bhatagavakar Pandurang Krushna</t>
         </is>
       </c>
       <c r="L869" t="inlineStr">
@@ -48386,12 +48386,12 @@
       </c>
       <c r="K870" t="inlineStr">
         <is>
-          <t>Bhatagavakar Mandakini Panduranga</t>
+          <t>Bhatagavakar Mandakini Pandurang</t>
         </is>
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>Bhatagavakar Panduranga</t>
+          <t>Bhatagavakar Pandurang</t>
         </is>
       </c>
     </row>
@@ -49164,7 +49164,7 @@
       </c>
       <c r="K884" t="inlineStr">
         <is>
-          <t>Pavar Makaranda Baa</t>
+          <t>Pavar Makarand Baa</t>
         </is>
       </c>
       <c r="L884" t="inlineStr">
@@ -49221,12 +49221,12 @@
       </c>
       <c r="K885" t="inlineStr">
         <is>
-          <t>Raut Bhagavan Kashinatha</t>
+          <t>Raut Bhagavan Kashinath</t>
         </is>
       </c>
       <c r="L885" t="inlineStr">
         <is>
-          <t>Raut Kashinatha</t>
+          <t>Raut Kashinath</t>
         </is>
       </c>
     </row>
@@ -49506,12 +49506,12 @@
       </c>
       <c r="K890" t="inlineStr">
         <is>
-          <t>Thakur Madhukar Lakshman</t>
+          <t>Thakur Madhukar Lakshmana</t>
         </is>
       </c>
       <c r="L890" t="inlineStr">
         <is>
-          <t>Thakur Lakshman</t>
+          <t>Thakur Lakshmana</t>
         </is>
       </c>
     </row>
@@ -49834,7 +49834,7 @@
       </c>
       <c r="K897" t="inlineStr">
         <is>
-          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
+          <t>Ghar Kramank Matadarache Purna Nanv Nate Natevaikache Purna Nanv Ling Vay</t>
         </is>
       </c>
     </row>
@@ -49970,12 +49970,12 @@
       </c>
       <c r="K900" t="inlineStr">
         <is>
-          <t>Raut Vishvanatha Panduranga</t>
+          <t>Raut Vishvanath Pandurang</t>
         </is>
       </c>
       <c r="L900" t="inlineStr">
         <is>
-          <t>Raut Panduranga</t>
+          <t>Raut Pandurang</t>
         </is>
       </c>
     </row>
@@ -50027,12 +50027,12 @@
       </c>
       <c r="K901" t="inlineStr">
         <is>
-          <t>Raut Sanjivini Vishvanatha</t>
+          <t>Raut Sanjivini Vishvanath</t>
         </is>
       </c>
       <c r="L901" t="inlineStr">
         <is>
-          <t>Raut Vishvanatha</t>
+          <t>Raut Vishvanath</t>
         </is>
       </c>
     </row>
@@ -50084,12 +50084,12 @@
       </c>
       <c r="K902" t="inlineStr">
         <is>
-          <t>Raut Kalpesh Vishvanatha</t>
+          <t>Raut Kalpesh Vishvanath</t>
         </is>
       </c>
       <c r="L902" t="inlineStr">
         <is>
-          <t>Raut Vishvanatha</t>
+          <t>Raut Vishvanath</t>
         </is>
       </c>
     </row>
@@ -50141,12 +50141,12 @@
       </c>
       <c r="K903" t="inlineStr">
         <is>
-          <t>Raut Vilas Panduranga</t>
+          <t>Raut Vilas Pandurang</t>
         </is>
       </c>
       <c r="L903" t="inlineStr">
         <is>
-          <t>Raut Panduranga</t>
+          <t>Raut Pandurang</t>
         </is>
       </c>
     </row>
@@ -50768,7 +50768,7 @@
       </c>
       <c r="K914" t="inlineStr">
         <is>
-          <t>Rana Hemanta Champakalal</t>
+          <t>Rana Hemant Champakalal</t>
         </is>
       </c>
       <c r="L914" t="inlineStr">
@@ -50825,12 +50825,12 @@
       </c>
       <c r="K915" t="inlineStr">
         <is>
-          <t>Rana Darshana Hemanta</t>
+          <t>Rana Darshana Hemant</t>
         </is>
       </c>
       <c r="L915" t="inlineStr">
         <is>
-          <t>Rana Hemanta</t>
+          <t>Rana Hemant</t>
         </is>
       </c>
     </row>
@@ -51323,12 +51323,12 @@
       </c>
       <c r="K924" t="inlineStr">
         <is>
-          <t>Bhosale Prakash Vasanta</t>
+          <t>Bhosale Prakash Vasant</t>
         </is>
       </c>
       <c r="L924" t="inlineStr">
         <is>
-          <t>Bhosale Vasanta</t>
+          <t>Bhosale Vasant</t>
         </is>
       </c>
     </row>
@@ -52210,7 +52210,7 @@
       </c>
       <c r="K940" t="inlineStr">
         <is>
-          <t>Vab Nayar Bhaskar</t>
+          <t>Vab Nayar Bhaskara</t>
         </is>
       </c>
     </row>
@@ -52376,7 +52376,7 @@
       </c>
       <c r="K943" t="inlineStr">
         <is>
-          <t>Nayar Prashanta Shankar</t>
+          <t>Nayar Prashant Shankar</t>
         </is>
       </c>
       <c r="L943" t="inlineStr">
@@ -52476,7 +52476,7 @@
       </c>
       <c r="K946" t="inlineStr">
         <is>
-          <t>Ghar Kramanka Matadarache Purna Nanva Nate Natevaikache Purna Nanva Linga Vay</t>
+          <t>Ghar Kramank Matadarache Purna Nanv Nate Natevaikache Purna Nanv Ling Vay</t>
         </is>
       </c>
     </row>
@@ -52813,7 +52813,7 @@
       </c>
       <c r="K952" t="inlineStr">
         <is>
-          <t>Kulakani Ranganatha Ramarav</t>
+          <t>Kulakani Ranganath Ramarav</t>
         </is>
       </c>
       <c r="L952" t="inlineStr">
@@ -52870,12 +52870,12 @@
       </c>
       <c r="K953" t="inlineStr">
         <is>
-          <t>Kulakani Radha Ranganatha</t>
+          <t>Kulakani Radha Ranganath</t>
         </is>
       </c>
       <c r="L953" t="inlineStr">
         <is>
-          <t>Kulakani Ranganatha</t>
+          <t>Kulakani Ranganath</t>
         </is>
       </c>
     </row>
@@ -53425,7 +53425,7 @@
       </c>
       <c r="K963" t="inlineStr">
         <is>
-          <t>Kini Ananta Narayan</t>
+          <t>Kini Anant Narayan</t>
         </is>
       </c>
       <c r="L963" t="inlineStr">
@@ -53482,12 +53482,12 @@
       </c>
       <c r="K964" t="inlineStr">
         <is>
-          <t>Kini Manaku Ananta</t>
+          <t>Kini Manaku Anant</t>
         </is>
       </c>
       <c r="L964" t="inlineStr">
         <is>
-          <t>Kini Ananta</t>
+          <t>Kini Anant</t>
         </is>
       </c>
     </row>
@@ -53539,12 +53539,12 @@
       </c>
       <c r="K965" t="inlineStr">
         <is>
-          <t>Kini Ajit Ananta</t>
+          <t>Kini Ajit Anant</t>
         </is>
       </c>
       <c r="L965" t="inlineStr">
         <is>
-          <t>Kini Ananta</t>
+          <t>Kini Anant</t>
         </is>
       </c>
     </row>
@@ -53995,7 +53995,7 @@
       </c>
       <c r="K973" t="inlineStr">
         <is>
-          <t>Kini Panduranga Narayan</t>
+          <t>Kini Pandurang Narayan</t>
         </is>
       </c>
       <c r="L973" t="inlineStr">
@@ -54052,12 +54052,12 @@
       </c>
       <c r="K974" t="inlineStr">
         <is>
-          <t>Kini Manda Panduranga</t>
+          <t>Kini Manda Pandurang</t>
         </is>
       </c>
       <c r="L974" t="inlineStr">
         <is>
-          <t>Kini Panduranga</t>
+          <t>Kini Pandurang</t>
         </is>
       </c>
     </row>
@@ -54114,7 +54114,7 @@
       </c>
       <c r="L975" t="inlineStr">
         <is>
-          <t>Kini Panduranga</t>
+          <t>Kini Pandurang</t>
         </is>
       </c>
     </row>
@@ -54223,12 +54223,12 @@
       </c>
       <c r="K977" t="inlineStr">
         <is>
-          <t>Kini Rakesh Panduranga</t>
+          <t>Kini Rakesh Pandurang</t>
         </is>
       </c>
       <c r="L977" t="inlineStr">
         <is>
-          <t>Kini Panduranga</t>
+          <t>Kini Pandurang</t>
         </is>
       </c>
     </row>
@@ -54726,7 +54726,7 @@
       </c>
       <c r="K986" t="inlineStr">
         <is>
-          <t>Vab Shirasagar Viththal</t>
+          <t>Vab Shirasagar Viththala</t>
         </is>
       </c>
     </row>
@@ -55063,12 +55063,12 @@
       </c>
       <c r="K992" t="inlineStr">
         <is>
-          <t>Shirasagar Naredra Viththal</t>
+          <t>Shirasagar Naredra Viththala</t>
         </is>
       </c>
       <c r="L992" t="inlineStr">
         <is>
-          <t>Shirasagar Viththal</t>
+          <t>Shirasagar Viththala</t>
         </is>
       </c>
     </row>
@@ -55121,7 +55121,7 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>Shirasagar Nishikanta Viththal</t>
+          <t>Shirasagar Nishikant Viththala</t>
         </is>
       </c>
       <c r="L994" t="inlineStr">
@@ -55178,12 +55178,12 @@
       </c>
       <c r="K995" t="inlineStr">
         <is>
-          <t>Shirasagar Sujata Nishikanta</t>
+          <t>Shirasagar Sujata Nishikant</t>
         </is>
       </c>
       <c r="L995" t="inlineStr">
         <is>
-          <t>Shirasagar Nishikanta</t>
+          <t>Shirasagar Nishikant</t>
         </is>
       </c>
     </row>
@@ -55235,12 +55235,12 @@
       </c>
       <c r="K996" t="inlineStr">
         <is>
-          <t>Shirasagar Yogita Nishikanta</t>
+          <t>Shirasagar Yogita Nishikant</t>
         </is>
       </c>
       <c r="L996" t="inlineStr">
         <is>
-          <t>Shirasagar Nishikanta</t>
+          <t>Shirasagar Nishikant</t>
         </is>
       </c>
     </row>
@@ -55463,7 +55463,7 @@
       </c>
       <c r="K1000" t="inlineStr">
         <is>
-          <t>Raut Niakantha Ramesh</t>
+          <t>Raut Niakanth Ramesh</t>
         </is>
       </c>
       <c r="L1000" t="inlineStr">
@@ -55733,7 +55733,7 @@
       </c>
       <c r="K1005" t="inlineStr">
         <is>
-          <t>Raut Chandrakanta Narayan</t>
+          <t>Raut Chandrakant Narayan</t>
         </is>
       </c>
       <c r="L1005" t="inlineStr">
@@ -55847,12 +55847,12 @@
       </c>
       <c r="K1007" t="inlineStr">
         <is>
-          <t>Raut Naredra Jagannatha</t>
+          <t>Raut Naredra Jagannath</t>
         </is>
       </c>
       <c r="L1007" t="inlineStr">
         <is>
-          <t>Raut Jagannatha</t>
+          <t>Raut Jagannath</t>
         </is>
       </c>
     </row>
@@ -55961,7 +55961,7 @@
       </c>
       <c r="K1009" t="inlineStr">
         <is>
-          <t>Thombare Dasharatha Arjun</t>
+          <t>Thombare Dasharath Arjun</t>
         </is>
       </c>
       <c r="L1009" t="inlineStr">
@@ -56018,12 +56018,12 @@
       </c>
       <c r="K1010" t="inlineStr">
         <is>
-          <t>Thombare Sudha Dasharatha</t>
+          <t>Thombare Sudha Dasharath</t>
         </is>
       </c>
       <c r="L1010" t="inlineStr">
         <is>
-          <t>Thombare Dasharatha</t>
+          <t>Thombare Dasharath</t>
         </is>
       </c>
     </row>
@@ -56075,12 +56075,12 @@
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t>Thombare Jitendra Dasharatha</t>
+          <t>Thombare Jitendra Dasharath</t>
         </is>
       </c>
       <c r="L1011" t="inlineStr">
         <is>
-          <t>Thombare Dasharatha</t>
+          <t>Thombare Dasharath</t>
         </is>
       </c>
     </row>
@@ -56132,12 +56132,12 @@
       </c>
       <c r="K1012" t="inlineStr">
         <is>
-          <t>Thombare Arpana Dasharatha</t>
+          <t>Thombare Arpana Dasharath</t>
         </is>
       </c>
       <c r="L1012" t="inlineStr">
         <is>
-          <t>Thombare Dasharatha</t>
+          <t>Thombare Dasharath</t>
         </is>
       </c>
     </row>
@@ -56303,7 +56303,7 @@
       </c>
       <c r="K1015" t="inlineStr">
         <is>
-          <t>Dolatode Hemanta Aba</t>
+          <t>Dolatode Hemant Aba</t>
         </is>
       </c>
       <c r="L1015" t="inlineStr">
@@ -57160,7 +57160,7 @@
       </c>
       <c r="K1031" t="inlineStr">
         <is>
-          <t>Jindal Udhamasinga Karatar</t>
+          <t>Jindal Udhamasing Karatar</t>
         </is>
       </c>
       <c r="L1031" t="inlineStr">
@@ -57207,7 +57207,7 @@
       </c>
       <c r="K1032" t="inlineStr">
         <is>
-          <t>Jindal Manjil Udhamasinga Pa Jindal Udhamasinga Satri</t>
+          <t>Jindal Manjil Udhamasing Pa Jindal Udhamasing Satri</t>
         </is>
       </c>
     </row>
@@ -57259,12 +57259,12 @@
       </c>
       <c r="K1033" t="inlineStr">
         <is>
-          <t>Jindal Sandip Udhamasinga</t>
+          <t>Jindal Sandip Udhamasing</t>
         </is>
       </c>
       <c r="L1033" t="inlineStr">
         <is>
-          <t>Jindal Udhamasinga</t>
+          <t>Jindal Udhamasing</t>
         </is>
       </c>
     </row>
@@ -57316,12 +57316,12 @@
       </c>
       <c r="K1034" t="inlineStr">
         <is>
-          <t>Jindal Sanjiv Udhamasaunga</t>
+          <t>Jindal Sanjiv Udhamasaung</t>
         </is>
       </c>
       <c r="L1034" t="inlineStr">
         <is>
-          <t>Jindal Udhamasinga</t>
+          <t>Jindal Udhamasing</t>
         </is>
       </c>
     </row>
@@ -58253,7 +58253,7 @@
       </c>
       <c r="K1053" t="inlineStr">
         <is>
-          <t>Ravat Gyanasinga Sundarasi</t>
+          <t>Ravat Gyanasing Sundarasi</t>
         </is>
       </c>
       <c r="L1053" t="inlineStr">
@@ -58310,12 +58310,12 @@
       </c>
       <c r="K1054" t="inlineStr">
         <is>
-          <t>Ravat Radha Gyanasinga</t>
+          <t>Ravat Radha Gyanasing</t>
         </is>
       </c>
       <c r="L1054" t="inlineStr">
         <is>
-          <t>Ravat Gyanasinga</t>
+          <t>Ravat Gyanasing</t>
         </is>
       </c>
     </row>
@@ -59182,7 +59182,7 @@
       </c>
       <c r="K1070" t="inlineStr">
         <is>
-          <t>Pamakortab Bhanukuttan Krushnan Cha Bhanukuttan Q</t>
+          <t>Pamakortaba Bhanukuttana Krushnana Cha Bhanukuttana Q</t>
         </is>
       </c>
     </row>
@@ -59239,12 +59239,12 @@
       </c>
       <c r="K1071" t="inlineStr">
         <is>
-          <t>Bhanukuttan Shamala Krushnan</t>
+          <t>Bhanukuttana Shamala Krushnana</t>
         </is>
       </c>
       <c r="L1071" t="inlineStr">
         <is>
-          <t>Bhanukuttan Krushnan</t>
+          <t>Bhanukuttana Krushnana</t>
         </is>
       </c>
     </row>
@@ -59514,7 +59514,7 @@
       </c>
       <c r="L1076" t="inlineStr">
         <is>
-          <t>Natarajan Kannan Va Natarajan</t>
+          <t>Natarajan Kannana Va Natarajan</t>
         </is>
       </c>
     </row>
@@ -59566,7 +59566,7 @@
       </c>
       <c r="K1077" t="inlineStr">
         <is>
-          <t>Pamakortab Natarajan Vasanti</t>
+          <t>Pamakortaba Natarajan Vasanti</t>
         </is>
       </c>
       <c r="L1077" t="inlineStr">
@@ -59851,12 +59851,12 @@
       </c>
       <c r="K1082" t="inlineStr">
         <is>
-          <t>Pamakortasi Ravat Viredrasinga</t>
+          <t>Pamakortasi Ravat Viredrasing</t>
         </is>
       </c>
       <c r="L1082" t="inlineStr">
         <is>
-          <t>Ravat Virendrasinga</t>
+          <t>Ravat Virendrasing</t>
         </is>
       </c>
     </row>
@@ -59908,12 +59908,12 @@
       </c>
       <c r="K1083" t="inlineStr">
         <is>
-          <t>Ravat Gita Virendrasinga</t>
+          <t>Ravat Gita Virendrasing</t>
         </is>
       </c>
       <c r="L1083" t="inlineStr">
         <is>
-          <t>Ravat Virendrasonga</t>
+          <t>Ravat Virendrasong</t>
         </is>
       </c>
     </row>
@@ -60278,12 +60278,12 @@
       </c>
       <c r="K1091" t="inlineStr">
         <is>
-          <t>Bandekar Ramakrushna Niakantha</t>
+          <t>Bandekar Ramakrushna Niakanth</t>
         </is>
       </c>
       <c r="L1091" t="inlineStr">
         <is>
-          <t>Bandekar Niakantha</t>
+          <t>Bandekar Niakanth</t>
         </is>
       </c>
     </row>
@@ -60667,7 +60667,7 @@
       </c>
       <c r="K1098" t="inlineStr">
         <is>
-          <t>Vab Shekha Nasir</t>
+          <t>Vab Shekh Nasir</t>
         </is>
       </c>
     </row>
@@ -60719,12 +60719,12 @@
       </c>
       <c r="K1099" t="inlineStr">
         <is>
-          <t>Shekha Rijhavana Javed</t>
+          <t>Shekh Rijhavana Javed</t>
         </is>
       </c>
       <c r="L1099" t="inlineStr">
         <is>
-          <t>Shekha Javed</t>
+          <t>Shekh Javed</t>
         </is>
       </c>
     </row>
@@ -60776,12 +60776,12 @@
       </c>
       <c r="K1100" t="inlineStr">
         <is>
-          <t>Shekha Anjum Nasir</t>
+          <t>Shekh Anjum Nasir</t>
         </is>
       </c>
       <c r="L1100" t="inlineStr">
         <is>
-          <t>Shekha Nasir</t>
+          <t>Shekh Nasir</t>
         </is>
       </c>
     </row>
@@ -60833,12 +60833,12 @@
       </c>
       <c r="K1101" t="inlineStr">
         <is>
-          <t>Kasarale Gajanan Vishvanatha</t>
+          <t>Kasarale Gajanan Vishvanath</t>
         </is>
       </c>
       <c r="L1101" t="inlineStr">
         <is>
-          <t>Kasarale Vishvanatha</t>
+          <t>Kasarale Vishvanath</t>
         </is>
       </c>
     </row>
@@ -60890,12 +60890,12 @@
       </c>
       <c r="K1102" t="inlineStr">
         <is>
-          <t>Kasarale Lilavati Vishvanatha</t>
+          <t>Kasarale Lilavati Vishvanath</t>
         </is>
       </c>
       <c r="L1102" t="inlineStr">
         <is>
-          <t>Kasarale Vishvanatha</t>
+          <t>Kasarale Vishvanath</t>
         </is>
       </c>
     </row>
@@ -61165,7 +61165,7 @@
       </c>
       <c r="K1107" t="inlineStr">
         <is>
-          <t>Vach Bharadvaj Raghunatha</t>
+          <t>Vach Bharadvaj Raghunath</t>
         </is>
       </c>
     </row>
@@ -61274,12 +61274,12 @@
       </c>
       <c r="K1109" t="inlineStr">
         <is>
-          <t>Shekha Mohammad Yasin</t>
+          <t>Shekh Mohammada Yasin</t>
         </is>
       </c>
       <c r="L1109" t="inlineStr">
         <is>
-          <t>Shekha Yasin</t>
+          <t>Shekh Yasin</t>
         </is>
       </c>
     </row>
@@ -61331,12 +61331,12 @@
       </c>
       <c r="K1110" t="inlineStr">
         <is>
-          <t>Shekha Rajiyakhatun Mohamma</t>
+          <t>Shekh Rajiyakhatun Mohamma</t>
         </is>
       </c>
       <c r="L1110" t="inlineStr">
         <is>
-          <t>Shekha Mohammad</t>
+          <t>Shekh Mohammada</t>
         </is>
       </c>
     </row>
@@ -61388,12 +61388,12 @@
       </c>
       <c r="K1111" t="inlineStr">
         <is>
-          <t>Shekha Yusupha Mohammad</t>
+          <t>Shekh Yusuph Mohammada</t>
         </is>
       </c>
       <c r="L1111" t="inlineStr">
         <is>
-          <t>Shekha Mohammad</t>
+          <t>Shekh Mohammada</t>
         </is>
       </c>
     </row>
@@ -61445,12 +61445,12 @@
       </c>
       <c r="K1112" t="inlineStr">
         <is>
-          <t>Shekha Abida Yusupha</t>
+          <t>Shekh Abida Yusuph</t>
         </is>
       </c>
       <c r="L1112" t="inlineStr">
         <is>
-          <t>Shekha Yusupha</t>
+          <t>Shekh Yusuph</t>
         </is>
       </c>
     </row>
@@ -61502,12 +61502,12 @@
       </c>
       <c r="K1113" t="inlineStr">
         <is>
-          <t>Shekha Yunus Mohammad</t>
+          <t>Shekh Yunus Mohammada</t>
         </is>
       </c>
       <c r="L1113" t="inlineStr">
         <is>
-          <t>Shekha Mohammad</t>
+          <t>Shekh Mohammada</t>
         </is>
       </c>
     </row>
@@ -61559,12 +61559,12 @@
       </c>
       <c r="K1114" t="inlineStr">
         <is>
-          <t>Shekha Salim Mohammad</t>
+          <t>Shekh Salim Mohammada</t>
         </is>
       </c>
       <c r="L1114" t="inlineStr">
         <is>
-          <t>Shekha Mohammad</t>
+          <t>Shekh Mohammada</t>
         </is>
       </c>
     </row>
@@ -61616,12 +61616,12 @@
       </c>
       <c r="K1115" t="inlineStr">
         <is>
-          <t>Shekha Shakol Mohammad</t>
+          <t>Shekh Shakol Mohammada</t>
         </is>
       </c>
       <c r="L1115" t="inlineStr">
         <is>
-          <t>Shekha Mohammad</t>
+          <t>Shekh Mohammada</t>
         </is>
       </c>
     </row>
@@ -61673,12 +61673,12 @@
       </c>
       <c r="K1116" t="inlineStr">
         <is>
-          <t>Shekha Naushad Mohammad</t>
+          <t>Shekh Naushad Mohammada</t>
         </is>
       </c>
       <c r="L1116" t="inlineStr">
         <is>
-          <t>Shekha Mohammad</t>
+          <t>Shekh Mohammada</t>
         </is>
       </c>
     </row>
@@ -61844,12 +61844,12 @@
       </c>
       <c r="K1119" t="inlineStr">
         <is>
-          <t>Karayat Tejasaunha Hyatasinga</t>
+          <t>Karayat Tejasaunh Hyatasing</t>
         </is>
       </c>
       <c r="L1119" t="inlineStr">
         <is>
-          <t>Karayat Hyatasinga</t>
+          <t>Karayat Hyatasing</t>
         </is>
       </c>
     </row>
@@ -61901,12 +61901,12 @@
       </c>
       <c r="K1120" t="inlineStr">
         <is>
-          <t>Karayat Pushpa Tejasinha</t>
+          <t>Karayat Pushpa Tejasinh</t>
         </is>
       </c>
       <c r="L1120" t="inlineStr">
         <is>
-          <t>Karayat Tejasinha</t>
+          <t>Karayat Tejasinh</t>
         </is>
       </c>
     </row>
@@ -61958,12 +61958,12 @@
       </c>
       <c r="K1121" t="inlineStr">
         <is>
-          <t>Karayat Yogesh Tejasinha</t>
+          <t>Karayat Yogesh Tejasinh</t>
         </is>
       </c>
       <c r="L1121" t="inlineStr">
         <is>
-          <t>Karayat Tejasinha</t>
+          <t>Karayat Tejasinh</t>
         </is>
       </c>
     </row>
@@ -62072,12 +62072,12 @@
       </c>
       <c r="K1123" t="inlineStr">
         <is>
-          <t>Karayat Vini Tejasinha</t>
+          <t>Karayat Vini Tejasinh</t>
         </is>
       </c>
       <c r="L1123" t="inlineStr">
         <is>
-          <t>Karayat Tejasinha</t>
+          <t>Karayat Tejasinh</t>
         </is>
       </c>
     </row>
@@ -62129,12 +62129,12 @@
       </c>
       <c r="K1124" t="inlineStr">
         <is>
-          <t>Karayat Roki Tejasinha</t>
+          <t>Karayat Roki Tejasinh</t>
         </is>
       </c>
       <c r="L1124" t="inlineStr">
         <is>
-          <t>Karayat Tejasinha</t>
+          <t>Karayat Tejasinh</t>
         </is>
       </c>
     </row>
@@ -62652,7 +62652,7 @@
       </c>
       <c r="K1133" t="inlineStr">
         <is>
-          <t>Prasad Shivaprasad Mhaisananda</t>
+          <t>Prasad Shivaprasad Mhaisanand</t>
         </is>
       </c>
       <c r="L1133" t="inlineStr">
@@ -63007,7 +63007,7 @@
       </c>
       <c r="L1141" t="inlineStr">
         <is>
-          <t>Savanta Chandrakanta Dhondu Va Savanta Dhondu</t>
+          <t>Savant Chandrakant Dhondu Va Savant Dhondu</t>
         </is>
       </c>
     </row>
@@ -63064,7 +63064,7 @@
       </c>
       <c r="L1142" t="inlineStr">
         <is>
-          <t>Sabanta Madhuri Chandrakanta Pa Savanta Chandrakanta</t>
+          <t>Sabant Madhuri Chandrakant Pa Savant Chandrakant</t>
         </is>
       </c>
     </row>
@@ -63116,12 +63116,12 @@
       </c>
       <c r="K1143" t="inlineStr">
         <is>
-          <t>Savanta Girish Chandrakanta</t>
+          <t>Savant Girish Chandrakant</t>
         </is>
       </c>
       <c r="L1143" t="inlineStr">
         <is>
-          <t>Savanta Chandrakanta</t>
+          <t>Savant Chandrakant</t>
         </is>
       </c>
     </row>
@@ -63178,7 +63178,7 @@
       </c>
       <c r="L1144" t="inlineStr">
         <is>
-          <t>Savanta Anandi Dhondu Pa Savanta Dhondu</t>
+          <t>Savant Anandi Dhondu Pa Savant Dhondu</t>
         </is>
       </c>
     </row>
@@ -63344,7 +63344,7 @@
       </c>
       <c r="K1147" t="inlineStr">
         <is>
-          <t>Kentura Shankarasaunga Bhagava</t>
+          <t>Kentura Shankarasaung Bhagava</t>
         </is>
       </c>
       <c r="L1147" t="inlineStr">
@@ -63401,12 +63401,12 @@
       </c>
       <c r="K1148" t="inlineStr">
         <is>
-          <t>Kentura Liladevi Shankarasinga</t>
+          <t>Kentura Liladevi Shankarasing</t>
         </is>
       </c>
       <c r="L1148" t="inlineStr">
         <is>
-          <t>Kentura Shankarasinga</t>
+          <t>Kentura Shankarasing</t>
         </is>
       </c>
     </row>
@@ -63458,12 +63458,12 @@
       </c>
       <c r="K1149" t="inlineStr">
         <is>
-          <t>Gavai Manohar Panduranga</t>
+          <t>Gavai Manohar Pandurang</t>
         </is>
       </c>
       <c r="L1149" t="inlineStr">
         <is>
-          <t>Gavai Panduranga</t>
+          <t>Gavai Pandurang</t>
         </is>
       </c>
     </row>
@@ -63681,12 +63681,12 @@
       </c>
       <c r="K1153" t="inlineStr">
         <is>
-          <t>Bandagae Sadananda Yashavanta</t>
+          <t>Bandagae Sadanand Yashavant</t>
         </is>
       </c>
       <c r="L1153" t="inlineStr">
         <is>
-          <t>Bandagae Yashavanta</t>
+          <t>Bandagae Yashavant</t>
         </is>
       </c>
     </row>
@@ -63743,12 +63743,12 @@
       </c>
       <c r="K1154" t="inlineStr">
         <is>
-          <t>Bandagae Suvarna Sadananda</t>
+          <t>Bandagae Suvarna Sadanand</t>
         </is>
       </c>
       <c r="L1154" t="inlineStr">
         <is>
-          <t>Bandagae Sadananda</t>
+          <t>Bandagae Sadanand</t>
         </is>
       </c>
     </row>
@@ -63800,12 +63800,12 @@
       </c>
       <c r="K1155" t="inlineStr">
         <is>
-          <t>Bandagae Sachin Sadananda</t>
+          <t>Bandagae Sachin Sadanand</t>
         </is>
       </c>
       <c r="L1155" t="inlineStr">
         <is>
-          <t>Bandagae Sadananda</t>
+          <t>Bandagae Sadanand</t>
         </is>
       </c>
     </row>
@@ -63857,12 +63857,12 @@
       </c>
       <c r="K1156" t="inlineStr">
         <is>
-          <t>Bandagae Sudhakar Sadananda</t>
+          <t>Bandagae Sudhakar Sadanand</t>
         </is>
       </c>
       <c r="L1156" t="inlineStr">
         <is>
-          <t>Bandagae Sadananda</t>
+          <t>Bandagae Sadanand</t>
         </is>
       </c>
     </row>
@@ -63914,12 +63914,12 @@
       </c>
       <c r="K1157" t="inlineStr">
         <is>
-          <t>Bandagae Sandip Yashavanta</t>
+          <t>Bandagae Sandip Yashavant</t>
         </is>
       </c>
       <c r="L1157" t="inlineStr">
         <is>
-          <t>Bandagae Yashavanta</t>
+          <t>Bandagae Yashavant</t>
         </is>
       </c>
     </row>
@@ -63971,7 +63971,7 @@
       </c>
       <c r="K1158" t="inlineStr">
         <is>
-          <t>Notiyal Maheshananda Sitaram</t>
+          <t>Notiyal Maheshanand Sitaram</t>
         </is>
       </c>
       <c r="L1158" t="inlineStr">
@@ -64033,7 +64033,7 @@
       </c>
       <c r="L1159" t="inlineStr">
         <is>
-          <t>Notiyal Maheshananda</t>
+          <t>Notiyal Maheshanand</t>
         </is>
       </c>
     </row>
@@ -64090,12 +64090,12 @@
       </c>
       <c r="K1160" t="inlineStr">
         <is>
-          <t>Notiyal Anil Maheshananda</t>
+          <t>Notiyal Anil Maheshanand</t>
         </is>
       </c>
       <c r="L1160" t="inlineStr">
         <is>
-          <t>Notiyal Maheshananda</t>
+          <t>Notiyal Maheshanand</t>
         </is>
       </c>
     </row>
@@ -64152,12 +64152,12 @@
       </c>
       <c r="K1161" t="inlineStr">
         <is>
-          <t>Notiyal Arun Maheshananda</t>
+          <t>Notiyal Arun Maheshanand</t>
         </is>
       </c>
       <c r="L1161" t="inlineStr">
         <is>
-          <t>Notiyal Maheshananda</t>
+          <t>Notiyal Maheshanand</t>
         </is>
       </c>
     </row>
@@ -64214,7 +64214,7 @@
       </c>
       <c r="L1162" t="inlineStr">
         <is>
-          <t>Kurup Govinda</t>
+          <t>Kurup Govind</t>
         </is>
       </c>
     </row>
@@ -64437,7 +64437,7 @@
       </c>
       <c r="K1166" t="inlineStr">
         <is>
-          <t>Nadar Ravidran Si</t>
+          <t>Nadar Ravidrana Si</t>
         </is>
       </c>
       <c r="L1166" t="inlineStr">
@@ -64494,12 +64494,12 @@
       </c>
       <c r="K1167" t="inlineStr">
         <is>
-          <t>Nadar Umamagheshvari Ravindran</t>
+          <t>Nadar Umamagheshvari Ravindrana</t>
         </is>
       </c>
       <c r="L1167" t="inlineStr">
         <is>
-          <t>Nadar Ravidran</t>
+          <t>Nadar Ravidrana</t>
         </is>
       </c>
     </row>
@@ -64551,12 +64551,12 @@
       </c>
       <c r="K1168" t="inlineStr">
         <is>
-          <t>Jadhav Nilesh Panduranga</t>
+          <t>Jadhav Nilesh Pandurang</t>
         </is>
       </c>
       <c r="L1168" t="inlineStr">
         <is>
-          <t>Jadhav Panduranga</t>
+          <t>Jadhav Pandurang</t>
         </is>
       </c>
     </row>
@@ -64608,7 +64608,7 @@
       </c>
       <c r="K1169" t="inlineStr">
         <is>
-          <t>Jadhav Panduranga Dhondu</t>
+          <t>Jadhav Pandurang Dhondu</t>
         </is>
       </c>
       <c r="L1169" t="inlineStr">
@@ -64665,12 +64665,12 @@
       </c>
       <c r="K1170" t="inlineStr">
         <is>
-          <t>Jadhav Pramila Panduranga</t>
+          <t>Jadhav Pramila Pandurang</t>
         </is>
       </c>
       <c r="L1170" t="inlineStr">
         <is>
-          <t>Jadhav Panduranga</t>
+          <t>Jadhav Pandurang</t>
         </is>
       </c>
     </row>
@@ -64764,7 +64764,7 @@
       </c>
       <c r="K1172" t="inlineStr">
         <is>
-          <t>Bokha Putul Mrunalakanta</t>
+          <t>Bokha Putul Mrunalakant</t>
         </is>
       </c>
       <c r="L1172" t="inlineStr">
@@ -64935,7 +64935,7 @@
       </c>
       <c r="K1175" t="inlineStr">
         <is>
-          <t>Tambe Shashikanta Shankar</t>
+          <t>Tambe Shashikant Shankar</t>
         </is>
       </c>
       <c r="L1175" t="inlineStr">
@@ -64997,12 +64997,12 @@
       </c>
       <c r="K1176" t="inlineStr">
         <is>
-          <t>Tambe Smita Shashikanta</t>
+          <t>Tambe Smita Shashikant</t>
         </is>
       </c>
       <c r="L1176" t="inlineStr">
         <is>
-          <t>Tambe Shashikanta</t>
+          <t>Tambe Shashikant</t>
         </is>
       </c>
     </row>
@@ -65054,12 +65054,12 @@
       </c>
       <c r="K1177" t="inlineStr">
         <is>
-          <t>Nayar Shradhiran Kuttan</t>
+          <t>Nayar Shradhiran Kuttana</t>
         </is>
       </c>
       <c r="L1177" t="inlineStr">
         <is>
-          <t>Nayar Kuttan</t>
+          <t>Nayar Kuttana</t>
         </is>
       </c>
     </row>
@@ -65163,7 +65163,7 @@
       </c>
       <c r="K1179" t="inlineStr">
         <is>
-          <t>Kundanab Bhaskaran Krushnan</t>
+          <t>Kundanab Bhaskaran Krushnana</t>
         </is>
       </c>
     </row>
@@ -65215,12 +65215,12 @@
       </c>
       <c r="K1180" t="inlineStr">
         <is>
-          <t>Miya~ Babujonna Alamashe</t>
+          <t>Miyan Babujonn Alamashe</t>
         </is>
       </c>
       <c r="L1180" t="inlineStr">
         <is>
-          <t>Miya~ Alamasher</t>
+          <t>Miyan Alamasher</t>
         </is>
       </c>
     </row>
@@ -65272,12 +65272,12 @@
       </c>
       <c r="K1181" t="inlineStr">
         <is>
-          <t>Miya~ Sayarabivi Babujon</t>
+          <t>Miyan Sayarabivi Babujon</t>
         </is>
       </c>
       <c r="L1181" t="inlineStr">
         <is>
-          <t>Miya~ Babujon</t>
+          <t>Miyan Babujon</t>
         </is>
       </c>
     </row>
@@ -65357,12 +65357,12 @@
       </c>
       <c r="K1184" t="inlineStr">
         <is>
-          <t>Miya~ Samimanisa Babujon</t>
+          <t>Miyan Samimanisa Babujon</t>
         </is>
       </c>
       <c r="L1184" t="inlineStr">
         <is>
-          <t>Miya~ Babujon</t>
+          <t>Miyan Babujon</t>
         </is>
       </c>
     </row>
@@ -65528,7 +65528,7 @@
       </c>
       <c r="K1187" t="inlineStr">
         <is>
-          <t>Barua Abhitabha Anupakuma</t>
+          <t>Barua Abhitabh Anupakuma</t>
         </is>
       </c>
       <c r="L1187" t="inlineStr">
@@ -65585,7 +65585,7 @@
       </c>
       <c r="K1188" t="inlineStr">
         <is>
-          <t>Barua Ajitabha Anupakuma</t>
+          <t>Barua Ajitabh Anupakuma</t>
         </is>
       </c>
       <c r="L1188" t="inlineStr">
@@ -65813,7 +65813,7 @@
       </c>
       <c r="K1192" t="inlineStr">
         <is>
-          <t>Nayar Satyan Svaminathan</t>
+          <t>Nayar Satyana Svaminathan</t>
         </is>
       </c>
       <c r="L1192" t="inlineStr">
@@ -66227,7 +66227,7 @@
       </c>
       <c r="K1199" t="inlineStr">
         <is>
-          <t>Dudavadakar Ananda Gajanan</t>
+          <t>Dudavadakar Anand Gajanan</t>
         </is>
       </c>
       <c r="L1199" t="inlineStr">
@@ -66284,12 +66284,12 @@
       </c>
       <c r="K1200" t="inlineStr">
         <is>
-          <t>Dudabadakar Ashvini Ananda</t>
+          <t>Dudabadakar Ashvini Anand</t>
         </is>
       </c>
       <c r="L1200" t="inlineStr">
         <is>
-          <t>Dudavarakar Ananda</t>
+          <t>Dudavarakar Anand</t>
         </is>
       </c>
     </row>
@@ -66512,12 +66512,12 @@
       </c>
       <c r="K1204" t="inlineStr">
         <is>
-          <t>Pille Shivanakutti Kuttappan</t>
+          <t>Pille Shivanakutti Kuttappana</t>
         </is>
       </c>
       <c r="L1204" t="inlineStr">
         <is>
-          <t>Pille Kuttappan</t>
+          <t>Pille Kuttappana</t>
         </is>
       </c>
     </row>
@@ -66626,12 +66626,12 @@
       </c>
       <c r="K1206" t="inlineStr">
         <is>
-          <t>Pille Lakshmi Kuttappan</t>
+          <t>Pille Lakshmi Kuttappana</t>
         </is>
       </c>
       <c r="L1206" t="inlineStr">
         <is>
-          <t>Pille Kuttappan</t>
+          <t>Pille Kuttappana</t>
         </is>
       </c>
     </row>
@@ -66968,7 +66968,7 @@
       </c>
       <c r="K1212" t="inlineStr">
         <is>
-          <t>Jakhia Chandrakanta Premaji</t>
+          <t>Jakhia Chandrakant Premaji</t>
         </is>
       </c>
       <c r="L1212" t="inlineStr">
@@ -67025,12 +67025,12 @@
       </c>
       <c r="K1213" t="inlineStr">
         <is>
-          <t>Jakhia Jasmina Chandrakanta</t>
+          <t>Jakhia Jasmina Chandrakant</t>
         </is>
       </c>
       <c r="L1213" t="inlineStr">
         <is>
-          <t>Jakhia Chandrakanta</t>
+          <t>Jakhia Chandrakant</t>
         </is>
       </c>
     </row>
@@ -67441,12 +67441,12 @@
       </c>
       <c r="K1221" t="inlineStr">
         <is>
-          <t>Nakhava Jivan Bhaskar</t>
+          <t>Nakhava Jivan Bhaskara</t>
         </is>
       </c>
       <c r="L1221" t="inlineStr">
         <is>
-          <t>Nakhava Bhaskar</t>
+          <t>Nakhava Bhaskara</t>
         </is>
       </c>
     </row>
@@ -67560,7 +67560,7 @@
       </c>
       <c r="K1223" t="inlineStr">
         <is>
-          <t>Bishta Khemasinha Chandrasih</t>
+          <t>Bishta Khemasinh Chandrasih</t>
         </is>
       </c>
       <c r="L1223" t="inlineStr">
@@ -67622,12 +67622,12 @@
       </c>
       <c r="K1224" t="inlineStr">
         <is>
-          <t>Bishta Pramod Khemasinha</t>
+          <t>Bishta Pramod Khemasinh</t>
         </is>
       </c>
       <c r="L1224" t="inlineStr">
         <is>
-          <t>Bishta Khemasinha</t>
+          <t>Bishta Khemasinh</t>
         </is>
       </c>
     </row>
@@ -67746,12 +67746,12 @@
       </c>
       <c r="K1226" t="inlineStr">
         <is>
-          <t>Bishta Gita Khemasinha</t>
+          <t>Bishta Gita Khemasinh</t>
         </is>
       </c>
       <c r="L1226" t="inlineStr">
         <is>
-          <t>Bishta Khemasinha</t>
+          <t>Bishta Khemasinh</t>
         </is>
       </c>
     </row>
@@ -67803,12 +67803,12 @@
       </c>
       <c r="K1227" t="inlineStr">
         <is>
-          <t>Mustapha Mohammad Kaundat</t>
+          <t>Mustapha Mohammada Kaundat</t>
         </is>
       </c>
       <c r="L1227" t="inlineStr">
         <is>
-          <t>Mohammad Kaundat</t>
+          <t>Mohammada Kaundat</t>
         </is>
       </c>
     </row>
@@ -67860,12 +67860,12 @@
       </c>
       <c r="K1228" t="inlineStr">
         <is>
-          <t>Mohammad Shabarina Mustapha</t>
+          <t>Mohammada Shabarina Mustapha</t>
         </is>
       </c>
       <c r="L1228" t="inlineStr">
         <is>
-          <t>Mohammad Mustapha</t>
+          <t>Mohammada Mustapha</t>
         </is>
       </c>
     </row>
@@ -68230,12 +68230,12 @@
       </c>
       <c r="K1236" t="inlineStr">
         <is>
-          <t>Bora Hanipha Mahammad</t>
+          <t>Bora Hanipha Mahammada</t>
         </is>
       </c>
       <c r="L1236" t="inlineStr">
         <is>
-          <t>Vora Mahammad</t>
+          <t>Vora Mahammada</t>
         </is>
       </c>
     </row>
@@ -68277,7 +68277,7 @@
       </c>
       <c r="K1237" t="inlineStr">
         <is>
-          <t>Mahammad Bora Hanipha</t>
+          <t>Mahammada Bora Hanipha</t>
         </is>
       </c>
     </row>
@@ -68319,7 +68319,7 @@
       </c>
       <c r="K1238" t="inlineStr">
         <is>
-          <t>Mahammad Vora Hanipha</t>
+          <t>Mahammada Vora Hanipha</t>
         </is>
       </c>
     </row>
@@ -68656,12 +68656,12 @@
       </c>
       <c r="K1244" t="inlineStr">
         <is>
-          <t>Rathod Rajendrasig Vikramasinga</t>
+          <t>Rathod Rajendrasig Vikramasing</t>
         </is>
       </c>
       <c r="L1244" t="inlineStr">
         <is>
-          <t>Rathod Vikramasinga</t>
+          <t>Rathod Vikramasing</t>
         </is>
       </c>
     </row>
@@ -68718,7 +68718,7 @@
       </c>
       <c r="L1245" t="inlineStr">
         <is>
-          <t>Rathod Rajendrasinga</t>
+          <t>Rathod Rajendrasing</t>
         </is>
       </c>
     </row>
@@ -69283,12 +69283,12 @@
       </c>
       <c r="K1255" t="inlineStr">
         <is>
-          <t>Shikhavat Rajavirasinga Anupasinga</t>
+          <t>Shikhavat Rajavirasing Anupasing</t>
         </is>
       </c>
       <c r="L1255" t="inlineStr">
         <is>
-          <t>Shikhavat Anupasinga</t>
+          <t>Shikhavat Anupasing</t>
         </is>
       </c>
     </row>
@@ -69340,12 +69340,12 @@
       </c>
       <c r="K1256" t="inlineStr">
         <is>
-          <t>Shikhavat Vinod Rajavirasinga</t>
+          <t>Shikhavat Vinod Rajavirasing</t>
         </is>
       </c>
       <c r="L1256" t="inlineStr">
         <is>
-          <t>Shikhavat Rajavirasinga</t>
+          <t>Shikhavat Rajavirasing</t>
         </is>
       </c>
     </row>
@@ -69397,12 +69397,12 @@
       </c>
       <c r="K1257" t="inlineStr">
         <is>
-          <t>Chauhan Samarasinga Padmasi</t>
+          <t>Chauhan Samarasing Padmasi</t>
         </is>
       </c>
       <c r="L1257" t="inlineStr">
         <is>
-          <t>Chauhan Padmasinga</t>
+          <t>Chauhan Padmasing</t>
         </is>
       </c>
     </row>
@@ -69459,7 +69459,7 @@
       </c>
       <c r="L1258" t="inlineStr">
         <is>
-          <t>Chauhan Samarasinga</t>
+          <t>Chauhan Samarasing</t>
         </is>
       </c>
     </row>
@@ -69511,12 +69511,12 @@
       </c>
       <c r="K1259" t="inlineStr">
         <is>
-          <t>Kundanapha Prasad Vishvanatha</t>
+          <t>Kundanaph Prasad Vishvanath</t>
         </is>
       </c>
       <c r="L1259" t="inlineStr">
         <is>
-          <t>Prasad Vishvanatha</t>
+          <t>Prasad Vishvanath</t>
         </is>
       </c>
     </row>
@@ -69568,12 +69568,12 @@
       </c>
       <c r="K1260" t="inlineStr">
         <is>
-          <t>Prasad Dipti Vishvanatha</t>
+          <t>Prasad Dipti Vishvanath</t>
         </is>
       </c>
       <c r="L1260" t="inlineStr">
         <is>
-          <t>Prasad Vishvanatha</t>
+          <t>Prasad Vishvanath</t>
         </is>
       </c>
     </row>
@@ -69625,12 +69625,12 @@
       </c>
       <c r="K1261" t="inlineStr">
         <is>
-          <t>Prasad Sangita Vishvanatha</t>
+          <t>Prasad Sangita Vishvanath</t>
         </is>
       </c>
       <c r="L1261" t="inlineStr">
         <is>
-          <t>Prasad Vishvanatha</t>
+          <t>Prasad Vishvanath</t>
         </is>
       </c>
     </row>
@@ -69682,12 +69682,12 @@
       </c>
       <c r="K1262" t="inlineStr">
         <is>
-          <t>Prasad Sanjay Vishvanatha</t>
+          <t>Prasad Sanjay Vishvanath</t>
         </is>
       </c>
       <c r="L1262" t="inlineStr">
         <is>
-          <t>Prasad Vishvanatha</t>
+          <t>Prasad Vishvanath</t>
         </is>
       </c>
     </row>
@@ -70185,7 +70185,7 @@
       </c>
       <c r="K1271" t="inlineStr">
         <is>
-          <t>Badrike Panduranga Sadashiv</t>
+          <t>Badrike Pandurang Sadashiv</t>
         </is>
       </c>
       <c r="L1271" t="inlineStr">
@@ -70242,12 +70242,12 @@
       </c>
       <c r="K1272" t="inlineStr">
         <is>
-          <t>Badrike Surekha Panduranga</t>
+          <t>Badrike Surekha Pandurang</t>
         </is>
       </c>
       <c r="L1272" t="inlineStr">
         <is>
-          <t>Badrike Panduranga</t>
+          <t>Badrike Pandurang</t>
         </is>
       </c>
     </row>
@@ -70726,12 +70726,12 @@
       </c>
       <c r="K1282" t="inlineStr">
         <is>
-          <t>Kakkar Pritam Paramananda</t>
+          <t>Kakkara Pritam Paramanand</t>
         </is>
       </c>
       <c r="L1282" t="inlineStr">
         <is>
-          <t>Kakkar Paramananda</t>
+          <t>Kakkara Paramanand</t>
         </is>
       </c>
     </row>
@@ -70783,12 +70783,12 @@
       </c>
       <c r="K1283" t="inlineStr">
         <is>
-          <t>Kakkar Rajakumari Pritam</t>
+          <t>Kakkara Rajakumari Pritam</t>
         </is>
       </c>
       <c r="L1283" t="inlineStr">
         <is>
-          <t>Kakkar Pritam</t>
+          <t>Kakkara Pritam</t>
         </is>
       </c>
     </row>
@@ -70840,12 +70840,12 @@
       </c>
       <c r="K1284" t="inlineStr">
         <is>
-          <t>Kakkar Ajay Pritam</t>
+          <t>Kakkara Ajay Pritam</t>
         </is>
       </c>
       <c r="L1284" t="inlineStr">
         <is>
-          <t>Kakkar Pritam</t>
+          <t>Kakkara Pritam</t>
         </is>
       </c>
     </row>
@@ -70897,12 +70897,12 @@
       </c>
       <c r="K1285" t="inlineStr">
         <is>
-          <t>Kakkar Anubala Ajay</t>
+          <t>Kakkara Anubala Ajay</t>
         </is>
       </c>
       <c r="L1285" t="inlineStr">
         <is>
-          <t>Kakkar Ajay</t>
+          <t>Kakkara Ajay</t>
         </is>
       </c>
     </row>
@@ -70954,12 +70954,12 @@
       </c>
       <c r="K1286" t="inlineStr">
         <is>
-          <t>Kakkar Ranjana Pritam</t>
+          <t>Kakkara Ranjana Pritam</t>
         </is>
       </c>
       <c r="L1286" t="inlineStr">
         <is>
-          <t>Kakkar Pritam</t>
+          <t>Kakkara Pritam</t>
         </is>
       </c>
     </row>
@@ -71001,7 +71001,7 @@
       </c>
       <c r="K1287" t="inlineStr">
         <is>
-          <t>Vach Kakkar Pritam</t>
+          <t>Vach Kakkara Pritam</t>
         </is>
       </c>
     </row>
@@ -71053,12 +71053,12 @@
       </c>
       <c r="K1288" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanatha Baavanta</t>
+          <t>Chavhan Vishvanath Baavant</t>
         </is>
       </c>
       <c r="L1288" t="inlineStr">
         <is>
-          <t>Chavhan Baavanta</t>
+          <t>Chavhan Baavant</t>
         </is>
       </c>
     </row>
@@ -71110,12 +71110,12 @@
       </c>
       <c r="K1289" t="inlineStr">
         <is>
-          <t>Chavhan Prabha Vishvanatha</t>
+          <t>Chavhan Prabha Vishvanath</t>
         </is>
       </c>
       <c r="L1289" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanatha</t>
+          <t>Chavhan Vishvanath</t>
         </is>
       </c>
     </row>
@@ -71167,12 +71167,12 @@
       </c>
       <c r="K1290" t="inlineStr">
         <is>
-          <t>Chavhan Sadananda Vishvanatha</t>
+          <t>Chavhan Sadanand Vishvanath</t>
         </is>
       </c>
       <c r="L1290" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanatha</t>
+          <t>Chavhan Vishvanath</t>
         </is>
       </c>
     </row>
@@ -71224,12 +71224,12 @@
       </c>
       <c r="K1291" t="inlineStr">
         <is>
-          <t>Chavhan Kamal Vishvanatha</t>
+          <t>Chavhan Kamal Vishvanath</t>
         </is>
       </c>
       <c r="L1291" t="inlineStr">
         <is>
-          <t>Chavhan Vishvanatha</t>
+          <t>Chavhan Vishvanath</t>
         </is>
       </c>
     </row>
@@ -71271,7 +71271,7 @@
       </c>
       <c r="K1292" t="inlineStr">
         <is>
-          <t>Vach Chavhan Vishvanatha</t>
+          <t>Vach Chavhan Vishvanath</t>
         </is>
       </c>
     </row>
@@ -72964,7 +72964,7 @@
       </c>
       <c r="K1321" t="inlineStr">
         <is>
-          <t>Ghag Shashanka Harishchandra</t>
+          <t>Ghag Shashank Harishchandra</t>
         </is>
       </c>
       <c r="L1321" t="inlineStr">
@@ -73178,12 +73178,12 @@
       </c>
       <c r="K1326" t="inlineStr">
         <is>
-          <t>Nerakar Dipti Dasharatha</t>
+          <t>Nerakar Dipti Dasharath</t>
         </is>
       </c>
       <c r="L1326" t="inlineStr">
         <is>
-          <t>Nerakar Dasharatha</t>
+          <t>Nerakar Dasharath</t>
         </is>
       </c>
     </row>
@@ -73225,7 +73225,7 @@
       </c>
       <c r="K1327" t="inlineStr">
         <is>
-          <t>Bhiva Nerakar Dasharatha</t>
+          <t>Bhiva Nerakar Dasharath</t>
         </is>
       </c>
     </row>
@@ -73277,12 +73277,12 @@
       </c>
       <c r="K1328" t="inlineStr">
         <is>
-          <t>Nerakar Darshana Dasharatha</t>
+          <t>Nerakar Darshana Dasharath</t>
         </is>
       </c>
       <c r="L1328" t="inlineStr">
         <is>
-          <t>Nerakar Dasharatha</t>
+          <t>Nerakar Dasharath</t>
         </is>
       </c>
     </row>
@@ -73753,7 +73753,7 @@
       </c>
       <c r="K1336" t="inlineStr">
         <is>
-          <t>Saavi Sachin Shyamasunda</t>
+          <t>Saavi Sachin Shyamasund</t>
         </is>
       </c>
       <c r="L1336" t="inlineStr">
@@ -74484,12 +74484,12 @@
       </c>
       <c r="K1349" t="inlineStr">
         <is>
-          <t>Gavai Devadas Ekanatha</t>
+          <t>Gavai Devadas Ekanath</t>
         </is>
       </c>
       <c r="L1349" t="inlineStr">
         <is>
-          <t>Gavai Ekanatha</t>
+          <t>Gavai Ekanath</t>
         </is>
       </c>
     </row>
@@ -74598,7 +74598,7 @@
       </c>
       <c r="K1351" t="inlineStr">
         <is>
-          <t>Shelar Bhaskar Shankar</t>
+          <t>Shelar Bhaskara Shankar</t>
         </is>
       </c>
       <c r="L1351" t="inlineStr">
@@ -74660,12 +74660,12 @@
       </c>
       <c r="K1352" t="inlineStr">
         <is>
-          <t>Shelar Bharati Bhaskar</t>
+          <t>Shelar Bharati Bhaskara</t>
         </is>
       </c>
       <c r="L1352" t="inlineStr">
         <is>
-          <t>Shelar Bhaskar</t>
+          <t>Shelar Bhaskara</t>
         </is>
       </c>
     </row>
@@ -74722,12 +74722,12 @@
       </c>
       <c r="K1353" t="inlineStr">
         <is>
-          <t>Shelar Santosh Bhaskar</t>
+          <t>Shelar Santosh Bhaskara</t>
         </is>
       </c>
       <c r="L1353" t="inlineStr">
         <is>
-          <t>Shelar Bhaskar</t>
+          <t>Shelar Bhaskara</t>
         </is>
       </c>
     </row>
@@ -74826,7 +74826,7 @@
       </c>
       <c r="K1355" t="inlineStr">
         <is>
-          <t>Shelar Vaishali Bhaskar Va Shelar Bhaskar Satri</t>
+          <t>Shelar Vaishali Bhaskara Va Shelar Bhaskara Satri</t>
         </is>
       </c>
     </row>
@@ -74883,12 +74883,12 @@
       </c>
       <c r="K1356" t="inlineStr">
         <is>
-          <t>Shelar Mahesh Bhaskar</t>
+          <t>Shelar Mahesh Bhaskara</t>
         </is>
       </c>
       <c r="L1356" t="inlineStr">
         <is>
-          <t>Shelar Bhaskar</t>
+          <t>Shelar Bhaskara</t>
         </is>
       </c>
     </row>
@@ -75354,7 +75354,7 @@
       </c>
       <c r="K1364" t="inlineStr">
         <is>
-          <t>Saavi Milinda Dattaram</t>
+          <t>Saavi Milind Dattaram</t>
         </is>
       </c>
       <c r="L1364" t="inlineStr">
@@ -75468,7 +75468,7 @@
       </c>
       <c r="K1366" t="inlineStr">
         <is>
-          <t>Gurav Panduranga Dhondu</t>
+          <t>Gurav Pandurang Dhondu</t>
         </is>
       </c>
       <c r="L1366" t="inlineStr">
@@ -75525,12 +75525,12 @@
       </c>
       <c r="K1367" t="inlineStr">
         <is>
-          <t>Gurav Sudhan Panduranga</t>
+          <t>Gurav Sudhan Pandurang</t>
         </is>
       </c>
       <c r="L1367" t="inlineStr">
         <is>
-          <t>Gurav Panduranga</t>
+          <t>Gurav Pandurang</t>
         </is>
       </c>
     </row>
@@ -75582,7 +75582,7 @@
       </c>
       <c r="K1368" t="inlineStr">
         <is>
-          <t>Pavar Viththal Sajanu</t>
+          <t>Pavar Viththala Sajanu</t>
         </is>
       </c>
       <c r="L1368" t="inlineStr">
@@ -75639,12 +75639,12 @@
       </c>
       <c r="K1369" t="inlineStr">
         <is>
-          <t>Pavar Sumati Viththal</t>
+          <t>Pavar Sumati Viththala</t>
         </is>
       </c>
       <c r="L1369" t="inlineStr">
         <is>
-          <t>Pavar Viththal</t>
+          <t>Pavar Viththala</t>
         </is>
       </c>
     </row>
@@ -75701,7 +75701,7 @@
       </c>
       <c r="L1370" t="inlineStr">
         <is>
-          <t>Pavar Viththal</t>
+          <t>Pavar Viththala</t>
         </is>
       </c>
     </row>
@@ -75796,12 +75796,12 @@
       </c>
       <c r="K1373" t="inlineStr">
         <is>
-          <t>Kadam Sharad Ananta</t>
+          <t>Kadam Sharad Anant</t>
         </is>
       </c>
       <c r="L1373" t="inlineStr">
         <is>
-          <t>Kadam Ananta</t>
+          <t>Kadam Anant</t>
         </is>
       </c>
     </row>
@@ -75910,12 +75910,12 @@
       </c>
       <c r="K1375" t="inlineStr">
         <is>
-          <t>Kadam Sanjay Ananta</t>
+          <t>Kadam Sanjay Anant</t>
         </is>
       </c>
       <c r="L1375" t="inlineStr">
         <is>
-          <t>Kadam Ananta</t>
+          <t>Kadam Anant</t>
         </is>
       </c>
     </row>
@@ -75967,7 +75967,7 @@
       </c>
       <c r="K1376" t="inlineStr">
         <is>
-          <t>Saavi Jayavanta Chandrarav</t>
+          <t>Saavi Jayavant Chandrarav</t>
         </is>
       </c>
       <c r="L1376" t="inlineStr">
@@ -76029,12 +76029,12 @@
       </c>
       <c r="K1377" t="inlineStr">
         <is>
-          <t>Saavi Nita Jayavanta</t>
+          <t>Saavi Nita Jayavant</t>
         </is>
       </c>
       <c r="L1377" t="inlineStr">
         <is>
-          <t>Saavi Jayavanta</t>
+          <t>Saavi Jayavant</t>
         </is>
       </c>
     </row>
@@ -76086,12 +76086,12 @@
       </c>
       <c r="K1378" t="inlineStr">
         <is>
-          <t>Saavi Atul Jayavanta</t>
+          <t>Saavi Atul Jayavant</t>
         </is>
       </c>
       <c r="L1378" t="inlineStr">
         <is>
-          <t>Saavi Jayavanta</t>
+          <t>Saavi Jayavant</t>
         </is>
       </c>
     </row>
@@ -76143,12 +76143,12 @@
       </c>
       <c r="K1379" t="inlineStr">
         <is>
-          <t>Saavi Mahesh Jayavanta</t>
+          <t>Saavi Mahesh Jayavant</t>
         </is>
       </c>
       <c r="L1379" t="inlineStr">
         <is>
-          <t>Saavi Jayavanta</t>
+          <t>Saavi Jayavant</t>
         </is>
       </c>
     </row>
@@ -76200,12 +76200,12 @@
       </c>
       <c r="K1380" t="inlineStr">
         <is>
-          <t>Saavi Sagar Jayavanta</t>
+          <t>Saavi Sagar Jayavant</t>
         </is>
       </c>
       <c r="L1380" t="inlineStr">
         <is>
-          <t>Saavi Jayavanta</t>
+          <t>Saavi Jayavant</t>
         </is>
       </c>
     </row>
@@ -76257,7 +76257,7 @@
       </c>
       <c r="K1381" t="inlineStr">
         <is>
-          <t>Manjarekar Panduranga Sakharam</t>
+          <t>Manjarekar Pandurang Sakharam</t>
         </is>
       </c>
       <c r="L1381" t="inlineStr">
@@ -76314,12 +76314,12 @@
       </c>
       <c r="K1382" t="inlineStr">
         <is>
-          <t>Manjarekar Rajashri Panduranga</t>
+          <t>Manjarekar Rajashri Pandurang</t>
         </is>
       </c>
       <c r="L1382" t="inlineStr">
         <is>
-          <t>Manjarekar Panduranga</t>
+          <t>Manjarekar Pandurang</t>
         </is>
       </c>
     </row>
@@ -76371,12 +76371,12 @@
       </c>
       <c r="K1383" t="inlineStr">
         <is>
-          <t>Manjarekar Yatin Panduranga</t>
+          <t>Manjarekar Yatin Pandurang</t>
         </is>
       </c>
       <c r="L1383" t="inlineStr">
         <is>
-          <t>Manjarekar Panduranga</t>
+          <t>Manjarekar Pandurang</t>
         </is>
       </c>
     </row>
@@ -76433,7 +76433,7 @@
       </c>
       <c r="L1384" t="inlineStr">
         <is>
-          <t>Manjarekar Panduranga</t>
+          <t>Manjarekar Pandurang</t>
         </is>
       </c>
     </row>
@@ -76485,12 +76485,12 @@
       </c>
       <c r="K1385" t="inlineStr">
         <is>
-          <t>Manjarekar Lalita Panduranga</t>
+          <t>Manjarekar Lalita Pandurang</t>
         </is>
       </c>
       <c r="L1385" t="inlineStr">
         <is>
-          <t>Manjarekar Panduranga</t>
+          <t>Manjarekar Pandurang</t>
         </is>
       </c>
     </row>
@@ -76547,7 +76547,7 @@
       </c>
       <c r="K1386" t="inlineStr">
         <is>
-          <t>Jadhav Ananta Shankar</t>
+          <t>Jadhav Anant Shankar</t>
         </is>
       </c>
       <c r="L1386" t="inlineStr">
@@ -76609,12 +76609,12 @@
       </c>
       <c r="K1387" t="inlineStr">
         <is>
-          <t>Jadhav Nilima Ananta</t>
+          <t>Jadhav Nilima Anant</t>
         </is>
       </c>
       <c r="L1387" t="inlineStr">
         <is>
-          <t>Jadhav Ananta</t>
+          <t>Jadhav Anant</t>
         </is>
       </c>
     </row>
@@ -76666,12 +76666,12 @@
       </c>
       <c r="K1388" t="inlineStr">
         <is>
-          <t>Jadhav Sanjog Ananta</t>
+          <t>Jadhav Sanjog Anant</t>
         </is>
       </c>
       <c r="L1388" t="inlineStr">
         <is>
-          <t>Jadhav Ananta</t>
+          <t>Jadhav Anant</t>
         </is>
       </c>
     </row>
@@ -76713,7 +76713,7 @@
       </c>
       <c r="K1389" t="inlineStr">
         <is>
-          <t>Sanjog Jadhav Ananta</t>
+          <t>Sanjog Jadhav Anant</t>
         </is>
       </c>
     </row>
@@ -77112,12 +77112,12 @@
       </c>
       <c r="K1396" t="inlineStr">
         <is>
-          <t>Kadam Vinayak Lakshman</t>
+          <t>Kadam Vinayak Lakshmana</t>
         </is>
       </c>
       <c r="L1396" t="inlineStr">
         <is>
-          <t>Kadam Lakshman</t>
+          <t>Kadam Lakshmana</t>
         </is>
       </c>
     </row>
@@ -78150,7 +78150,7 @@
       </c>
       <c r="L1415" t="inlineStr">
         <is>
-          <t>Solanko Govinda</t>
+          <t>Solanko Govind</t>
         </is>
       </c>
     </row>
@@ -78317,7 +78317,7 @@
       </c>
       <c r="K1419" t="inlineStr">
         <is>
-          <t>More Chandrakanta Gopa</t>
+          <t>More Chandrakant Gopa</t>
         </is>
       </c>
       <c r="L1419" t="inlineStr">
@@ -78374,12 +78374,12 @@
       </c>
       <c r="K1420" t="inlineStr">
         <is>
-          <t>More Nita Chandrakanta</t>
+          <t>More Nita Chandrakant</t>
         </is>
       </c>
       <c r="L1420" t="inlineStr">
         <is>
-          <t>More Chandrakanta</t>
+          <t>More Chandrakant</t>
         </is>
       </c>
     </row>
@@ -78545,12 +78545,12 @@
       </c>
       <c r="K1423" t="inlineStr">
         <is>
-          <t>Jadhav Kanu Lakshman</t>
+          <t>Jadhav Kanu Lakshmana</t>
         </is>
       </c>
       <c r="L1423" t="inlineStr">
         <is>
-          <t>Jadhav Lakshman</t>
+          <t>Jadhav Lakshmana</t>
         </is>
       </c>
     </row>
@@ -78649,7 +78649,7 @@
       </c>
       <c r="K1425" t="inlineStr">
         <is>
-          <t>Lakshman Jadhav Kanu</t>
+          <t>Lakshmana Jadhav Kanu</t>
         </is>
       </c>
     </row>
@@ -78701,7 +78701,7 @@
       </c>
       <c r="K1426" t="inlineStr">
         <is>
-          <t>Dhuri Lakshman Prabhakar</t>
+          <t>Dhuri Lakshmana Prabhakar</t>
         </is>
       </c>
       <c r="L1426" t="inlineStr">
@@ -78748,7 +78748,7 @@
       </c>
       <c r="K1427" t="inlineStr">
         <is>
-          <t>Prabhakar Dhuri Lakshman</t>
+          <t>Prabhakar Dhuri Lakshmana</t>
         </is>
       </c>
     </row>
@@ -78842,12 +78842,12 @@
       </c>
       <c r="K1429" t="inlineStr">
         <is>
-          <t>Dhuri Snehal Lakshman</t>
+          <t>Dhuri Snehal Lakshmana</t>
         </is>
       </c>
       <c r="L1429" t="inlineStr">
         <is>
-          <t>Dhuri Lakshman</t>
+          <t>Dhuri Lakshmana</t>
         </is>
       </c>
     </row>
@@ -78889,7 +78889,7 @@
       </c>
       <c r="K1430" t="inlineStr">
         <is>
-          <t>Prabhakar Dhuri Lakshman</t>
+          <t>Prabhakar Dhuri Lakshmana</t>
         </is>
       </c>
     </row>
@@ -78941,7 +78941,7 @@
       </c>
       <c r="K1431" t="inlineStr">
         <is>
-          <t>Nikam Ananta Govinda</t>
+          <t>Nikam Anant Govind</t>
         </is>
       </c>
       <c r="L1431" t="inlineStr">
@@ -78998,12 +78998,12 @@
       </c>
       <c r="K1432" t="inlineStr">
         <is>
-          <t>Nikam Arati Ananta</t>
+          <t>Nikam Arati Anant</t>
         </is>
       </c>
       <c r="L1432" t="inlineStr">
         <is>
-          <t>Nikam Ananta</t>
+          <t>Nikam Anant</t>
         </is>
       </c>
     </row>
@@ -79055,12 +79055,12 @@
       </c>
       <c r="K1433" t="inlineStr">
         <is>
-          <t>Shekha Mahamadajaphar Imauddin</t>
+          <t>Shekh Mahamadajaphar Imauddin</t>
         </is>
       </c>
       <c r="L1433" t="inlineStr">
         <is>
-          <t>Shekha Imauddin</t>
+          <t>Shekh Imauddin</t>
         </is>
       </c>
     </row>
@@ -79112,12 +79112,12 @@
       </c>
       <c r="K1434" t="inlineStr">
         <is>
-          <t>Shekha Aripha Mahamadajaphar</t>
+          <t>Shekh Aripha Mahamadajaphar</t>
         </is>
       </c>
       <c r="L1434" t="inlineStr">
         <is>
-          <t>Shekha Mahamadajaphar</t>
+          <t>Shekh Mahamadajaphar</t>
         </is>
       </c>
     </row>
@@ -79625,7 +79625,7 @@
       </c>
       <c r="K1443" t="inlineStr">
         <is>
-          <t>Kae Shriram Govinda</t>
+          <t>Kae Shriram Govind</t>
         </is>
       </c>
       <c r="L1443" t="inlineStr">
@@ -80081,7 +80081,7 @@
       </c>
       <c r="K1451" t="inlineStr">
         <is>
-          <t>Rasam Prashanta Prabhakar</t>
+          <t>Rasam Prashant Prabhakar</t>
         </is>
       </c>
       <c r="L1451" t="inlineStr">
@@ -80596,7 +80596,7 @@
       </c>
       <c r="K1461" t="inlineStr">
         <is>
-          <t>Martad Dikshit Sarasvati</t>
+          <t>Martada Dikshit Sarasvati</t>
         </is>
       </c>
     </row>
@@ -80810,7 +80810,7 @@
       </c>
       <c r="K1466" t="inlineStr">
         <is>
-          <t>Vach Vagha Baavanta</t>
+          <t>Vach Vagh Baavant</t>
         </is>
       </c>
     </row>
@@ -80862,12 +80862,12 @@
       </c>
       <c r="K1467" t="inlineStr">
         <is>
-          <t>Vagha Sunita Bhairinatha</t>
+          <t>Vagh Sunita Bhairinath</t>
         </is>
       </c>
       <c r="L1467" t="inlineStr">
         <is>
-          <t>Vagha Bhairinatha</t>
+          <t>Vagh Bhairinath</t>
         </is>
       </c>
     </row>
@@ -81199,12 +81199,12 @@
       </c>
       <c r="K1473" t="inlineStr">
         <is>
-          <t>Vainjakar Kashinatha Viththal</t>
+          <t>Vainjakar Kashinath Viththala</t>
         </is>
       </c>
       <c r="L1473" t="inlineStr">
         <is>
-          <t>Vainjakar Viththal</t>
+          <t>Vainjakar Viththala</t>
         </is>
       </c>
     </row>
@@ -81256,12 +81256,12 @@
       </c>
       <c r="K1474" t="inlineStr">
         <is>
-          <t>Vainjakar Smita Kashinatha</t>
+          <t>Vainjakar Smita Kashinath</t>
         </is>
       </c>
       <c r="L1474" t="inlineStr">
         <is>
-          <t>Vainjakar Kashinatha</t>
+          <t>Vainjakar Kashinath</t>
         </is>
       </c>
     </row>
@@ -81313,12 +81313,12 @@
       </c>
       <c r="K1475" t="inlineStr">
         <is>
-          <t>Varaujakar Krushnakanta Kashinatha</t>
+          <t>Varaujakar Krushnakant Kashinath</t>
         </is>
       </c>
       <c r="L1475" t="inlineStr">
         <is>
-          <t>Varijakar Kashinatha</t>
+          <t>Varijakar Kashinath</t>
         </is>
       </c>
     </row>
@@ -81370,12 +81370,12 @@
       </c>
       <c r="K1476" t="inlineStr">
         <is>
-          <t>Vaijakar Bharat Kashinatha</t>
+          <t>Vaijakar Bharat Kashinath</t>
         </is>
       </c>
       <c r="L1476" t="inlineStr">
         <is>
-          <t>Varijakar Kashinatha</t>
+          <t>Varijakar Kashinath</t>
         </is>
       </c>
     </row>
@@ -81417,7 +81417,7 @@
       </c>
       <c r="K1477" t="inlineStr">
         <is>
-          <t>Krushnakanta Vainjakar Kashinatha</t>
+          <t>Krushnakant Vainjakar Kashinath</t>
         </is>
       </c>
     </row>
@@ -81459,7 +81459,7 @@
       </c>
       <c r="K1478" t="inlineStr">
         <is>
-          <t>Bharat Vaijakar Kashinatha</t>
+          <t>Bharat Vaijakar Kashinath</t>
         </is>
       </c>
     </row>
@@ -81739,7 +81739,7 @@
       </c>
       <c r="K1483" t="inlineStr">
         <is>
-          <t>Kumbhar Chaya Govinda</t>
+          <t>Kumbhar Chaya Govind</t>
         </is>
       </c>
       <c r="L1483" t="inlineStr">
@@ -81853,12 +81853,12 @@
       </c>
       <c r="K1485" t="inlineStr">
         <is>
-          <t>Kumbhar Pradip Govinda</t>
+          <t>Kumbhar Pradip Govind</t>
         </is>
       </c>
       <c r="L1485" t="inlineStr">
         <is>
-          <t>Kumbhar Govinda</t>
+          <t>Kumbhar Govind</t>
         </is>
       </c>
     </row>
@@ -82024,7 +82024,7 @@
       </c>
       <c r="K1488" t="inlineStr">
         <is>
-          <t>Bhalerav Dasharatha Nana</t>
+          <t>Bhalerav Dasharath Nana</t>
         </is>
       </c>
       <c r="L1488" t="inlineStr">
@@ -82081,12 +82081,12 @@
       </c>
       <c r="K1489" t="inlineStr">
         <is>
-          <t>Bhalerav Gayabai Dasharatha</t>
+          <t>Bhalerav Gayabai Dasharath</t>
         </is>
       </c>
       <c r="L1489" t="inlineStr">
         <is>
-          <t>Bhalerav Dasharatha</t>
+          <t>Bhalerav Dasharath</t>
         </is>
       </c>
     </row>
@@ -82133,7 +82133,7 @@
       </c>
       <c r="K1490" t="inlineStr">
         <is>
-          <t>Vab Bhalerav Dasharatha</t>
+          <t>Vab Bhalerav Dasharath</t>
         </is>
       </c>
     </row>
@@ -82175,7 +82175,7 @@
       </c>
       <c r="K1491" t="inlineStr">
         <is>
-          <t>Dinesh Bhalerav Dasharatha</t>
+          <t>Dinesh Bhalerav Dasharath</t>
         </is>
       </c>
     </row>
@@ -82227,12 +82227,12 @@
       </c>
       <c r="K1492" t="inlineStr">
         <is>
-          <t>Bhalerav Santosh Dasharatha</t>
+          <t>Bhalerav Santosh Dasharath</t>
         </is>
       </c>
       <c r="L1492" t="inlineStr">
         <is>
-          <t>Bhalerav Dasharatha</t>
+          <t>Bhalerav Dasharath</t>
         </is>
       </c>
     </row>
@@ -82522,12 +82522,12 @@
       </c>
       <c r="K1497" t="inlineStr">
         <is>
-          <t>Janavalekar Kashinatha Panduranga</t>
+          <t>Janavalekar Kashinath Pandurang</t>
         </is>
       </c>
       <c r="L1497" t="inlineStr">
         <is>
-          <t>Janavalekar Panduranga</t>
+          <t>Janavalekar Pandurang</t>
         </is>
       </c>
     </row>
@@ -82579,12 +82579,12 @@
       </c>
       <c r="K1498" t="inlineStr">
         <is>
-          <t>Janavalekar Kanta Kashinatha</t>
+          <t>Janavalekar Kanta Kashinath</t>
         </is>
       </c>
       <c r="L1498" t="inlineStr">
         <is>
-          <t>Janavalekar Kashinatha</t>
+          <t>Janavalekar Kashinath</t>
         </is>
       </c>
     </row>
@@ -82636,12 +82636,12 @@
       </c>
       <c r="K1499" t="inlineStr">
         <is>
-          <t>Janavalekar Kishor Kashinatha</t>
+          <t>Janavalekar Kishor Kashinath</t>
         </is>
       </c>
       <c r="L1499" t="inlineStr">
         <is>
-          <t>Janavalekar Kashinatha</t>
+          <t>Janavalekar Kashinath</t>
         </is>
       </c>
     </row>
@@ -82683,7 +82683,7 @@
       </c>
       <c r="K1500" t="inlineStr">
         <is>
-          <t>Kishor Janavalekar Kashinatha</t>
+          <t>Kishor Janavalekar Kashinath</t>
         </is>
       </c>
     </row>
@@ -83323,7 +83323,7 @@
       </c>
       <c r="K1513" t="inlineStr">
         <is>
-          <t>Satam Suryakanta Shankar</t>
+          <t>Satam Suryakant Shankar</t>
         </is>
       </c>
       <c r="L1513" t="inlineStr">
@@ -83385,12 +83385,12 @@
       </c>
       <c r="K1514" t="inlineStr">
         <is>
-          <t>Satam Suvarnalata Suryakanta</t>
+          <t>Satam Suvarnalata Suryakant</t>
         </is>
       </c>
       <c r="L1514" t="inlineStr">
         <is>
-          <t>Satam Suryakanta</t>
+          <t>Satam Suryakant</t>
         </is>
       </c>
     </row>
@@ -83447,7 +83447,7 @@
       </c>
       <c r="K1515" t="inlineStr">
         <is>
-          <t>Satam Hemanta Suryakanta</t>
+          <t>Satam Hemant Suryakant</t>
         </is>
       </c>
       <c r="L1515" t="inlineStr">
@@ -83504,12 +83504,12 @@
       </c>
       <c r="K1516" t="inlineStr">
         <is>
-          <t>Satam Shrikanta Suryakanta</t>
+          <t>Satam Shrikant Suryakant</t>
         </is>
       </c>
       <c r="L1516" t="inlineStr">
         <is>
-          <t>Satam Suryakanta</t>
+          <t>Satam Suryakant</t>
         </is>
       </c>
     </row>
@@ -83913,7 +83913,7 @@
       </c>
       <c r="K1523" t="inlineStr">
         <is>
-          <t>Banjari Shrimanta Keru</t>
+          <t>Banjari Shrimant Keru</t>
         </is>
       </c>
       <c r="L1523" t="inlineStr">
@@ -83970,12 +83970,12 @@
       </c>
       <c r="K1524" t="inlineStr">
         <is>
-          <t>Banjari Dhanashri Shrimanta</t>
+          <t>Banjari Dhanashri Shrimant</t>
         </is>
       </c>
       <c r="L1524" t="inlineStr">
         <is>
-          <t>Vanjari Shrimanta</t>
+          <t>Vanjari Shrimant</t>
         </is>
       </c>
     </row>
@@ -84017,7 +84017,7 @@
       </c>
       <c r="K1525" t="inlineStr">
         <is>
-          <t>Keru Banjari Shrimanta</t>
+          <t>Keru Banjari Shrimant</t>
         </is>
       </c>
     </row>
@@ -84282,7 +84282,7 @@
       </c>
       <c r="K1530" t="inlineStr">
         <is>
-          <t>Sonavane Varsha Chandukha</t>
+          <t>Sonavane Varsha Chandukh</t>
         </is>
       </c>
       <c r="L1530" t="inlineStr">
@@ -84510,12 +84510,12 @@
       </c>
       <c r="K1534" t="inlineStr">
         <is>
-          <t>Thakur Sunil Rupasinga</t>
+          <t>Thakur Sunil Rupasing</t>
         </is>
       </c>
       <c r="L1534" t="inlineStr">
         <is>
-          <t>Thakur Rupasinga</t>
+          <t>Thakur Rupasing</t>
         </is>
       </c>
     </row>
@@ -84914,12 +84914,12 @@
       </c>
       <c r="K1541" t="inlineStr">
         <is>
-          <t>Thakuradesai Sanjay Kashinatha</t>
+          <t>Thakuradesai Sanjay Kashinath</t>
         </is>
       </c>
       <c r="L1541" t="inlineStr">
         <is>
-          <t>Thakuradesai Kashinatha</t>
+          <t>Thakuradesai Kashinath</t>
         </is>
       </c>
     </row>
@@ -85147,12 +85147,12 @@
       </c>
       <c r="K1545" t="inlineStr">
         <is>
-          <t>Shekha Shariphauddin Basirauddin</t>
+          <t>Shekh Shariphauddin Basirauddin</t>
         </is>
       </c>
       <c r="L1545" t="inlineStr">
         <is>
-          <t>Shekha Basirauddin</t>
+          <t>Shekh Basirauddin</t>
         </is>
       </c>
     </row>
@@ -85209,12 +85209,12 @@
       </c>
       <c r="K1546" t="inlineStr">
         <is>
-          <t>Shekha Rajiya Sharipha</t>
+          <t>Shekh Rajiya Shariph</t>
         </is>
       </c>
       <c r="L1546" t="inlineStr">
         <is>
-          <t>Shekha Sharipha</t>
+          <t>Shekh Shariph</t>
         </is>
       </c>
     </row>
@@ -85266,12 +85266,12 @@
       </c>
       <c r="K1547" t="inlineStr">
         <is>
-          <t>Shekha Rahena Sharipha</t>
+          <t>Shekh Rahena Shariph</t>
         </is>
       </c>
       <c r="L1547" t="inlineStr">
         <is>
-          <t>Shekha Sharipha</t>
+          <t>Shekh Shariph</t>
         </is>
       </c>
     </row>
@@ -85323,12 +85323,12 @@
       </c>
       <c r="K1548" t="inlineStr">
         <is>
-          <t>Shekha Sulatana Sharipha</t>
+          <t>Shekh Sulatana Shariph</t>
         </is>
       </c>
       <c r="L1548" t="inlineStr">
         <is>
-          <t>Shekha Sharipha</t>
+          <t>Shekh Shariph</t>
         </is>
       </c>
     </row>
